--- a/data_input/MI_Buildings_Oorschot2023.xlsx
+++ b/data_input/MI_Buildings_Oorschot2023.xlsx
@@ -1,47 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mira/Desktop/IE/REAL UTOPIAN HOUSING/Post-GrowthHousingScenarios/Code/data_input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mira/Documents/IE/REAL UTOPIAN HOUSING/Post-GrowthHousingScenarios/Code/housing-footprints/data_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB6C275-9FE7-164B-AF9A-FD045C886500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C266CA18-0F84-B645-8ED8-B1CC5C1D3A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41960" yWindow="500" windowWidth="22040" windowHeight="18320" tabRatio="902" activeTab="5" xr2:uid="{501A363E-84AB-4328-B285-EDCE5CC29F1E}"/>
+    <workbookView xWindow="10660" yWindow="500" windowWidth="14940" windowHeight="15500" tabRatio="902" activeTab="2" xr2:uid="{501A363E-84AB-4328-B285-EDCE5CC29F1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="24" r:id="rId1"/>
     <sheet name="meta" sheetId="31" r:id="rId2"/>
-    <sheet name="MI_2018" sheetId="22" r:id="rId3"/>
-    <sheet name="MI_2018-2050" sheetId="23" r:id="rId4"/>
-    <sheet name="Share_of_insulation_materials" sheetId="27" r:id="rId5"/>
-    <sheet name="GHG_Primary_production" sheetId="2" r:id="rId6"/>
-    <sheet name="GHG_Secondary_production" sheetId="1" r:id="rId7"/>
-    <sheet name="LCI_comparison" sheetId="14" r:id="rId8"/>
-    <sheet name="RR_MRC" sheetId="4" r:id="rId9"/>
-    <sheet name="UFA" sheetId="29" r:id="rId10"/>
-    <sheet name="Stock_2018_UFA" sheetId="30" r:id="rId11"/>
-    <sheet name="Stock_2018" sheetId="12" r:id="rId12"/>
-    <sheet name="Stock_2050" sheetId="13" r:id="rId13"/>
-    <sheet name="Stock_per_capita" sheetId="28" r:id="rId14"/>
-    <sheet name="Demand_outflow_recycled" sheetId="11" r:id="rId15"/>
-    <sheet name="Demand_outflow_urbanization" sheetId="18" r:id="rId16"/>
-    <sheet name="Demolition" sheetId="6" r:id="rId17"/>
-    <sheet name="Primary_secondary_demand" sheetId="8" r:id="rId18"/>
-    <sheet name="Demand" sheetId="5" r:id="rId19"/>
-    <sheet name="GHG" sheetId="9" r:id="rId20"/>
-    <sheet name="Land_occupation" sheetId="21" r:id="rId21"/>
-    <sheet name="Land_use" sheetId="15" r:id="rId22"/>
-    <sheet name="BAU_RR" sheetId="7" r:id="rId23"/>
-    <sheet name="Current_best_RR" sheetId="19" r:id="rId24"/>
-    <sheet name="Current_best_RR_II" sheetId="20" r:id="rId25"/>
-    <sheet name="Max_RR" sheetId="25" r:id="rId26"/>
+    <sheet name="mi_pre2018" sheetId="32" r:id="rId3"/>
+    <sheet name="MI_2018" sheetId="22" r:id="rId4"/>
+    <sheet name="MI_2018-2050" sheetId="23" r:id="rId5"/>
+    <sheet name="Share_of_insulation_materials" sheetId="27" r:id="rId6"/>
+    <sheet name="GHG_Primary_production" sheetId="2" r:id="rId7"/>
+    <sheet name="GHG_Secondary_production" sheetId="1" r:id="rId8"/>
+    <sheet name="LCI_comparison" sheetId="14" r:id="rId9"/>
+    <sheet name="RR_MRC" sheetId="4" r:id="rId10"/>
+    <sheet name="UFA" sheetId="29" r:id="rId11"/>
+    <sheet name="Stock_2018_UFA" sheetId="30" r:id="rId12"/>
+    <sheet name="Stock_2018" sheetId="12" r:id="rId13"/>
+    <sheet name="Stock_2050" sheetId="13" r:id="rId14"/>
+    <sheet name="Stock_per_capita" sheetId="28" r:id="rId15"/>
+    <sheet name="Demand_outflow_recycled" sheetId="11" r:id="rId16"/>
+    <sheet name="Demand_outflow_urbanization" sheetId="18" r:id="rId17"/>
+    <sheet name="Demolition" sheetId="6" r:id="rId18"/>
+    <sheet name="Primary_secondary_demand" sheetId="8" r:id="rId19"/>
+    <sheet name="Demand" sheetId="5" r:id="rId20"/>
+    <sheet name="GHG" sheetId="9" r:id="rId21"/>
+    <sheet name="Land_occupation" sheetId="21" r:id="rId22"/>
+    <sheet name="Land_use" sheetId="15" r:id="rId23"/>
+    <sheet name="BAU_RR" sheetId="7" r:id="rId24"/>
+    <sheet name="Current_best_RR" sheetId="19" r:id="rId25"/>
+    <sheet name="Current_best_RR_II" sheetId="20" r:id="rId26"/>
+    <sheet name="Max_RR" sheetId="25" r:id="rId27"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId27"/>
+    <externalReference r:id="rId28"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -81,8 +82,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="582">
   <si>
     <t>aluminium, wrought alloy | treatment of aluminium scrap, post-consumer, prepared for recycling, at remelter | RER | kilogram | cutoff38 - Janneke</t>
   </si>
@@ -2112,6 +2135,27 @@
   <si>
     <t>Baseline (without biobased construction)</t>
   </si>
+  <si>
+    <t>1975-2005</t>
+  </si>
+  <si>
+    <t>2006-2018</t>
+  </si>
+  <si>
+    <t>pre 1945</t>
+  </si>
+  <si>
+    <t>1946-1974</t>
+  </si>
+  <si>
+    <t>detached (vrijstaand)</t>
+  </si>
+  <si>
+    <t>row house (tussenwoning)</t>
+  </si>
+  <si>
+    <t>multiple fam (meergezins)</t>
+  </si>
 </sst>
 </file>
 
@@ -3226,7 +3270,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="604">
+  <cellXfs count="602">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4480,12 +4524,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -17675,6 +17713,868 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DF2012-C526-49AC-BBB5-413BFD42E12E}">
+  <sheetPr>
+    <tabColor theme="3" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:S52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.1640625" customWidth="1"/>
+    <col min="2" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="54.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" style="1"/>
+    <col min="9" max="9" width="44.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" customWidth="1"/>
+    <col min="15" max="15" width="19.6640625" customWidth="1"/>
+    <col min="16" max="16" width="23.5" customWidth="1"/>
+    <col min="17" max="17" width="25.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="258" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="394" t="s">
+        <v>498</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>500</v>
+      </c>
+      <c r="D1" s="89" t="s">
+        <v>497</v>
+      </c>
+      <c r="E1" s="89" t="s">
+        <v>367</v>
+      </c>
+      <c r="F1" s="259" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="567"/>
+      <c r="I1" s="567"/>
+      <c r="J1" s="567"/>
+      <c r="K1" s="567"/>
+      <c r="L1" s="567"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="42"/>
+      <c r="S1" s="188"/>
+    </row>
+    <row r="2" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="260" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="264">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="C2" s="265">
+        <f>0.53*0.85</f>
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="D2" s="266">
+        <v>1</v>
+      </c>
+      <c r="E2" s="266">
+        <v>0.37</v>
+      </c>
+      <c r="F2" s="267" t="s">
+        <v>429</v>
+      </c>
+      <c r="G2" s="268" t="s">
+        <v>366</v>
+      </c>
+      <c r="H2" s="270"/>
+      <c r="I2" s="271"/>
+      <c r="J2" s="271"/>
+      <c r="N2" s="272"/>
+      <c r="O2" s="273" t="s">
+        <v>280</v>
+      </c>
+      <c r="P2" s="273" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q2" s="273" t="s">
+        <v>282</v>
+      </c>
+      <c r="R2" s="273" t="s">
+        <v>283</v>
+      </c>
+      <c r="S2" s="274" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="261" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="264">
+        <v>0.01</v>
+      </c>
+      <c r="C3" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D3" s="266">
+        <v>1</v>
+      </c>
+      <c r="E3" s="266">
+        <v>0.25</v>
+      </c>
+      <c r="F3" s="275" t="s">
+        <v>430</v>
+      </c>
+      <c r="G3" s="276"/>
+      <c r="H3" s="270"/>
+      <c r="I3" s="271"/>
+      <c r="J3" s="271"/>
+      <c r="N3" s="277" t="s">
+        <v>197</v>
+      </c>
+      <c r="O3" s="271">
+        <v>11642</v>
+      </c>
+      <c r="P3" s="271">
+        <v>530</v>
+      </c>
+      <c r="Q3" s="271">
+        <v>53</v>
+      </c>
+      <c r="R3" s="278">
+        <f>Q3/O3</f>
+        <v>4.5524823913416935E-3</v>
+      </c>
+      <c r="S3" s="279">
+        <f>SUM(Q3:Q8)/SUM(O3:O8)</f>
+        <v>1.4528631597813424E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="261" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="264">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="C4" s="265">
+        <f>0.53*0.85</f>
+        <v>0.45050000000000001</v>
+      </c>
+      <c r="D4" s="266">
+        <v>1</v>
+      </c>
+      <c r="E4" s="266">
+        <v>0.37</v>
+      </c>
+      <c r="F4" s="275" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="276"/>
+      <c r="H4" s="270"/>
+      <c r="I4" s="271"/>
+      <c r="J4" s="271"/>
+      <c r="N4" s="280" t="s">
+        <v>237</v>
+      </c>
+      <c r="O4" s="271">
+        <v>42941</v>
+      </c>
+      <c r="P4" s="271">
+        <v>15029</v>
+      </c>
+      <c r="Q4" s="271">
+        <v>751</v>
+      </c>
+      <c r="R4" s="278">
+        <f t="shared" ref="R4:R8" si="0">Q4/O4</f>
+        <v>1.7489112968957405E-2</v>
+      </c>
+      <c r="S4" s="281"/>
+    </row>
+    <row r="5" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="260" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="264">
+        <v>0.9</v>
+      </c>
+      <c r="C5" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D5" s="265">
+        <v>1</v>
+      </c>
+      <c r="E5" s="265">
+        <v>1</v>
+      </c>
+      <c r="F5" s="267" t="s">
+        <v>433</v>
+      </c>
+      <c r="G5" s="282"/>
+      <c r="H5" s="270"/>
+      <c r="I5" s="271"/>
+      <c r="J5" s="271"/>
+      <c r="N5" s="283" t="s">
+        <v>196</v>
+      </c>
+      <c r="O5" s="271">
+        <v>7800</v>
+      </c>
+      <c r="P5" s="271">
+        <v>355</v>
+      </c>
+      <c r="Q5" s="271">
+        <v>0</v>
+      </c>
+      <c r="R5" s="278">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S5" s="281"/>
+    </row>
+    <row r="6" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="262" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="264">
+        <v>0</v>
+      </c>
+      <c r="C6" s="265">
+        <v>0</v>
+      </c>
+      <c r="D6" s="265">
+        <v>1</v>
+      </c>
+      <c r="E6" s="265">
+        <v>0</v>
+      </c>
+      <c r="F6" s="267" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" s="282"/>
+      <c r="H6" s="270"/>
+      <c r="I6" s="271"/>
+      <c r="J6" s="271"/>
+      <c r="N6" s="284" t="s">
+        <v>194</v>
+      </c>
+      <c r="O6" s="271">
+        <v>3185</v>
+      </c>
+      <c r="P6" s="271">
+        <v>145</v>
+      </c>
+      <c r="Q6" s="271">
+        <v>0</v>
+      </c>
+      <c r="R6" s="278">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S6" s="281"/>
+    </row>
+    <row r="7" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="262" t="s">
+        <v>196</v>
+      </c>
+      <c r="B7" s="264">
+        <v>0</v>
+      </c>
+      <c r="C7" s="265">
+        <v>0</v>
+      </c>
+      <c r="D7" s="265">
+        <v>1</v>
+      </c>
+      <c r="E7" s="265">
+        <v>0</v>
+      </c>
+      <c r="F7" s="267" t="s">
+        <v>195</v>
+      </c>
+      <c r="G7" s="285"/>
+      <c r="H7" s="270"/>
+      <c r="I7" s="271"/>
+      <c r="J7" s="271"/>
+      <c r="N7" s="286" t="s">
+        <v>199</v>
+      </c>
+      <c r="O7" s="271">
+        <v>20071</v>
+      </c>
+      <c r="P7" s="271">
+        <v>7025</v>
+      </c>
+      <c r="Q7" s="271">
+        <v>476</v>
+      </c>
+      <c r="R7" s="278">
+        <f t="shared" si="0"/>
+        <v>2.371580887848139E-2</v>
+      </c>
+      <c r="S7" s="281"/>
+    </row>
+    <row r="8" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="262" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="264">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C8" s="265">
+        <f>0.75*0.9</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="D8" s="265">
+        <v>1</v>
+      </c>
+      <c r="E8" s="265">
+        <v>0.12</v>
+      </c>
+      <c r="F8" s="267" t="s">
+        <v>198</v>
+      </c>
+      <c r="G8" s="282"/>
+      <c r="H8" s="270"/>
+      <c r="I8" s="271"/>
+      <c r="J8" s="271"/>
+      <c r="N8" s="287" t="s">
+        <v>284</v>
+      </c>
+      <c r="O8" s="288">
+        <v>3633</v>
+      </c>
+      <c r="P8" s="288">
+        <v>165</v>
+      </c>
+      <c r="Q8" s="288">
+        <v>17</v>
+      </c>
+      <c r="R8" s="289">
+        <f t="shared" si="0"/>
+        <v>4.6793283787503444E-3</v>
+      </c>
+      <c r="S8" s="290"/>
+    </row>
+    <row r="9" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="261" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="264">
+        <v>2.4E-2</v>
+      </c>
+      <c r="C9" s="265">
+        <f>0.75*0.9</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="D9" s="265">
+        <v>1</v>
+      </c>
+      <c r="E9" s="265">
+        <v>0.8</v>
+      </c>
+      <c r="F9" s="267" t="s">
+        <v>200</v>
+      </c>
+      <c r="G9" s="285"/>
+      <c r="H9" s="270"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+    </row>
+    <row r="10" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="261" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="264">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="C10" s="265">
+        <f>0.75*0.9</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="D10" s="265">
+        <v>1</v>
+      </c>
+      <c r="E10" s="265">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="275" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="282"/>
+      <c r="H10" s="270"/>
+      <c r="I10" s="271"/>
+      <c r="J10" s="271"/>
+    </row>
+    <row r="11" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="261" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="264">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C11" s="265">
+        <f>0.75*0.9</f>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="D11" s="265">
+        <v>1</v>
+      </c>
+      <c r="E11" s="265">
+        <v>0.8</v>
+      </c>
+      <c r="F11" s="275" t="s">
+        <v>195</v>
+      </c>
+      <c r="G11" s="282" t="s">
+        <v>204</v>
+      </c>
+      <c r="H11" s="270"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="271"/>
+    </row>
+    <row r="12" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="261" t="s">
+        <v>205</v>
+      </c>
+      <c r="B12" s="264">
+        <v>0.01</v>
+      </c>
+      <c r="C12" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D12" s="265">
+        <v>1</v>
+      </c>
+      <c r="E12" s="265">
+        <v>0.25</v>
+      </c>
+      <c r="F12" s="275" t="s">
+        <v>206</v>
+      </c>
+      <c r="G12" s="276"/>
+      <c r="H12" s="270"/>
+      <c r="I12" s="271"/>
+      <c r="J12" s="271"/>
+    </row>
+    <row r="13" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="261" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="264">
+        <f>0.073*0.95</f>
+        <v>6.9349999999999995E-2</v>
+      </c>
+      <c r="C13" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D13" s="265">
+        <v>1</v>
+      </c>
+      <c r="E13" s="265">
+        <v>0.93300000000000005</v>
+      </c>
+      <c r="F13" s="275" t="s">
+        <v>208</v>
+      </c>
+      <c r="G13" s="282"/>
+      <c r="H13" s="271"/>
+      <c r="I13" s="271"/>
+      <c r="J13" s="271"/>
+    </row>
+    <row r="14" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="262" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" s="264">
+        <f>0.43*0.95</f>
+        <v>0.40849999999999997</v>
+      </c>
+      <c r="C14" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D14" s="265">
+        <v>0</v>
+      </c>
+      <c r="E14" s="265">
+        <v>0.77</v>
+      </c>
+      <c r="F14" s="275" t="s">
+        <v>210</v>
+      </c>
+      <c r="G14" s="282"/>
+      <c r="H14" s="271"/>
+      <c r="I14" s="271"/>
+      <c r="J14" s="271"/>
+    </row>
+    <row r="15" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="262" t="s">
+        <v>421</v>
+      </c>
+      <c r="B15" s="264">
+        <f>0.25*0.95</f>
+        <v>0.23749999999999999</v>
+      </c>
+      <c r="C15" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D15" s="265">
+        <v>1</v>
+      </c>
+      <c r="E15" s="265">
+        <v>1</v>
+      </c>
+      <c r="F15" s="291" t="s">
+        <v>211</v>
+      </c>
+      <c r="G15" s="285" t="s">
+        <v>212</v>
+      </c>
+      <c r="H15" s="271"/>
+      <c r="I15" s="271"/>
+      <c r="J15" s="271"/>
+    </row>
+    <row r="16" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="262" t="s">
+        <v>422</v>
+      </c>
+      <c r="B16" s="264">
+        <f>0.8*0.95</f>
+        <v>0.76</v>
+      </c>
+      <c r="C16" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D16" s="265">
+        <v>1</v>
+      </c>
+      <c r="E16" s="265">
+        <v>1</v>
+      </c>
+      <c r="F16" s="275" t="s">
+        <v>211</v>
+      </c>
+      <c r="G16" s="282" t="s">
+        <v>213</v>
+      </c>
+      <c r="H16" s="271"/>
+      <c r="I16" s="271"/>
+      <c r="J16" s="271"/>
+    </row>
+    <row r="17" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="262" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" s="264" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" s="265" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="265" t="s">
+        <v>279</v>
+      </c>
+      <c r="E17" s="265" t="s">
+        <v>279</v>
+      </c>
+      <c r="F17" s="291" t="s">
+        <v>215</v>
+      </c>
+      <c r="G17" s="285" t="s">
+        <v>216</v>
+      </c>
+      <c r="H17" s="271"/>
+      <c r="I17" s="271"/>
+      <c r="J17" s="271"/>
+    </row>
+    <row r="18" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="262" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="264">
+        <v>0.25</v>
+      </c>
+      <c r="C18" s="265">
+        <v>0.9</v>
+      </c>
+      <c r="D18" s="265">
+        <v>1</v>
+      </c>
+      <c r="E18" s="265">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="275" t="s">
+        <v>286</v>
+      </c>
+      <c r="G18" s="282" t="s">
+        <v>287</v>
+      </c>
+      <c r="H18" s="271"/>
+      <c r="I18" s="271"/>
+      <c r="J18" s="271"/>
+    </row>
+    <row r="19" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="262" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="264">
+        <v>0.9</v>
+      </c>
+      <c r="C19" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D19" s="265">
+        <v>1</v>
+      </c>
+      <c r="E19" s="265">
+        <v>1</v>
+      </c>
+      <c r="F19" s="291" t="s">
+        <v>217</v>
+      </c>
+      <c r="G19" s="285"/>
+      <c r="H19" s="271"/>
+      <c r="I19" s="271"/>
+      <c r="J19" s="271"/>
+    </row>
+    <row r="20" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="262" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="264">
+        <v>0.8</v>
+      </c>
+      <c r="C20" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D20" s="265">
+        <v>1</v>
+      </c>
+      <c r="E20" s="265">
+        <v>1</v>
+      </c>
+      <c r="F20" s="275" t="s">
+        <v>217</v>
+      </c>
+      <c r="G20" s="292"/>
+      <c r="H20" s="271"/>
+      <c r="I20" s="271"/>
+      <c r="J20" s="271"/>
+    </row>
+    <row r="21" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="262" t="s">
+        <v>218</v>
+      </c>
+      <c r="B21" s="264">
+        <v>0.9</v>
+      </c>
+      <c r="C21" s="265">
+        <v>0.95</v>
+      </c>
+      <c r="D21" s="265">
+        <v>1</v>
+      </c>
+      <c r="E21" s="265">
+        <v>1</v>
+      </c>
+      <c r="F21" s="293" t="s">
+        <v>219</v>
+      </c>
+      <c r="G21" s="285"/>
+      <c r="H21" s="271"/>
+      <c r="I21" s="271"/>
+      <c r="J21" s="271"/>
+    </row>
+    <row r="22" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="263" t="s">
+        <v>220</v>
+      </c>
+      <c r="B22" s="294">
+        <f>(B15+B16)/2</f>
+        <v>0.49875000000000003</v>
+      </c>
+      <c r="C22" s="295">
+        <v>0.95</v>
+      </c>
+      <c r="D22" s="295">
+        <v>1</v>
+      </c>
+      <c r="E22" s="295">
+        <v>1</v>
+      </c>
+      <c r="F22" s="296" t="s">
+        <v>221</v>
+      </c>
+      <c r="G22" s="282"/>
+      <c r="H22" s="271"/>
+      <c r="I22" s="271"/>
+      <c r="J22" s="271"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="56"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="257"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="57" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="57" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="57"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="57"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="190" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H33"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H34"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H35"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="11" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="11" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="58" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="58" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" s="11" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" s="58"/>
+      <c r="B52" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F25C51DE-CA3A-4353-98EB-35B5D3953A88}">
   <sheetPr>
     <tabColor rgb="FF8DAEC9"/>
@@ -18355,7 +19255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E4808C-D5C9-4E68-8E31-71DF3D032D79}">
   <sheetPr>
     <tabColor rgb="FF8DAEC9"/>
@@ -18889,7 +19789,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4ED266-1B7F-4685-B863-6C081F955C48}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -20235,7 +21135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E74EB30E-EEE8-4876-8F54-0E333A39E59D}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -23244,7 +24144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446FF50C-DD3B-4014-A36F-0B4181A3BDD4}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -23846,7 +24746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BB88AB0-6B52-4513-82BD-95B1EC7DFBCF}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -27027,7 +27927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490E8D32-5A80-49F7-8432-3994CE3361FB}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -28195,7 +29095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D26611B-4DD4-43FD-844F-794A76526AFE}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -28806,7 +29706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83F35568-D1AC-4582-8011-22D28965E9D9}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -30460,7 +31360,76 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC18034E-7D62-4647-B5A2-E87654E924DA}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B1" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B3" s="540" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B4" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>564</v>
+      </c>
+      <c r="B5" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>565</v>
+      </c>
+      <c r="B6" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>566</v>
+      </c>
+      <c r="B7" t="s">
+        <v>573</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{E0AF4259-4C2C-7441-943A-F2FA755D77C5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FE6E631-DD42-45CC-95A7-440C565DB771}">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
@@ -35100,76 +36069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC18034E-7D62-4647-B5A2-E87654E924DA}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>560</v>
-      </c>
-      <c r="B1" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>561</v>
-      </c>
-      <c r="B2" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>562</v>
-      </c>
-      <c r="B3" s="540" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>563</v>
-      </c>
-      <c r="B4" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>564</v>
-      </c>
-      <c r="B5" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>565</v>
-      </c>
-      <c r="B6" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>566</v>
-      </c>
-      <c r="B7" t="s">
-        <v>573</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{E0AF4259-4C2C-7441-943A-F2FA755D77C5}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3F2D30-F001-4447-B54E-6D4085D7F3FB}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
@@ -37536,7 +38436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C590453-861B-4F67-8594-8C10681C81A6}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
@@ -38230,7 +39130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50EF86C-7804-41A8-A94D-47C5C8234528}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
@@ -40120,7 +41020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E850E2F2-80C3-43A7-9571-AD42C095D520}">
   <sheetPr>
     <tabColor rgb="FFB3A2C7"/>
@@ -44597,7 +45497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309FA9A6-1662-4DA8-991D-409ADE0A6D6C}">
   <sheetPr>
     <tabColor rgb="FFB3A2C7"/>
@@ -49074,7 +49974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EF3EA57-229F-4FB5-826B-04B00230472C}">
   <sheetPr>
     <tabColor rgb="FFB3A2C7"/>
@@ -51286,7 +52186,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5EADAE-6ACA-427A-B174-44F738A32F04}">
   <sheetPr>
     <tabColor rgb="FFB3A2C7"/>
@@ -55704,6 +56604,1394 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BB1108-8C3C-F641-97AC-472BA22EDCB3}">
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="69" t="s">
+        <v>395</v>
+      </c>
+      <c r="B1" s="70" t="s">
+        <v>396</v>
+      </c>
+      <c r="C1" s="79" t="s">
+        <v>397</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="79" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" s="79" t="s">
+        <v>88</v>
+      </c>
+      <c r="I1" s="79" t="s">
+        <v>190</v>
+      </c>
+      <c r="J1" s="79" t="s">
+        <v>191</v>
+      </c>
+      <c r="K1" s="79" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="79" t="s">
+        <v>205</v>
+      </c>
+      <c r="M1" s="79" t="s">
+        <v>112</v>
+      </c>
+      <c r="N1" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="O1" s="70" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="D2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="E2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="F2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="G2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="H2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="I2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="J2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="K2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="L2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="M2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="N2" s="352" t="s">
+        <v>454</v>
+      </c>
+      <c r="O2" s="353" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="60" t="s">
+        <v>579</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>577</v>
+      </c>
+      <c r="C3" s="354">
+        <v>64.536322439436617</v>
+      </c>
+      <c r="D3" s="354">
+        <v>0.88389121126760573</v>
+      </c>
+      <c r="E3" s="354">
+        <v>0.15058813239436622</v>
+      </c>
+      <c r="F3" s="354">
+        <v>2.6386156640845067</v>
+      </c>
+      <c r="G3" s="354">
+        <v>134.5922306746472</v>
+      </c>
+      <c r="H3" s="354">
+        <v>1382.6945053443642</v>
+      </c>
+      <c r="I3" s="354">
+        <v>306.15153726760565</v>
+      </c>
+      <c r="J3" s="354">
+        <v>361.47610075352111</v>
+      </c>
+      <c r="K3" s="354">
+        <v>9.0275356338028176E-2</v>
+      </c>
+      <c r="L3" s="354">
+        <v>18.528317862676055</v>
+      </c>
+      <c r="M3" s="354">
+        <v>1.2819120188732387</v>
+      </c>
+      <c r="N3" s="354">
+        <v>13.977078654929578</v>
+      </c>
+      <c r="O3" s="354">
+        <v>1.5863528683098591</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="60"/>
+      <c r="B4" s="61" t="s">
+        <v>578</v>
+      </c>
+      <c r="C4" s="354" cm="1">
+        <f t="array" ref="C4:O4">(25/30)*MI_2018!C4:O4+(5/30)*MI_2018!C5:O5</f>
+        <v>58.195908616314554</v>
+      </c>
+      <c r="D4" s="354">
+        <v>0.88389121126760584</v>
+      </c>
+      <c r="E4" s="354">
+        <v>0.24335573532863852</v>
+      </c>
+      <c r="F4" s="354">
+        <v>2.6610961119718306</v>
+      </c>
+      <c r="G4" s="354">
+        <v>67.379139350234752</v>
+      </c>
+      <c r="H4" s="354">
+        <v>1443.4427281109135</v>
+      </c>
+      <c r="I4" s="354">
+        <v>275.53638354107983</v>
+      </c>
+      <c r="J4" s="354">
+        <v>453.40153391314522</v>
+      </c>
+      <c r="K4" s="354">
+        <v>3.3223656880281691</v>
+      </c>
+      <c r="L4" s="354">
+        <v>15.912623697183097</v>
+      </c>
+      <c r="M4" s="354">
+        <v>1.6021925321361492</v>
+      </c>
+      <c r="N4" s="354">
+        <v>14.553682518779341</v>
+      </c>
+      <c r="O4" s="354">
+        <v>1.9276526771126758</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="60"/>
+      <c r="B5" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="C5" s="354" cm="1">
+        <f t="array" ref="C5:O5">(25/30)*MI_2018!C5:O5+(5/30)*MI_2018!C6:O6</f>
+        <v>53.760244008215963</v>
+      </c>
+      <c r="D5" s="354">
+        <v>0.88389121126760584</v>
+      </c>
+      <c r="E5" s="354">
+        <v>0.22328285563380282</v>
+      </c>
+      <c r="F5" s="354">
+        <v>2.6610961119718306</v>
+      </c>
+      <c r="G5" s="354">
+        <v>28.88863652899061</v>
+      </c>
+      <c r="H5" s="354">
+        <v>1450.3671319436598</v>
+      </c>
+      <c r="I5" s="354">
+        <v>122.46061490845072</v>
+      </c>
+      <c r="J5" s="354">
+        <v>766.16843432394228</v>
+      </c>
+      <c r="K5" s="354">
+        <v>5.6310016387323945</v>
+      </c>
+      <c r="L5" s="354">
+        <v>2.8341528697183032</v>
+      </c>
+      <c r="M5" s="354">
+        <v>1.8005107287323932</v>
+      </c>
+      <c r="N5" s="354">
+        <v>15.194186373239429</v>
+      </c>
+      <c r="O5" s="354">
+        <v>1.9343643245305164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A6" s="60"/>
+      <c r="B6" s="61" t="s">
+        <v>576</v>
+      </c>
+      <c r="C6" s="354">
+        <v>53.747727971830976</v>
+      </c>
+      <c r="D6" s="354">
+        <v>0.88389121126760573</v>
+      </c>
+      <c r="E6" s="354">
+        <v>0.22328285563380282</v>
+      </c>
+      <c r="F6" s="354">
+        <v>2.6610961119718306</v>
+      </c>
+      <c r="G6" s="354">
+        <v>39.052213596478872</v>
+      </c>
+      <c r="H6" s="354">
+        <v>1450.3671319436598</v>
+      </c>
+      <c r="I6" s="354">
+        <v>122.46061490845072</v>
+      </c>
+      <c r="J6" s="354">
+        <v>766.16843432394228</v>
+      </c>
+      <c r="K6" s="354">
+        <v>5.6310016387323945</v>
+      </c>
+      <c r="L6" s="354">
+        <v>2.8341528697183032</v>
+      </c>
+      <c r="M6" s="354">
+        <v>1.8005107287323932</v>
+      </c>
+      <c r="N6" s="354">
+        <v>16.061437992957746</v>
+      </c>
+      <c r="O6" s="354">
+        <v>2.0107568838028169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A7" s="60" t="s">
+        <v>580</v>
+      </c>
+      <c r="B7" s="61" t="s">
+        <v>577</v>
+      </c>
+      <c r="C7" s="354">
+        <v>51.236411047826117</v>
+      </c>
+      <c r="D7" s="354">
+        <v>0.35149360434782612</v>
+      </c>
+      <c r="E7" s="354">
+        <v>0.37854946376811599</v>
+      </c>
+      <c r="F7" s="354">
+        <v>1.4697139710144911</v>
+      </c>
+      <c r="G7" s="354">
+        <v>64.768413495652169</v>
+      </c>
+      <c r="H7" s="354">
+        <v>1144.3172885652173</v>
+      </c>
+      <c r="I7" s="354">
+        <v>162.86606424637682</v>
+      </c>
+      <c r="J7" s="354">
+        <v>297.16810726811593</v>
+      </c>
+      <c r="K7" s="354">
+        <v>0.23043419420289715</v>
+      </c>
+      <c r="L7" s="354">
+        <v>2.7625526971014498</v>
+      </c>
+      <c r="M7" s="354">
+        <v>0.81826993999999875</v>
+      </c>
+      <c r="N7" s="354">
+        <v>13.21922307536232</v>
+      </c>
+      <c r="O7" s="354">
+        <v>1.37412562173913</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A8" s="60"/>
+      <c r="B8" s="61" t="s">
+        <v>578</v>
+      </c>
+      <c r="C8" s="354" cm="1">
+        <f t="array" ref="C8:O8">(25/30)*MI_2018!C8:O8+(5/30)*MI_2018!C9:O9</f>
+        <v>53.458638824154598</v>
+      </c>
+      <c r="D8" s="354">
+        <v>0.35149360434782612</v>
+      </c>
+      <c r="E8" s="354">
+        <v>0.45919950893719808</v>
+      </c>
+      <c r="F8" s="354">
+        <v>1.5202924623188392</v>
+      </c>
+      <c r="G8" s="354">
+        <v>37.434904464734288</v>
+      </c>
+      <c r="H8" s="354">
+        <v>1238.7900545992754</v>
+      </c>
+      <c r="I8" s="354">
+        <v>146.57945782125606</v>
+      </c>
+      <c r="J8" s="354">
+        <v>333.65549843212563</v>
+      </c>
+      <c r="K8" s="354">
+        <v>2.6610480983091773</v>
+      </c>
+      <c r="L8" s="354">
+        <v>2.7625526971014502</v>
+      </c>
+      <c r="M8" s="354">
+        <v>1.2663894665700473</v>
+      </c>
+      <c r="N8" s="354">
+        <v>13.538302693236718</v>
+      </c>
+      <c r="O8" s="354">
+        <v>1.9604835096618356</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="60"/>
+      <c r="B9" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="C9" s="354" cm="1">
+        <f t="array" ref="C9:O9">(25/30)*MI_2018!C9:O9+(5/30)*MI_2018!C10:O10</f>
+        <v>54.822601641787458</v>
+      </c>
+      <c r="D9" s="354">
+        <v>0.35149360434782612</v>
+      </c>
+      <c r="E9" s="354">
+        <v>0.37808582173913052</v>
+      </c>
+      <c r="F9" s="354">
+        <v>1.5202924623188392</v>
+      </c>
+      <c r="G9" s="354">
+        <v>22.392486746859905</v>
+      </c>
+      <c r="H9" s="354">
+        <v>1304.4812254217393</v>
+      </c>
+      <c r="I9" s="354">
+        <v>65.146425695652184</v>
+      </c>
+      <c r="J9" s="354">
+        <v>470.94709410000007</v>
+      </c>
+      <c r="K9" s="354">
+        <v>4.3972008869565204</v>
+      </c>
+      <c r="L9" s="354">
+        <v>2.7625526971014502</v>
+      </c>
+      <c r="M9" s="354">
+        <v>1.8714109544927529</v>
+      </c>
+      <c r="N9" s="354">
+        <v>13.953603213043479</v>
+      </c>
+      <c r="O9" s="354">
+        <v>1.9730191130434778</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="60"/>
+      <c r="B10" s="61" t="s">
+        <v>576</v>
+      </c>
+      <c r="C10" s="354">
+        <v>54.810216828985524</v>
+      </c>
+      <c r="D10" s="354">
+        <v>0.35149360434782612</v>
+      </c>
+      <c r="E10" s="354">
+        <v>0.37808582173913047</v>
+      </c>
+      <c r="F10" s="354">
+        <v>1.5202924623188392</v>
+      </c>
+      <c r="G10" s="354">
+        <v>32.834914582608697</v>
+      </c>
+      <c r="H10" s="354">
+        <v>1304.4812254217391</v>
+      </c>
+      <c r="I10" s="354">
+        <v>65.146425695652184</v>
+      </c>
+      <c r="J10" s="354">
+        <v>470.94709410000002</v>
+      </c>
+      <c r="K10" s="354">
+        <v>4.3972008869565204</v>
+      </c>
+      <c r="L10" s="354">
+        <v>2.7625526971014498</v>
+      </c>
+      <c r="M10" s="354">
+        <v>1.8714109544927526</v>
+      </c>
+      <c r="N10" s="354">
+        <v>14.505308227536233</v>
+      </c>
+      <c r="O10" s="354">
+        <v>2.0533810913043462</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="60" t="s">
+        <v>400</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>577</v>
+      </c>
+      <c r="C11" s="354">
+        <v>46.466515152747249</v>
+      </c>
+      <c r="D11" s="354">
+        <v>0.20715254395604393</v>
+      </c>
+      <c r="E11" s="354">
+        <v>0.11701019340659341</v>
+      </c>
+      <c r="F11" s="354">
+        <v>0.46113914505494502</v>
+      </c>
+      <c r="G11" s="354">
+        <v>42.832492139560415</v>
+      </c>
+      <c r="H11" s="354">
+        <v>1097.8571164296693</v>
+      </c>
+      <c r="I11" s="354">
+        <v>171.36517329670332</v>
+      </c>
+      <c r="J11" s="354">
+        <v>275.99687683296702</v>
+      </c>
+      <c r="K11" s="354">
+        <v>11.018224612087911</v>
+      </c>
+      <c r="L11" s="354">
+        <v>18.81893665164834</v>
+      </c>
+      <c r="M11" s="354">
+        <v>1.4989690769230766</v>
+      </c>
+      <c r="N11" s="354">
+        <v>16.883190557142861</v>
+      </c>
+      <c r="O11" s="354">
+        <v>2.0109270461538458</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="60"/>
+      <c r="B12" s="61" t="s">
+        <v>578</v>
+      </c>
+      <c r="C12" s="354" cm="1">
+        <f t="array" ref="C12:O12">(25/30)*MI_2018!C12:O12+(5/30)*MI_2018!C13:O13</f>
+        <v>46.81397656428571</v>
+      </c>
+      <c r="D12" s="354">
+        <v>0.20721356025641025</v>
+      </c>
+      <c r="E12" s="354">
+        <v>0.35430559652014637</v>
+      </c>
+      <c r="F12" s="354">
+        <v>0.49499219999999994</v>
+      </c>
+      <c r="G12" s="354">
+        <v>21.92045452728938</v>
+      </c>
+      <c r="H12" s="354">
+        <v>1175.5814979241745</v>
+      </c>
+      <c r="I12" s="354">
+        <v>154.22865596703298</v>
+      </c>
+      <c r="J12" s="354">
+        <v>290.47608246043956</v>
+      </c>
+      <c r="K12" s="354">
+        <v>14.681625428754568</v>
+      </c>
+      <c r="L12" s="354">
+        <v>16.48994256923076</v>
+      </c>
+      <c r="M12" s="354">
+        <v>1.7784211177655678</v>
+      </c>
+      <c r="N12" s="354">
+        <v>16.398045225641027</v>
+      </c>
+      <c r="O12" s="354">
+        <v>3.1644151946886443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="60"/>
+      <c r="B13" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="C13" s="354" cm="1">
+        <f t="array" ref="C13:O13">(25/30)*MI_2018!C13:O13+(5/30)*MI_2018!C14:O14</f>
+        <v>48.051661081684976</v>
+      </c>
+      <c r="D13" s="354">
+        <v>0.20751864175824175</v>
+      </c>
+      <c r="E13" s="354">
+        <v>1.471625101098901</v>
+      </c>
+      <c r="F13" s="354">
+        <v>0.49499219999999994</v>
+      </c>
+      <c r="G13" s="354">
+        <v>10.256355973626373</v>
+      </c>
+      <c r="H13" s="354">
+        <v>1208.6320879021953</v>
+      </c>
+      <c r="I13" s="354">
+        <v>68.546069318681319</v>
+      </c>
+      <c r="J13" s="354">
+        <v>363.12482263076919</v>
+      </c>
+      <c r="K13" s="354">
+        <v>17.298340297802184</v>
+      </c>
+      <c r="L13" s="354">
+        <v>4.8449721571428466</v>
+      </c>
+      <c r="M13" s="354">
+        <v>1.81145223956044</v>
+      </c>
+      <c r="N13" s="354">
+        <v>11.606467100732601</v>
+      </c>
+      <c r="O13" s="354">
+        <v>3.1290036838827837</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="60"/>
+      <c r="B14" s="61" t="s">
+        <v>576</v>
+      </c>
+      <c r="C14" s="354">
+        <v>48.035462363736258</v>
+      </c>
+      <c r="D14" s="354">
+        <v>0.20751864175824175</v>
+      </c>
+      <c r="E14" s="354">
+        <v>1.4716251010989008</v>
+      </c>
+      <c r="F14" s="354">
+        <v>0.49499219999999994</v>
+      </c>
+      <c r="G14" s="354">
+        <v>14.176482770329667</v>
+      </c>
+      <c r="H14" s="354">
+        <v>1208.6320879021953</v>
+      </c>
+      <c r="I14" s="354">
+        <v>68.546069318681319</v>
+      </c>
+      <c r="J14" s="354">
+        <v>363.12482263076919</v>
+      </c>
+      <c r="K14" s="354">
+        <v>17.298340297802184</v>
+      </c>
+      <c r="L14" s="354">
+        <v>4.8449721571428466</v>
+      </c>
+      <c r="M14" s="354">
+        <v>1.8114522395604398</v>
+      </c>
+      <c r="N14" s="354">
+        <v>7.846258802197803</v>
+      </c>
+      <c r="O14" s="354">
+        <v>3.1135820868131865</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="60" t="s">
+        <v>581</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>577</v>
+      </c>
+      <c r="C15" s="354">
+        <v>63.247573617468966</v>
+      </c>
+      <c r="D15" s="354">
+        <v>0.28948117869684653</v>
+      </c>
+      <c r="E15" s="354">
+        <v>0.18861372983158145</v>
+      </c>
+      <c r="F15" s="354">
+        <v>0.67728006011227893</v>
+      </c>
+      <c r="G15" s="354">
+        <v>45.805600065892257</v>
+      </c>
+      <c r="H15" s="354">
+        <v>1191.0069261759434</v>
+      </c>
+      <c r="I15" s="354">
+        <v>117.82556523387481</v>
+      </c>
+      <c r="J15" s="354">
+        <v>235.38274034205628</v>
+      </c>
+      <c r="K15" s="354">
+        <v>0.85341120142737692</v>
+      </c>
+      <c r="L15" s="354">
+        <v>5.70253540081222</v>
+      </c>
+      <c r="M15" s="354">
+        <v>1.0111190749378882</v>
+      </c>
+      <c r="N15" s="354">
+        <v>19.453144785744144</v>
+      </c>
+      <c r="O15" s="354">
+        <v>1.9778029835636648</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="60"/>
+      <c r="B16" s="61" t="s">
+        <v>578</v>
+      </c>
+      <c r="C16" s="354" cm="1">
+        <f t="array" ref="C16:O16">(25/30)*MI_2018!C16:O16+(5/30)*MI_2018!C17:O17</f>
+        <v>65.670949423824482</v>
+      </c>
+      <c r="D16" s="354">
+        <v>0.28948117869684653</v>
+      </c>
+      <c r="E16" s="354">
+        <v>1.3195180358566245</v>
+      </c>
+      <c r="F16" s="354">
+        <v>0.67814005609491945</v>
+      </c>
+      <c r="G16" s="354">
+        <v>24.518831205931473</v>
+      </c>
+      <c r="H16" s="354">
+        <v>1336.5840813672546</v>
+      </c>
+      <c r="I16" s="354">
+        <v>101.91568068312031</v>
+      </c>
+      <c r="J16" s="354">
+        <v>225.6525787730217</v>
+      </c>
+      <c r="K16" s="354">
+        <v>4.669764673103793</v>
+      </c>
+      <c r="L16" s="354">
+        <v>5.675151514036858</v>
+      </c>
+      <c r="M16" s="354">
+        <v>1.4505484462300917</v>
+      </c>
+      <c r="N16" s="354">
+        <v>18.950573495849255</v>
+      </c>
+      <c r="O16" s="354">
+        <v>4.6279342452771148</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="60"/>
+      <c r="B17" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="C17" s="354" cm="1">
+        <f t="array" ref="C17:O17">(25/30)*MI_2018!C17:O17+(5/30)*MI_2018!C18:O18</f>
+        <v>78.146748098021206</v>
+      </c>
+      <c r="D17" s="354">
+        <v>0.28948117869684653</v>
+      </c>
+      <c r="E17" s="354">
+        <v>6.9569849296643529</v>
+      </c>
+      <c r="F17" s="354">
+        <v>0.6824400360081222</v>
+      </c>
+      <c r="G17" s="354">
+        <v>9.8615794611920649</v>
+      </c>
+      <c r="H17" s="354">
+        <v>1591.1174348635261</v>
+      </c>
+      <c r="I17" s="354">
+        <v>22.366257929347825</v>
+      </c>
+      <c r="J17" s="354">
+        <v>177.65653974034873</v>
+      </c>
+      <c r="K17" s="354">
+        <v>7.3957314389751536</v>
+      </c>
+      <c r="L17" s="354">
+        <v>5.5382320801600464</v>
+      </c>
+      <c r="M17" s="354">
+        <v>2.0721546994003806</v>
+      </c>
+      <c r="N17" s="354">
+        <v>12.964776412330774</v>
+      </c>
+      <c r="O17" s="354">
+        <v>4.7904670616979228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18" s="60"/>
+      <c r="B18" s="61" t="s">
+        <v>576</v>
+      </c>
+      <c r="C18" s="354">
+        <v>78.130278452675611</v>
+      </c>
+      <c r="D18" s="354">
+        <v>0.28948117869684653</v>
+      </c>
+      <c r="E18" s="354">
+        <v>6.9569849296643529</v>
+      </c>
+      <c r="F18" s="354">
+        <v>0.6824400360081222</v>
+      </c>
+      <c r="G18" s="354">
+        <v>9.8615794611920649</v>
+      </c>
+      <c r="H18" s="354">
+        <v>1591.1174348635261</v>
+      </c>
+      <c r="I18" s="354">
+        <v>22.366257929347825</v>
+      </c>
+      <c r="J18" s="354">
+        <v>177.65653974034873</v>
+      </c>
+      <c r="K18" s="354">
+        <v>7.3957314389751536</v>
+      </c>
+      <c r="L18" s="354">
+        <v>5.5382320801600464</v>
+      </c>
+      <c r="M18" s="354">
+        <v>2.0721546994003806</v>
+      </c>
+      <c r="N18" s="354">
+        <v>7.9364854664894775</v>
+      </c>
+      <c r="O18" s="354">
+        <v>4.725455303754778</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19" s="60" t="s">
+        <v>402</v>
+      </c>
+      <c r="B19" s="61" t="s">
+        <v>577</v>
+      </c>
+      <c r="C19" s="354">
+        <v>73.961058518555888</v>
+      </c>
+      <c r="D19" s="354">
+        <v>0.33846705315336822</v>
+      </c>
+      <c r="E19" s="354">
+        <v>9.831651352723364E-2</v>
+      </c>
+      <c r="F19" s="354">
+        <v>0.77648306174271364</v>
+      </c>
+      <c r="G19" s="354">
+        <v>49.785507205022697</v>
+      </c>
+      <c r="H19" s="354">
+        <v>920.82528349550876</v>
+      </c>
+      <c r="I19" s="354">
+        <v>86.539151842570462</v>
+      </c>
+      <c r="J19" s="354">
+        <v>304.4730898909699</v>
+      </c>
+      <c r="K19" s="354">
+        <v>1.6636304101230293</v>
+      </c>
+      <c r="L19" s="354">
+        <v>5.2831196812470083</v>
+      </c>
+      <c r="M19" s="354">
+        <v>1.3213306606987565</v>
+      </c>
+      <c r="N19" s="354">
+        <v>19.886053018352843</v>
+      </c>
+      <c r="O19" s="354">
+        <v>2.1094656848136637</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20" s="60"/>
+      <c r="B20" s="61" t="s">
+        <v>578</v>
+      </c>
+      <c r="C20" s="354" cm="1">
+        <f t="array" ref="C20:O20">(25/30)*MI_2018!C20:O20+(5/30)*MI_2018!C21:O21</f>
+        <v>76.434133711324449</v>
+      </c>
+      <c r="D20" s="354">
+        <v>0.33846705315336822</v>
+      </c>
+      <c r="E20" s="354">
+        <v>1.2623580732660447</v>
+      </c>
+      <c r="F20" s="354">
+        <v>0.77797776986303535</v>
+      </c>
+      <c r="G20" s="354">
+        <v>21.658335410913359</v>
+      </c>
+      <c r="H20" s="354">
+        <v>1032.3069697481424</v>
+      </c>
+      <c r="I20" s="354">
+        <v>78.580250793627556</v>
+      </c>
+      <c r="J20" s="354">
+        <v>302.45387997401855</v>
+      </c>
+      <c r="K20" s="354">
+        <v>5.8367979462016244</v>
+      </c>
+      <c r="L20" s="354">
+        <v>5.2831196812470083</v>
+      </c>
+      <c r="M20" s="354">
+        <v>1.6917920370634243</v>
+      </c>
+      <c r="N20" s="354">
+        <v>19.975870281084767</v>
+      </c>
+      <c r="O20" s="354">
+        <v>2.044294966726389</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="60"/>
+      <c r="B21" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="C21" s="354" cm="1">
+        <f t="array" ref="C21:O21">(25/30)*MI_2018!C21:O21+(5/30)*MI_2018!C22:O22</f>
+        <v>88.38035420300308</v>
+      </c>
+      <c r="D21" s="354">
+        <v>0.33846705315336822</v>
+      </c>
+      <c r="E21" s="354">
+        <v>7.1459152274904394</v>
+      </c>
+      <c r="F21" s="354">
+        <v>0.78545131046464389</v>
+      </c>
+      <c r="G21" s="354">
+        <v>3.15910185140946</v>
+      </c>
+      <c r="H21" s="354">
+        <v>1301.4636763662436</v>
+      </c>
+      <c r="I21" s="354">
+        <v>38.785745548913042</v>
+      </c>
+      <c r="J21" s="354">
+        <v>292.35783038926184</v>
+      </c>
+      <c r="K21" s="354">
+        <v>8.8176319009316764</v>
+      </c>
+      <c r="L21" s="354">
+        <v>5.2831196812470083</v>
+      </c>
+      <c r="M21" s="354">
+        <v>1.7773783645090762</v>
+      </c>
+      <c r="N21" s="354">
+        <v>14.902098572928606</v>
+      </c>
+      <c r="O21" s="354">
+        <v>2.1939223311544422</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="60"/>
+      <c r="B22" s="61" t="s">
+        <v>576</v>
+      </c>
+      <c r="C22" s="354">
+        <v>88.364030628762535</v>
+      </c>
+      <c r="D22" s="354">
+        <v>0.33846705315336822</v>
+      </c>
+      <c r="E22" s="354">
+        <v>7.1459152274904394</v>
+      </c>
+      <c r="F22" s="354">
+        <v>0.78545131046464389</v>
+      </c>
+      <c r="G22" s="354">
+        <v>3.1591018514094595</v>
+      </c>
+      <c r="H22" s="354">
+        <v>1301.4636763662436</v>
+      </c>
+      <c r="I22" s="354">
+        <v>38.785745548913042</v>
+      </c>
+      <c r="J22" s="354">
+        <v>292.35783038926184</v>
+      </c>
+      <c r="K22" s="354">
+        <v>8.8176319009316764</v>
+      </c>
+      <c r="L22" s="354">
+        <v>5.2831196812470083</v>
+      </c>
+      <c r="M22" s="354">
+        <v>1.7773783645090762</v>
+      </c>
+      <c r="N22" s="354">
+        <v>11.48879000888078</v>
+      </c>
+      <c r="O22" s="354">
+        <v>2.1294871696786899</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="60" t="s">
+        <v>403</v>
+      </c>
+      <c r="B23" s="61" t="s">
+        <v>577</v>
+      </c>
+      <c r="C23" s="354">
+        <v>92.106593835443078</v>
+      </c>
+      <c r="D23" s="354">
+        <v>0.24424686412042113</v>
+      </c>
+      <c r="E23" s="354">
+        <v>0.12761050637201135</v>
+      </c>
+      <c r="F23" s="354">
+        <v>0.18228375881772313</v>
+      </c>
+      <c r="G23" s="354">
+        <v>77.515275772012501</v>
+      </c>
+      <c r="H23" s="354">
+        <v>816.66961909891938</v>
+      </c>
+      <c r="I23" s="354">
+        <v>10.018767650658033</v>
+      </c>
+      <c r="J23" s="354">
+        <v>39.883713630077871</v>
+      </c>
+      <c r="K23" s="354">
+        <v>7.9699212064048591E-2</v>
+      </c>
+      <c r="L23" s="354">
+        <v>0.19992887625027414</v>
+      </c>
+      <c r="M23" s="354">
+        <v>1.8818543859799244</v>
+      </c>
+      <c r="N23" s="354">
+        <v>12.388943001568325</v>
+      </c>
+      <c r="O23" s="354">
+        <v>0.39648400197510358</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="60"/>
+      <c r="B24" s="61" t="s">
+        <v>578</v>
+      </c>
+      <c r="C24" s="354" cm="1">
+        <f t="array" ref="C24:O24">(25/30)*MI_2018!C24:O24+(5/30)*MI_2018!C25:O25</f>
+        <v>84.96842454855522</v>
+      </c>
+      <c r="D24" s="354">
+        <v>0.24424686412042113</v>
+      </c>
+      <c r="E24" s="354">
+        <v>0.192789733146706</v>
+      </c>
+      <c r="F24" s="354">
+        <v>0.18228679015792934</v>
+      </c>
+      <c r="G24" s="354">
+        <v>32.731022077334394</v>
+      </c>
+      <c r="H24" s="354">
+        <v>816.741545244387</v>
+      </c>
+      <c r="I24" s="354">
+        <v>9.0196439414071001</v>
+      </c>
+      <c r="J24" s="354">
+        <v>41.714067175427729</v>
+      </c>
+      <c r="K24" s="354">
+        <v>0.59011593928127459</v>
+      </c>
+      <c r="L24" s="354">
+        <v>0.19992887625027417</v>
+      </c>
+      <c r="M24" s="354">
+        <v>2.1149229967434331</v>
+      </c>
+      <c r="N24" s="354">
+        <v>16.396464731459751</v>
+      </c>
+      <c r="O24" s="354">
+        <v>0.37791461881461524</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="60"/>
+      <c r="B25" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="C25" s="354" cm="1">
+        <f t="array" ref="C25:O25">(25/30)*MI_2018!C25:O25+(5/30)*MI_2018!C26:O26</f>
+        <v>80.172770817231651</v>
+      </c>
+      <c r="D25" s="354">
+        <v>0.24424686412042113</v>
+      </c>
+      <c r="E25" s="354">
+        <v>0.44696519143342783</v>
+      </c>
+      <c r="F25" s="354">
+        <v>0.18230194685896026</v>
+      </c>
+      <c r="G25" s="354">
+        <v>0.80942497554397819</v>
+      </c>
+      <c r="H25" s="354">
+        <v>819.25319799053455</v>
+      </c>
+      <c r="I25" s="354">
+        <v>4.0240253951524405</v>
+      </c>
+      <c r="J25" s="354">
+        <v>50.865834902177014</v>
+      </c>
+      <c r="K25" s="354">
+        <v>0.95469931585325674</v>
+      </c>
+      <c r="L25" s="354">
+        <v>0.19992887625027417</v>
+      </c>
+      <c r="M25" s="354">
+        <v>2.1069968816917077</v>
+      </c>
+      <c r="N25" s="354">
+        <v>22.017761082981465</v>
+      </c>
+      <c r="O25" s="354">
+        <v>0.31221953719456014</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="60"/>
+      <c r="B26" s="61" t="s">
+        <v>576</v>
+      </c>
+      <c r="C26" s="354">
+        <v>80.171314617411696</v>
+      </c>
+      <c r="D26" s="354">
+        <v>0.24424686412042113</v>
+      </c>
+      <c r="E26" s="354">
+        <v>0.44696519143342783</v>
+      </c>
+      <c r="F26" s="354">
+        <v>0.18230194685896023</v>
+      </c>
+      <c r="G26" s="354">
+        <v>0.80942497554397819</v>
+      </c>
+      <c r="H26" s="354">
+        <v>819.25319799053455</v>
+      </c>
+      <c r="I26" s="354">
+        <v>4.0240253951524405</v>
+      </c>
+      <c r="J26" s="354">
+        <v>50.865834902177014</v>
+      </c>
+      <c r="K26" s="354">
+        <v>0.95469931585325674</v>
+      </c>
+      <c r="L26" s="354">
+        <v>0.19992887625027414</v>
+      </c>
+      <c r="M26" s="354">
+        <v>2.1069968816917077</v>
+      </c>
+      <c r="N26" s="354">
+        <v>31.16315817618996</v>
+      </c>
+      <c r="O26" s="354">
+        <v>0.30647138029337567</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="60" t="s">
+        <v>404</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>577</v>
+      </c>
+      <c r="C27" s="354">
+        <v>76.371623519910798</v>
+      </c>
+      <c r="D27" s="354">
+        <v>0.32171694557062552</v>
+      </c>
+      <c r="E27" s="354">
+        <v>0.10965742456622675</v>
+      </c>
+      <c r="F27" s="354">
+        <v>0.7536273425403226</v>
+      </c>
+      <c r="G27" s="354">
+        <v>56.616516909457467</v>
+      </c>
+      <c r="H27" s="354">
+        <v>1244.4585829134276</v>
+      </c>
+      <c r="I27" s="354">
+        <v>141.5417439017595</v>
+      </c>
+      <c r="J27" s="354">
+        <v>228.63562795606668</v>
+      </c>
+      <c r="K27" s="354">
+        <v>0.81073296499266856</v>
+      </c>
+      <c r="L27" s="354">
+        <v>12.265440836119248</v>
+      </c>
+      <c r="M27" s="354">
+        <v>1.1337825718015635</v>
+      </c>
+      <c r="N27" s="354">
+        <v>17.710760958339442</v>
+      </c>
+      <c r="O27" s="354">
+        <v>2.0345576971713086</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="60"/>
+      <c r="B28" s="61" t="s">
+        <v>578</v>
+      </c>
+      <c r="C28" s="354" cm="1">
+        <f t="array" ref="C28:O28">(25/30)*MI_2018!C28:O28+(5/30)*MI_2018!C29:O29</f>
+        <v>76.069464293830436</v>
+      </c>
+      <c r="D28" s="354">
+        <v>0.3218891277930514</v>
+      </c>
+      <c r="E28" s="354">
+        <v>1.111510622939063</v>
+      </c>
+      <c r="F28" s="354">
+        <v>0.76766214890131168</v>
+      </c>
+      <c r="G28" s="354">
+        <v>27.060947509448319</v>
+      </c>
+      <c r="H28" s="354">
+        <v>1329.1327123600431</v>
+      </c>
+      <c r="I28" s="354">
+        <v>127.38756951139416</v>
+      </c>
+      <c r="J28" s="354">
+        <v>245.01502366370656</v>
+      </c>
+      <c r="K28" s="354">
+        <v>2.8722794099421636</v>
+      </c>
+      <c r="L28" s="354">
+        <v>11.197325601270764</v>
+      </c>
+      <c r="M28" s="354">
+        <v>1.3916081188924316</v>
+      </c>
+      <c r="N28" s="354">
+        <v>17.422629966882536</v>
+      </c>
+      <c r="O28" s="354">
+        <v>3.2508215694719356</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="60"/>
+      <c r="B29" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="C29" s="354" cm="1">
+        <f t="array" ref="C29:O29">(25/30)*MI_2018!C29:O29+(5/30)*MI_2018!C30:O30</f>
+        <v>77.42047600632128</v>
+      </c>
+      <c r="D29" s="354">
+        <v>0.32275003890518078</v>
+      </c>
+      <c r="E29" s="354">
+        <v>6.141978851362385</v>
+      </c>
+      <c r="F29" s="354">
+        <v>0.77157026455889544</v>
+      </c>
+      <c r="G29" s="354">
+        <v>6.3171164099767845</v>
+      </c>
+      <c r="H29" s="354">
+        <v>1378.8947615237157</v>
+      </c>
+      <c r="I29" s="354">
+        <v>56.616697559567442</v>
+      </c>
+      <c r="J29" s="354">
+        <v>326.91200220190592</v>
+      </c>
+      <c r="K29" s="354">
+        <v>4.1439175575533556</v>
+      </c>
+      <c r="L29" s="354">
+        <v>5.8567494270283404</v>
+      </c>
+      <c r="M29" s="354">
+        <v>1.6670462345764896</v>
+      </c>
+      <c r="N29" s="354">
+        <v>12.921935676399071</v>
+      </c>
+      <c r="O29" s="354">
+        <v>3.1764030885579571</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="66"/>
+      <c r="B30" s="61" t="s">
+        <v>576</v>
+      </c>
+      <c r="C30" s="354">
+        <v>77.420896134762941</v>
+      </c>
+      <c r="D30" s="354">
+        <v>0.32275003890518073</v>
+      </c>
+      <c r="E30" s="354">
+        <v>6.141978851362385</v>
+      </c>
+      <c r="F30" s="354">
+        <v>0.77157026455889544</v>
+      </c>
+      <c r="G30" s="354">
+        <v>7.4154301751283</v>
+      </c>
+      <c r="H30" s="354">
+        <v>1378.8947615237157</v>
+      </c>
+      <c r="I30" s="354">
+        <v>56.616697559567442</v>
+      </c>
+      <c r="J30" s="354">
+        <v>326.91200220190592</v>
+      </c>
+      <c r="K30" s="354">
+        <v>4.4154543561644672</v>
+      </c>
+      <c r="L30" s="354">
+        <v>5.8567494270283404</v>
+      </c>
+      <c r="M30" s="354">
+        <v>1.6713908232861669</v>
+      </c>
+      <c r="N30" s="354">
+        <v>8.9234626837304489</v>
+      </c>
+      <c r="O30" s="354">
+        <v>3.1264975707233607</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4C7019E-6F89-401C-A664-2A986FB7D8B2}">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -57090,7 +59378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEB4001A-C439-4868-92F5-62B3E92F47CB}">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -59602,7 +61890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA5E678-A17A-478A-82CD-142549B25FC8}">
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
@@ -59755,7 +62043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48422E00-43F9-4D2D-8655-A1669D3CE29C}">
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
@@ -59906,7 +62194,7 @@
       <c r="L4" s="9"/>
     </row>
     <row r="5" spans="1:18" s="46" customFormat="1" ht="29" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="603" t="s">
+      <c r="A5" s="21" t="s">
         <v>89</v>
       </c>
       <c r="B5" s="14" t="s">
@@ -60120,7 +62408,7 @@
       <c r="P10" s="79"/>
       <c r="R10" s="79"/>
     </row>
-    <row r="11" spans="1:18" ht="70" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="56" x14ac:dyDescent="0.2">
       <c r="A11" s="555"/>
       <c r="B11" s="2" t="s">
         <v>133</v>
@@ -60165,7 +62453,7 @@
       <c r="P11" s="57"/>
       <c r="R11" s="57"/>
     </row>
-    <row r="12" spans="1:18" ht="70" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="56" x14ac:dyDescent="0.2">
       <c r="A12" s="555"/>
       <c r="B12" s="2" t="s">
         <v>136</v>
@@ -60477,7 +62765,7 @@
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="1:12" ht="29" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="602" t="s">
+      <c r="A21" s="49" t="s">
         <v>178</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -60540,7 +62828,7 @@
       <c r="K22" s="14"/>
       <c r="L22" s="9"/>
     </row>
-    <row r="23" spans="1:12" ht="71" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="57" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="49" t="s">
         <v>179</v>
       </c>
@@ -60798,7 +63086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBA639B-D6A5-4911-A7CE-57686AB21F28}">
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
@@ -61838,7 +64126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544C846A-19A6-4ECA-A102-C192191B1470}">
   <sheetPr>
     <tabColor theme="7" tint="0.39997558519241921"/>
@@ -62397,866 +64685,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DF2012-C526-49AC-BBB5-413BFD42E12E}">
-  <sheetPr>
-    <tabColor theme="3" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:S52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="20.1640625" customWidth="1"/>
-    <col min="2" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="54.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="1"/>
-    <col min="9" max="9" width="44.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.83203125" customWidth="1"/>
-    <col min="14" max="14" width="18.33203125" customWidth="1"/>
-    <col min="15" max="15" width="19.6640625" customWidth="1"/>
-    <col min="16" max="16" width="23.5" customWidth="1"/>
-    <col min="17" max="17" width="25.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="258" t="s">
-        <v>188</v>
-      </c>
-      <c r="B1" s="394" t="s">
-        <v>498</v>
-      </c>
-      <c r="C1" s="89" t="s">
-        <v>500</v>
-      </c>
-      <c r="D1" s="89" t="s">
-        <v>497</v>
-      </c>
-      <c r="E1" s="89" t="s">
-        <v>367</v>
-      </c>
-      <c r="F1" s="259" t="s">
-        <v>189</v>
-      </c>
-      <c r="G1" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="567"/>
-      <c r="I1" s="567"/>
-      <c r="J1" s="567"/>
-      <c r="K1" s="567"/>
-      <c r="L1" s="567"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="188"/>
-    </row>
-    <row r="2" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="260" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="264">
-        <v>0.28499999999999998</v>
-      </c>
-      <c r="C2" s="265">
-        <f>0.53*0.85</f>
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="D2" s="266">
-        <v>1</v>
-      </c>
-      <c r="E2" s="266">
-        <v>0.37</v>
-      </c>
-      <c r="F2" s="267" t="s">
-        <v>429</v>
-      </c>
-      <c r="G2" s="268" t="s">
-        <v>366</v>
-      </c>
-      <c r="H2" s="270"/>
-      <c r="I2" s="271"/>
-      <c r="J2" s="271"/>
-      <c r="N2" s="272"/>
-      <c r="O2" s="273" t="s">
-        <v>280</v>
-      </c>
-      <c r="P2" s="273" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q2" s="273" t="s">
-        <v>282</v>
-      </c>
-      <c r="R2" s="273" t="s">
-        <v>283</v>
-      </c>
-      <c r="S2" s="274" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="261" t="s">
-        <v>190</v>
-      </c>
-      <c r="B3" s="264">
-        <v>0.01</v>
-      </c>
-      <c r="C3" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D3" s="266">
-        <v>1</v>
-      </c>
-      <c r="E3" s="266">
-        <v>0.25</v>
-      </c>
-      <c r="F3" s="275" t="s">
-        <v>430</v>
-      </c>
-      <c r="G3" s="276"/>
-      <c r="H3" s="270"/>
-      <c r="I3" s="271"/>
-      <c r="J3" s="271"/>
-      <c r="N3" s="277" t="s">
-        <v>197</v>
-      </c>
-      <c r="O3" s="271">
-        <v>11642</v>
-      </c>
-      <c r="P3" s="271">
-        <v>530</v>
-      </c>
-      <c r="Q3" s="271">
-        <v>53</v>
-      </c>
-      <c r="R3" s="278">
-        <f>Q3/O3</f>
-        <v>4.5524823913416935E-3</v>
-      </c>
-      <c r="S3" s="279">
-        <f>SUM(Q3:Q8)/SUM(O3:O8)</f>
-        <v>1.4528631597813424E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="261" t="s">
-        <v>191</v>
-      </c>
-      <c r="B4" s="264">
-        <v>0.28499999999999998</v>
-      </c>
-      <c r="C4" s="265">
-        <f>0.53*0.85</f>
-        <v>0.45050000000000001</v>
-      </c>
-      <c r="D4" s="266">
-        <v>1</v>
-      </c>
-      <c r="E4" s="266">
-        <v>0.37</v>
-      </c>
-      <c r="F4" s="275" t="s">
-        <v>192</v>
-      </c>
-      <c r="G4" s="276"/>
-      <c r="H4" s="270"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="N4" s="280" t="s">
-        <v>237</v>
-      </c>
-      <c r="O4" s="271">
-        <v>42941</v>
-      </c>
-      <c r="P4" s="271">
-        <v>15029</v>
-      </c>
-      <c r="Q4" s="271">
-        <v>751</v>
-      </c>
-      <c r="R4" s="278">
-        <f t="shared" ref="R4:R8" si="0">Q4/O4</f>
-        <v>1.7489112968957405E-2</v>
-      </c>
-      <c r="S4" s="281"/>
-    </row>
-    <row r="5" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="260" t="s">
-        <v>193</v>
-      </c>
-      <c r="B5" s="264">
-        <v>0.9</v>
-      </c>
-      <c r="C5" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D5" s="265">
-        <v>1</v>
-      </c>
-      <c r="E5" s="265">
-        <v>1</v>
-      </c>
-      <c r="F5" s="267" t="s">
-        <v>433</v>
-      </c>
-      <c r="G5" s="282"/>
-      <c r="H5" s="270"/>
-      <c r="I5" s="271"/>
-      <c r="J5" s="271"/>
-      <c r="N5" s="283" t="s">
-        <v>196</v>
-      </c>
-      <c r="O5" s="271">
-        <v>7800</v>
-      </c>
-      <c r="P5" s="271">
-        <v>355</v>
-      </c>
-      <c r="Q5" s="271">
-        <v>0</v>
-      </c>
-      <c r="R5" s="278">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S5" s="281"/>
-    </row>
-    <row r="6" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="262" t="s">
-        <v>194</v>
-      </c>
-      <c r="B6" s="264">
-        <v>0</v>
-      </c>
-      <c r="C6" s="265">
-        <v>0</v>
-      </c>
-      <c r="D6" s="265">
-        <v>1</v>
-      </c>
-      <c r="E6" s="265">
-        <v>0</v>
-      </c>
-      <c r="F6" s="267" t="s">
-        <v>195</v>
-      </c>
-      <c r="G6" s="282"/>
-      <c r="H6" s="270"/>
-      <c r="I6" s="271"/>
-      <c r="J6" s="271"/>
-      <c r="N6" s="284" t="s">
-        <v>194</v>
-      </c>
-      <c r="O6" s="271">
-        <v>3185</v>
-      </c>
-      <c r="P6" s="271">
-        <v>145</v>
-      </c>
-      <c r="Q6" s="271">
-        <v>0</v>
-      </c>
-      <c r="R6" s="278">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S6" s="281"/>
-    </row>
-    <row r="7" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="262" t="s">
-        <v>196</v>
-      </c>
-      <c r="B7" s="264">
-        <v>0</v>
-      </c>
-      <c r="C7" s="265">
-        <v>0</v>
-      </c>
-      <c r="D7" s="265">
-        <v>1</v>
-      </c>
-      <c r="E7" s="265">
-        <v>0</v>
-      </c>
-      <c r="F7" s="267" t="s">
-        <v>195</v>
-      </c>
-      <c r="G7" s="285"/>
-      <c r="H7" s="270"/>
-      <c r="I7" s="271"/>
-      <c r="J7" s="271"/>
-      <c r="N7" s="286" t="s">
-        <v>199</v>
-      </c>
-      <c r="O7" s="271">
-        <v>20071</v>
-      </c>
-      <c r="P7" s="271">
-        <v>7025</v>
-      </c>
-      <c r="Q7" s="271">
-        <v>476</v>
-      </c>
-      <c r="R7" s="278">
-        <f t="shared" si="0"/>
-        <v>2.371580887848139E-2</v>
-      </c>
-      <c r="S7" s="281"/>
-    </row>
-    <row r="8" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="262" t="s">
-        <v>197</v>
-      </c>
-      <c r="B8" s="264">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C8" s="265">
-        <f>0.75*0.9</f>
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="D8" s="265">
-        <v>1</v>
-      </c>
-      <c r="E8" s="265">
-        <v>0.12</v>
-      </c>
-      <c r="F8" s="267" t="s">
-        <v>198</v>
-      </c>
-      <c r="G8" s="282"/>
-      <c r="H8" s="270"/>
-      <c r="I8" s="271"/>
-      <c r="J8" s="271"/>
-      <c r="N8" s="287" t="s">
-        <v>284</v>
-      </c>
-      <c r="O8" s="288">
-        <v>3633</v>
-      </c>
-      <c r="P8" s="288">
-        <v>165</v>
-      </c>
-      <c r="Q8" s="288">
-        <v>17</v>
-      </c>
-      <c r="R8" s="289">
-        <f t="shared" si="0"/>
-        <v>4.6793283787503444E-3</v>
-      </c>
-      <c r="S8" s="290"/>
-    </row>
-    <row r="9" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="261" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="264">
-        <v>2.4E-2</v>
-      </c>
-      <c r="C9" s="265">
-        <f>0.75*0.9</f>
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="D9" s="265">
-        <v>1</v>
-      </c>
-      <c r="E9" s="265">
-        <v>0.8</v>
-      </c>
-      <c r="F9" s="267" t="s">
-        <v>200</v>
-      </c>
-      <c r="G9" s="285"/>
-      <c r="H9" s="270"/>
-      <c r="I9" s="271"/>
-      <c r="J9" s="271"/>
-    </row>
-    <row r="10" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="261" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="264">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="C10" s="265">
-        <f>0.75*0.9</f>
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="D10" s="265">
-        <v>1</v>
-      </c>
-      <c r="E10" s="265">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="275" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="282"/>
-      <c r="H10" s="270"/>
-      <c r="I10" s="271"/>
-      <c r="J10" s="271"/>
-    </row>
-    <row r="11" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="261" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="264">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="C11" s="265">
-        <f>0.75*0.9</f>
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="D11" s="265">
-        <v>1</v>
-      </c>
-      <c r="E11" s="265">
-        <v>0.8</v>
-      </c>
-      <c r="F11" s="275" t="s">
-        <v>195</v>
-      </c>
-      <c r="G11" s="282" t="s">
-        <v>204</v>
-      </c>
-      <c r="H11" s="270"/>
-      <c r="I11" s="271"/>
-      <c r="J11" s="271"/>
-    </row>
-    <row r="12" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="261" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="264">
-        <v>0.01</v>
-      </c>
-      <c r="C12" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D12" s="265">
-        <v>1</v>
-      </c>
-      <c r="E12" s="265">
-        <v>0.25</v>
-      </c>
-      <c r="F12" s="275" t="s">
-        <v>206</v>
-      </c>
-      <c r="G12" s="276"/>
-      <c r="H12" s="270"/>
-      <c r="I12" s="271"/>
-      <c r="J12" s="271"/>
-    </row>
-    <row r="13" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="261" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="264">
-        <f>0.073*0.95</f>
-        <v>6.9349999999999995E-2</v>
-      </c>
-      <c r="C13" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D13" s="265">
-        <v>1</v>
-      </c>
-      <c r="E13" s="265">
-        <v>0.93300000000000005</v>
-      </c>
-      <c r="F13" s="275" t="s">
-        <v>208</v>
-      </c>
-      <c r="G13" s="282"/>
-      <c r="H13" s="271"/>
-      <c r="I13" s="271"/>
-      <c r="J13" s="271"/>
-    </row>
-    <row r="14" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="262" t="s">
-        <v>209</v>
-      </c>
-      <c r="B14" s="264">
-        <f>0.43*0.95</f>
-        <v>0.40849999999999997</v>
-      </c>
-      <c r="C14" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D14" s="265">
-        <v>0</v>
-      </c>
-      <c r="E14" s="265">
-        <v>0.77</v>
-      </c>
-      <c r="F14" s="275" t="s">
-        <v>210</v>
-      </c>
-      <c r="G14" s="282"/>
-      <c r="H14" s="271"/>
-      <c r="I14" s="271"/>
-      <c r="J14" s="271"/>
-    </row>
-    <row r="15" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="262" t="s">
-        <v>421</v>
-      </c>
-      <c r="B15" s="264">
-        <f>0.25*0.95</f>
-        <v>0.23749999999999999</v>
-      </c>
-      <c r="C15" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D15" s="265">
-        <v>1</v>
-      </c>
-      <c r="E15" s="265">
-        <v>1</v>
-      </c>
-      <c r="F15" s="291" t="s">
-        <v>211</v>
-      </c>
-      <c r="G15" s="285" t="s">
-        <v>212</v>
-      </c>
-      <c r="H15" s="271"/>
-      <c r="I15" s="271"/>
-      <c r="J15" s="271"/>
-    </row>
-    <row r="16" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="262" t="s">
-        <v>422</v>
-      </c>
-      <c r="B16" s="264">
-        <f>0.8*0.95</f>
-        <v>0.76</v>
-      </c>
-      <c r="C16" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D16" s="265">
-        <v>1</v>
-      </c>
-      <c r="E16" s="265">
-        <v>1</v>
-      </c>
-      <c r="F16" s="275" t="s">
-        <v>211</v>
-      </c>
-      <c r="G16" s="282" t="s">
-        <v>213</v>
-      </c>
-      <c r="H16" s="271"/>
-      <c r="I16" s="271"/>
-      <c r="J16" s="271"/>
-    </row>
-    <row r="17" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="262" t="s">
-        <v>214</v>
-      </c>
-      <c r="B17" s="264" t="s">
-        <v>279</v>
-      </c>
-      <c r="C17" s="265" t="s">
-        <v>279</v>
-      </c>
-      <c r="D17" s="265" t="s">
-        <v>279</v>
-      </c>
-      <c r="E17" s="265" t="s">
-        <v>279</v>
-      </c>
-      <c r="F17" s="291" t="s">
-        <v>215</v>
-      </c>
-      <c r="G17" s="285" t="s">
-        <v>216</v>
-      </c>
-      <c r="H17" s="271"/>
-      <c r="I17" s="271"/>
-      <c r="J17" s="271"/>
-    </row>
-    <row r="18" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="262" t="s">
-        <v>180</v>
-      </c>
-      <c r="B18" s="264">
-        <v>0.25</v>
-      </c>
-      <c r="C18" s="265">
-        <v>0.9</v>
-      </c>
-      <c r="D18" s="265">
-        <v>1</v>
-      </c>
-      <c r="E18" s="265">
-        <v>0.5</v>
-      </c>
-      <c r="F18" s="275" t="s">
-        <v>286</v>
-      </c>
-      <c r="G18" s="282" t="s">
-        <v>287</v>
-      </c>
-      <c r="H18" s="271"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="271"/>
-    </row>
-    <row r="19" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="262" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="264">
-        <v>0.9</v>
-      </c>
-      <c r="C19" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D19" s="265">
-        <v>1</v>
-      </c>
-      <c r="E19" s="265">
-        <v>1</v>
-      </c>
-      <c r="F19" s="291" t="s">
-        <v>217</v>
-      </c>
-      <c r="G19" s="285"/>
-      <c r="H19" s="271"/>
-      <c r="I19" s="271"/>
-      <c r="J19" s="271"/>
-    </row>
-    <row r="20" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="262" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="264">
-        <v>0.8</v>
-      </c>
-      <c r="C20" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D20" s="265">
-        <v>1</v>
-      </c>
-      <c r="E20" s="265">
-        <v>1</v>
-      </c>
-      <c r="F20" s="275" t="s">
-        <v>217</v>
-      </c>
-      <c r="G20" s="292"/>
-      <c r="H20" s="271"/>
-      <c r="I20" s="271"/>
-      <c r="J20" s="271"/>
-    </row>
-    <row r="21" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="262" t="s">
-        <v>218</v>
-      </c>
-      <c r="B21" s="264">
-        <v>0.9</v>
-      </c>
-      <c r="C21" s="265">
-        <v>0.95</v>
-      </c>
-      <c r="D21" s="265">
-        <v>1</v>
-      </c>
-      <c r="E21" s="265">
-        <v>1</v>
-      </c>
-      <c r="F21" s="293" t="s">
-        <v>219</v>
-      </c>
-      <c r="G21" s="285"/>
-      <c r="H21" s="271"/>
-      <c r="I21" s="271"/>
-      <c r="J21" s="271"/>
-    </row>
-    <row r="22" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="263" t="s">
-        <v>220</v>
-      </c>
-      <c r="B22" s="294">
-        <f>(B15+B16)/2</f>
-        <v>0.49875000000000003</v>
-      </c>
-      <c r="C22" s="295">
-        <v>0.95</v>
-      </c>
-      <c r="D22" s="295">
-        <v>1</v>
-      </c>
-      <c r="E22" s="295">
-        <v>1</v>
-      </c>
-      <c r="F22" s="296" t="s">
-        <v>221</v>
-      </c>
-      <c r="G22" s="282"/>
-      <c r="H22" s="271"/>
-      <c r="I22" s="271"/>
-      <c r="J22" s="271"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="56"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="257"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="57" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="57" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="57"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A28" s="57"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A29" s="190" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="H30"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H31"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="H32"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H33"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="H34"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="H35"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" s="58" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="58" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="11" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="58"/>
-      <c r="B52" s="1"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="H1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
-</worksheet>
 </file>
--- a/data_input/MI_Buildings_Oorschot2023.xlsx
+++ b/data_input/MI_Buildings_Oorschot2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mira/Documents/IE/REAL UTOPIAN HOUSING/Post-GrowthHousingScenarios/Code/housing-footprints/data_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C266CA18-0F84-B645-8ED8-B1CC5C1D3A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A3E593-33EB-4540-B39B-01C96BD18665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10660" yWindow="500" windowWidth="14940" windowHeight="15500" tabRatio="902" activeTab="2" xr2:uid="{501A363E-84AB-4328-B285-EDCE5CC29F1E}"/>
   </bookViews>
@@ -2139,9 +2139,6 @@
     <t>1975-2005</t>
   </si>
   <si>
-    <t>2006-2018</t>
-  </si>
-  <si>
     <t>pre 1945</t>
   </si>
   <si>
@@ -2155,6 +2152,9 @@
   </si>
   <si>
     <t>multiple fam (meergezins)</t>
+  </si>
+  <si>
+    <t>2006-2022</t>
   </si>
 </sst>
 </file>
@@ -4432,16 +4432,10 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4450,7 +4444,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21200,11 +21200,11 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="571">
+      <c r="A2" s="575">
         <v>2018</v>
       </c>
-      <c r="B2" s="572"/>
-      <c r="C2" s="572"/>
+      <c r="B2" s="576"/>
+      <c r="C2" s="576"/>
       <c r="D2" s="174">
         <v>1849352203.1438973</v>
       </c>
@@ -21248,10 +21248,10 @@
       <c r="R2" s="175"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="573" t="s">
+      <c r="A3" s="577" t="s">
         <v>235</v>
       </c>
-      <c r="B3" s="575" t="s">
+      <c r="B3" s="573" t="s">
         <v>271</v>
       </c>
       <c r="C3" s="37" t="s">
@@ -21304,8 +21304,8 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="574"/>
-      <c r="B4" s="576"/>
+      <c r="A4" s="571"/>
+      <c r="B4" s="574"/>
       <c r="C4" s="11" t="s">
         <v>272</v>
       </c>
@@ -21356,8 +21356,8 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="574"/>
-      <c r="B5" s="576"/>
+      <c r="A5" s="571"/>
+      <c r="B5" s="574"/>
       <c r="C5" s="11" t="s">
         <v>273</v>
       </c>
@@ -21408,8 +21408,8 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="574"/>
-      <c r="B6" s="576" t="s">
+      <c r="A6" s="571"/>
+      <c r="B6" s="574" t="s">
         <v>274</v>
       </c>
       <c r="C6" s="11" t="s">
@@ -21462,8 +21462,8 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="574"/>
-      <c r="B7" s="576"/>
+      <c r="A7" s="571"/>
+      <c r="B7" s="574"/>
       <c r="C7" s="11" t="s">
         <v>272</v>
       </c>
@@ -21514,8 +21514,8 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="574"/>
-      <c r="B8" s="576"/>
+      <c r="A8" s="571"/>
+      <c r="B8" s="574"/>
       <c r="C8" s="11" t="s">
         <v>273</v>
       </c>
@@ -21566,10 +21566,10 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="574" t="s">
+      <c r="A9" s="571" t="s">
         <v>275</v>
       </c>
-      <c r="B9" s="575" t="s">
+      <c r="B9" s="573" t="s">
         <v>271</v>
       </c>
       <c r="C9" s="37" t="s">
@@ -21622,8 +21622,8 @@
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="574"/>
-      <c r="B10" s="576"/>
+      <c r="A10" s="571"/>
+      <c r="B10" s="574"/>
       <c r="C10" s="11" t="s">
         <v>272</v>
       </c>
@@ -21674,8 +21674,8 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="574"/>
-      <c r="B11" s="576"/>
+      <c r="A11" s="571"/>
+      <c r="B11" s="574"/>
       <c r="C11" s="11" t="s">
         <v>273</v>
       </c>
@@ -21726,8 +21726,8 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="574"/>
-      <c r="B12" s="576" t="s">
+      <c r="A12" s="571"/>
+      <c r="B12" s="574" t="s">
         <v>274</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -21780,8 +21780,8 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="574"/>
-      <c r="B13" s="576"/>
+      <c r="A13" s="571"/>
+      <c r="B13" s="574"/>
       <c r="C13" s="11" t="s">
         <v>272</v>
       </c>
@@ -21832,8 +21832,8 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="574"/>
-      <c r="B14" s="576"/>
+      <c r="A14" s="571"/>
+      <c r="B14" s="574"/>
       <c r="C14" s="11" t="s">
         <v>273</v>
       </c>
@@ -21884,10 +21884,10 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="574" t="s">
+      <c r="A15" s="571" t="s">
         <v>276</v>
       </c>
-      <c r="B15" s="575" t="s">
+      <c r="B15" s="573" t="s">
         <v>271</v>
       </c>
       <c r="C15" s="37" t="s">
@@ -21940,8 +21940,8 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="574"/>
-      <c r="B16" s="576"/>
+      <c r="A16" s="571"/>
+      <c r="B16" s="574"/>
       <c r="C16" s="11" t="s">
         <v>272</v>
       </c>
@@ -21992,8 +21992,8 @@
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="574"/>
-      <c r="B17" s="576"/>
+      <c r="A17" s="571"/>
+      <c r="B17" s="574"/>
       <c r="C17" s="11" t="s">
         <v>273</v>
       </c>
@@ -22044,8 +22044,8 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="574"/>
-      <c r="B18" s="576" t="s">
+      <c r="A18" s="571"/>
+      <c r="B18" s="574" t="s">
         <v>274</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -22098,8 +22098,8 @@
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="574"/>
-      <c r="B19" s="576"/>
+      <c r="A19" s="571"/>
+      <c r="B19" s="574"/>
       <c r="C19" s="11" t="s">
         <v>272</v>
       </c>
@@ -22150,8 +22150,8 @@
       </c>
     </row>
     <row r="20" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="574"/>
-      <c r="B20" s="576"/>
+      <c r="A20" s="571"/>
+      <c r="B20" s="574"/>
       <c r="C20" s="11" t="s">
         <v>273</v>
       </c>
@@ -22202,10 +22202,10 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="574" t="s">
+      <c r="A21" s="571" t="s">
         <v>236</v>
       </c>
-      <c r="B21" s="575" t="s">
+      <c r="B21" s="573" t="s">
         <v>271</v>
       </c>
       <c r="C21" s="37" t="s">
@@ -22258,8 +22258,8 @@
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="574"/>
-      <c r="B22" s="576"/>
+      <c r="A22" s="571"/>
+      <c r="B22" s="574"/>
       <c r="C22" s="11" t="s">
         <v>272</v>
       </c>
@@ -22310,8 +22310,8 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="574"/>
-      <c r="B23" s="576"/>
+      <c r="A23" s="571"/>
+      <c r="B23" s="574"/>
       <c r="C23" s="11" t="s">
         <v>273</v>
       </c>
@@ -22362,8 +22362,8 @@
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="574"/>
-      <c r="B24" s="576" t="s">
+      <c r="A24" s="571"/>
+      <c r="B24" s="574" t="s">
         <v>274</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -22416,8 +22416,8 @@
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="574"/>
-      <c r="B25" s="576"/>
+      <c r="A25" s="571"/>
+      <c r="B25" s="574"/>
       <c r="C25" s="11" t="s">
         <v>272</v>
       </c>
@@ -22468,8 +22468,8 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="574"/>
-      <c r="B26" s="576"/>
+      <c r="A26" s="571"/>
+      <c r="B26" s="574"/>
       <c r="C26" s="11" t="s">
         <v>273</v>
       </c>
@@ -22520,10 +22520,10 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="574" t="s">
+      <c r="A27" s="571" t="s">
         <v>277</v>
       </c>
-      <c r="B27" s="575" t="s">
+      <c r="B27" s="573" t="s">
         <v>271</v>
       </c>
       <c r="C27" s="37" t="s">
@@ -22576,8 +22576,8 @@
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" s="574"/>
-      <c r="B28" s="576"/>
+      <c r="A28" s="571"/>
+      <c r="B28" s="574"/>
       <c r="C28" s="11" t="s">
         <v>272</v>
       </c>
@@ -22628,8 +22628,8 @@
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A29" s="574"/>
-      <c r="B29" s="576"/>
+      <c r="A29" s="571"/>
+      <c r="B29" s="574"/>
       <c r="C29" s="11" t="s">
         <v>273</v>
       </c>
@@ -22680,8 +22680,8 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="574"/>
-      <c r="B30" s="576" t="s">
+      <c r="A30" s="571"/>
+      <c r="B30" s="574" t="s">
         <v>274</v>
       </c>
       <c r="C30" s="11" t="s">
@@ -22734,8 +22734,8 @@
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="574"/>
-      <c r="B31" s="576"/>
+      <c r="A31" s="571"/>
+      <c r="B31" s="574"/>
       <c r="C31" s="11" t="s">
         <v>272</v>
       </c>
@@ -22786,8 +22786,8 @@
       </c>
     </row>
     <row r="32" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="574"/>
-      <c r="B32" s="576"/>
+      <c r="A32" s="571"/>
+      <c r="B32" s="574"/>
       <c r="C32" s="11" t="s">
         <v>273</v>
       </c>
@@ -22838,10 +22838,10 @@
       </c>
     </row>
     <row r="33" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="574" t="s">
+      <c r="A33" s="571" t="s">
         <v>278</v>
       </c>
-      <c r="B33" s="575" t="s">
+      <c r="B33" s="573" t="s">
         <v>271</v>
       </c>
       <c r="C33" s="37" t="s">
@@ -22894,8 +22894,8 @@
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A34" s="574"/>
-      <c r="B34" s="576"/>
+      <c r="A34" s="571"/>
+      <c r="B34" s="574"/>
       <c r="C34" s="11" t="s">
         <v>272</v>
       </c>
@@ -22946,8 +22946,8 @@
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A35" s="574"/>
-      <c r="B35" s="576"/>
+      <c r="A35" s="571"/>
+      <c r="B35" s="574"/>
       <c r="C35" s="11" t="s">
         <v>273</v>
       </c>
@@ -22998,8 +22998,8 @@
       </c>
     </row>
     <row r="36" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="574"/>
-      <c r="B36" s="576" t="s">
+      <c r="A36" s="571"/>
+      <c r="B36" s="574" t="s">
         <v>274</v>
       </c>
       <c r="C36" s="11" t="s">
@@ -23052,8 +23052,8 @@
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A37" s="574"/>
-      <c r="B37" s="576"/>
+      <c r="A37" s="571"/>
+      <c r="B37" s="574"/>
       <c r="C37" s="11" t="s">
         <v>272</v>
       </c>
@@ -23104,8 +23104,8 @@
       </c>
     </row>
     <row r="38" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="574"/>
-      <c r="B38" s="576"/>
+      <c r="A38" s="571"/>
+      <c r="B38" s="574"/>
       <c r="C38" s="11" t="s">
         <v>273</v>
       </c>
@@ -23156,10 +23156,10 @@
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A39" s="574" t="s">
+      <c r="A39" s="571" t="s">
         <v>241</v>
       </c>
-      <c r="B39" s="575" t="s">
+      <c r="B39" s="573" t="s">
         <v>271</v>
       </c>
       <c r="C39" s="37" t="s">
@@ -23212,8 +23212,8 @@
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A40" s="574"/>
-      <c r="B40" s="576"/>
+      <c r="A40" s="571"/>
+      <c r="B40" s="574"/>
       <c r="C40" s="11" t="s">
         <v>272</v>
       </c>
@@ -23264,8 +23264,8 @@
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A41" s="574"/>
-      <c r="B41" s="576"/>
+      <c r="A41" s="571"/>
+      <c r="B41" s="574"/>
       <c r="C41" s="11" t="s">
         <v>273</v>
       </c>
@@ -23316,8 +23316,8 @@
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A42" s="574"/>
-      <c r="B42" s="576" t="s">
+      <c r="A42" s="571"/>
+      <c r="B42" s="574" t="s">
         <v>274</v>
       </c>
       <c r="C42" s="11" t="s">
@@ -23370,8 +23370,8 @@
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A43" s="574"/>
-      <c r="B43" s="576"/>
+      <c r="A43" s="571"/>
+      <c r="B43" s="574"/>
       <c r="C43" s="11" t="s">
         <v>272</v>
       </c>
@@ -23422,8 +23422,8 @@
       </c>
     </row>
     <row r="44" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="574"/>
-      <c r="B44" s="576"/>
+      <c r="A44" s="571"/>
+      <c r="B44" s="574"/>
       <c r="C44" s="11" t="s">
         <v>273</v>
       </c>
@@ -23474,10 +23474,10 @@
       </c>
     </row>
     <row r="45" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="574" t="s">
+      <c r="A45" s="571" t="s">
         <v>393</v>
       </c>
-      <c r="B45" s="575" t="s">
+      <c r="B45" s="573" t="s">
         <v>271</v>
       </c>
       <c r="C45" s="37" t="s">
@@ -23530,8 +23530,8 @@
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A46" s="574"/>
-      <c r="B46" s="576"/>
+      <c r="A46" s="571"/>
+      <c r="B46" s="574"/>
       <c r="C46" s="11" t="s">
         <v>272</v>
       </c>
@@ -23582,8 +23582,8 @@
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A47" s="574"/>
-      <c r="B47" s="576"/>
+      <c r="A47" s="571"/>
+      <c r="B47" s="574"/>
       <c r="C47" s="11" t="s">
         <v>273</v>
       </c>
@@ -23634,8 +23634,8 @@
       </c>
     </row>
     <row r="48" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="574"/>
-      <c r="B48" s="576" t="s">
+      <c r="A48" s="571"/>
+      <c r="B48" s="574" t="s">
         <v>274</v>
       </c>
       <c r="C48" s="11" t="s">
@@ -23688,8 +23688,8 @@
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A49" s="574"/>
-      <c r="B49" s="576"/>
+      <c r="A49" s="571"/>
+      <c r="B49" s="574"/>
       <c r="C49" s="11" t="s">
         <v>272</v>
       </c>
@@ -23740,8 +23740,8 @@
       </c>
     </row>
     <row r="50" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="574"/>
-      <c r="B50" s="576"/>
+      <c r="A50" s="571"/>
+      <c r="B50" s="574"/>
       <c r="C50" s="11" t="s">
         <v>273</v>
       </c>
@@ -23792,10 +23792,10 @@
       </c>
     </row>
     <row r="51" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="574" t="s">
+      <c r="A51" s="571" t="s">
         <v>394</v>
       </c>
-      <c r="B51" s="575" t="s">
+      <c r="B51" s="573" t="s">
         <v>271</v>
       </c>
       <c r="C51" s="37" t="s">
@@ -23848,8 +23848,8 @@
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A52" s="574"/>
-      <c r="B52" s="576"/>
+      <c r="A52" s="571"/>
+      <c r="B52" s="574"/>
       <c r="C52" s="11" t="s">
         <v>272</v>
       </c>
@@ -23900,8 +23900,8 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A53" s="574"/>
-      <c r="B53" s="576"/>
+      <c r="A53" s="571"/>
+      <c r="B53" s="574"/>
       <c r="C53" s="11" t="s">
         <v>273</v>
       </c>
@@ -23952,8 +23952,8 @@
       </c>
     </row>
     <row r="54" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="574"/>
-      <c r="B54" s="576" t="s">
+      <c r="A54" s="571"/>
+      <c r="B54" s="574" t="s">
         <v>274</v>
       </c>
       <c r="C54" s="11" t="s">
@@ -24006,8 +24006,8 @@
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A55" s="574"/>
-      <c r="B55" s="576"/>
+      <c r="A55" s="571"/>
+      <c r="B55" s="574"/>
       <c r="C55" s="11" t="s">
         <v>272</v>
       </c>
@@ -24058,8 +24058,8 @@
       </c>
     </row>
     <row r="56" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="577"/>
-      <c r="B56" s="576"/>
+      <c r="A56" s="572"/>
+      <c r="B56" s="574"/>
       <c r="C56" s="11" t="s">
         <v>273</v>
       </c>
@@ -24111,6 +24111,25 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B36:B38"/>
     <mergeCell ref="A51:A56"/>
     <mergeCell ref="B51:B53"/>
     <mergeCell ref="B54:B56"/>
@@ -24120,25 +24139,6 @@
     <mergeCell ref="A45:A50"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B48:B50"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="B12:B14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -56700,10 +56700,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="60" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B3" s="61" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C3" s="354">
         <v>64.536322439436617</v>
@@ -56748,7 +56748,7 @@
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="60"/>
       <c r="B4" s="61" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C4" s="354" cm="1">
         <f t="array" ref="C4:O4">(25/30)*MI_2018!C4:O4+(5/30)*MI_2018!C5:O5</f>
@@ -56840,7 +56840,7 @@
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="60"/>
       <c r="B6" s="61" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C6" s="354">
         <v>53.747727971830976</v>
@@ -56884,10 +56884,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="60" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B7" s="61" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C7" s="354">
         <v>51.236411047826117</v>
@@ -56932,7 +56932,7 @@
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="60"/>
       <c r="B8" s="61" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C8" s="354" cm="1">
         <f t="array" ref="C8:O8">(25/30)*MI_2018!C8:O8+(5/30)*MI_2018!C9:O9</f>
@@ -57024,7 +57024,7 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="60"/>
       <c r="B10" s="61" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C10" s="354">
         <v>54.810216828985524</v>
@@ -57071,7 +57071,7 @@
         <v>400</v>
       </c>
       <c r="B11" s="61" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C11" s="354">
         <v>46.466515152747249</v>
@@ -57116,7 +57116,7 @@
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="60"/>
       <c r="B12" s="61" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C12" s="354" cm="1">
         <f t="array" ref="C12:O12">(25/30)*MI_2018!C12:O12+(5/30)*MI_2018!C13:O13</f>
@@ -57208,7 +57208,7 @@
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="60"/>
       <c r="B14" s="61" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C14" s="354">
         <v>48.035462363736258</v>
@@ -57252,10 +57252,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="60" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B15" s="61" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C15" s="354">
         <v>63.247573617468966</v>
@@ -57300,7 +57300,7 @@
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="60"/>
       <c r="B16" s="61" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C16" s="354" cm="1">
         <f t="array" ref="C16:O16">(25/30)*MI_2018!C16:O16+(5/30)*MI_2018!C17:O17</f>
@@ -57392,7 +57392,7 @@
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="60"/>
       <c r="B18" s="61" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C18" s="354">
         <v>78.130278452675611</v>
@@ -57439,7 +57439,7 @@
         <v>402</v>
       </c>
       <c r="B19" s="61" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C19" s="354">
         <v>73.961058518555888</v>
@@ -57484,7 +57484,7 @@
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="60"/>
       <c r="B20" s="61" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C20" s="354" cm="1">
         <f t="array" ref="C20:O20">(25/30)*MI_2018!C20:O20+(5/30)*MI_2018!C21:O21</f>
@@ -57576,7 +57576,7 @@
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="60"/>
       <c r="B22" s="61" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C22" s="354">
         <v>88.364030628762535</v>
@@ -57623,7 +57623,7 @@
         <v>403</v>
       </c>
       <c r="B23" s="61" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C23" s="354">
         <v>92.106593835443078</v>
@@ -57668,7 +57668,7 @@
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="60"/>
       <c r="B24" s="61" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C24" s="354" cm="1">
         <f t="array" ref="C24:O24">(25/30)*MI_2018!C24:O24+(5/30)*MI_2018!C25:O25</f>
@@ -57760,7 +57760,7 @@
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="60"/>
       <c r="B26" s="61" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C26" s="354">
         <v>80.171314617411696</v>
@@ -57807,7 +57807,7 @@
         <v>404</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C27" s="354">
         <v>76.371623519910798</v>
@@ -57852,7 +57852,7 @@
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="60"/>
       <c r="B28" s="61" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C28" s="354" cm="1">
         <f t="array" ref="C28:O28">(25/30)*MI_2018!C28:O28+(5/30)*MI_2018!C29:O29</f>
@@ -57944,7 +57944,7 @@
     <row r="30" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="66"/>
       <c r="B30" s="61" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C30" s="354">
         <v>77.420896134762941</v>

--- a/data_input/MI_Buildings_Oorschot2023.xlsx
+++ b/data_input/MI_Buildings_Oorschot2023.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mira/Documents/IE/REAL UTOPIAN HOUSING/Post-GrowthHousingScenarios/Code/housing-footprints/data_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A3E593-33EB-4540-B39B-01C96BD18665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEB5C0C-B410-C448-ADA9-0E521AE16BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10660" yWindow="500" windowWidth="14940" windowHeight="15500" tabRatio="902" activeTab="2" xr2:uid="{501A363E-84AB-4328-B285-EDCE5CC29F1E}"/>
+    <workbookView xWindow="10660" yWindow="500" windowWidth="14940" windowHeight="15500" tabRatio="902" firstSheet="8" activeTab="5" xr2:uid="{501A363E-84AB-4328-B285-EDCE5CC29F1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="24" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2878" uniqueCount="581">
   <si>
     <t>aluminium, wrought alloy | treatment of aluminium scrap, post-consumer, prepared for recycling, at remelter | RER | kilogram | cutoff38 - Janneke</t>
   </si>
@@ -2145,16 +2145,13 @@
     <t>1946-1974</t>
   </si>
   <si>
-    <t>detached (vrijstaand)</t>
+    <t>2006-2022</t>
   </si>
   <si>
-    <t>row house (tussenwoning)</t>
+    <t>detached</t>
   </si>
   <si>
-    <t>multiple fam (meergezins)</t>
-  </si>
-  <si>
-    <t>2006-2022</t>
+    <t>multifamily</t>
   </si>
 </sst>
 </file>
@@ -4432,10 +4429,16 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4444,13 +4447,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21200,11 +21197,11 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="575">
+      <c r="A2" s="571">
         <v>2018</v>
       </c>
-      <c r="B2" s="576"/>
-      <c r="C2" s="576"/>
+      <c r="B2" s="572"/>
+      <c r="C2" s="572"/>
       <c r="D2" s="174">
         <v>1849352203.1438973</v>
       </c>
@@ -21248,10 +21245,10 @@
       <c r="R2" s="175"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="577" t="s">
+      <c r="A3" s="573" t="s">
         <v>235</v>
       </c>
-      <c r="B3" s="573" t="s">
+      <c r="B3" s="575" t="s">
         <v>271</v>
       </c>
       <c r="C3" s="37" t="s">
@@ -21304,8 +21301,8 @@
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="571"/>
-      <c r="B4" s="574"/>
+      <c r="A4" s="574"/>
+      <c r="B4" s="576"/>
       <c r="C4" s="11" t="s">
         <v>272</v>
       </c>
@@ -21356,8 +21353,8 @@
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="571"/>
-      <c r="B5" s="574"/>
+      <c r="A5" s="574"/>
+      <c r="B5" s="576"/>
       <c r="C5" s="11" t="s">
         <v>273</v>
       </c>
@@ -21408,8 +21405,8 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="571"/>
-      <c r="B6" s="574" t="s">
+      <c r="A6" s="574"/>
+      <c r="B6" s="576" t="s">
         <v>274</v>
       </c>
       <c r="C6" s="11" t="s">
@@ -21462,8 +21459,8 @@
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="571"/>
-      <c r="B7" s="574"/>
+      <c r="A7" s="574"/>
+      <c r="B7" s="576"/>
       <c r="C7" s="11" t="s">
         <v>272</v>
       </c>
@@ -21514,8 +21511,8 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="571"/>
-      <c r="B8" s="574"/>
+      <c r="A8" s="574"/>
+      <c r="B8" s="576"/>
       <c r="C8" s="11" t="s">
         <v>273</v>
       </c>
@@ -21566,10 +21563,10 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="571" t="s">
+      <c r="A9" s="574" t="s">
         <v>275</v>
       </c>
-      <c r="B9" s="573" t="s">
+      <c r="B9" s="575" t="s">
         <v>271</v>
       </c>
       <c r="C9" s="37" t="s">
@@ -21622,8 +21619,8 @@
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="571"/>
-      <c r="B10" s="574"/>
+      <c r="A10" s="574"/>
+      <c r="B10" s="576"/>
       <c r="C10" s="11" t="s">
         <v>272</v>
       </c>
@@ -21674,8 +21671,8 @@
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="571"/>
-      <c r="B11" s="574"/>
+      <c r="A11" s="574"/>
+      <c r="B11" s="576"/>
       <c r="C11" s="11" t="s">
         <v>273</v>
       </c>
@@ -21726,8 +21723,8 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="571"/>
-      <c r="B12" s="574" t="s">
+      <c r="A12" s="574"/>
+      <c r="B12" s="576" t="s">
         <v>274</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -21780,8 +21777,8 @@
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="571"/>
-      <c r="B13" s="574"/>
+      <c r="A13" s="574"/>
+      <c r="B13" s="576"/>
       <c r="C13" s="11" t="s">
         <v>272</v>
       </c>
@@ -21832,8 +21829,8 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="571"/>
-      <c r="B14" s="574"/>
+      <c r="A14" s="574"/>
+      <c r="B14" s="576"/>
       <c r="C14" s="11" t="s">
         <v>273</v>
       </c>
@@ -21884,10 +21881,10 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="571" t="s">
+      <c r="A15" s="574" t="s">
         <v>276</v>
       </c>
-      <c r="B15" s="573" t="s">
+      <c r="B15" s="575" t="s">
         <v>271</v>
       </c>
       <c r="C15" s="37" t="s">
@@ -21940,8 +21937,8 @@
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="571"/>
-      <c r="B16" s="574"/>
+      <c r="A16" s="574"/>
+      <c r="B16" s="576"/>
       <c r="C16" s="11" t="s">
         <v>272</v>
       </c>
@@ -21992,8 +21989,8 @@
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="571"/>
-      <c r="B17" s="574"/>
+      <c r="A17" s="574"/>
+      <c r="B17" s="576"/>
       <c r="C17" s="11" t="s">
         <v>273</v>
       </c>
@@ -22044,8 +22041,8 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="571"/>
-      <c r="B18" s="574" t="s">
+      <c r="A18" s="574"/>
+      <c r="B18" s="576" t="s">
         <v>274</v>
       </c>
       <c r="C18" s="11" t="s">
@@ -22098,8 +22095,8 @@
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="571"/>
-      <c r="B19" s="574"/>
+      <c r="A19" s="574"/>
+      <c r="B19" s="576"/>
       <c r="C19" s="11" t="s">
         <v>272</v>
       </c>
@@ -22150,8 +22147,8 @@
       </c>
     </row>
     <row r="20" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="571"/>
-      <c r="B20" s="574"/>
+      <c r="A20" s="574"/>
+      <c r="B20" s="576"/>
       <c r="C20" s="11" t="s">
         <v>273</v>
       </c>
@@ -22202,10 +22199,10 @@
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="571" t="s">
+      <c r="A21" s="574" t="s">
         <v>236</v>
       </c>
-      <c r="B21" s="573" t="s">
+      <c r="B21" s="575" t="s">
         <v>271</v>
       </c>
       <c r="C21" s="37" t="s">
@@ -22258,8 +22255,8 @@
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="571"/>
-      <c r="B22" s="574"/>
+      <c r="A22" s="574"/>
+      <c r="B22" s="576"/>
       <c r="C22" s="11" t="s">
         <v>272</v>
       </c>
@@ -22310,8 +22307,8 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="571"/>
-      <c r="B23" s="574"/>
+      <c r="A23" s="574"/>
+      <c r="B23" s="576"/>
       <c r="C23" s="11" t="s">
         <v>273</v>
       </c>
@@ -22362,8 +22359,8 @@
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="571"/>
-      <c r="B24" s="574" t="s">
+      <c r="A24" s="574"/>
+      <c r="B24" s="576" t="s">
         <v>274</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -22416,8 +22413,8 @@
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="571"/>
-      <c r="B25" s="574"/>
+      <c r="A25" s="574"/>
+      <c r="B25" s="576"/>
       <c r="C25" s="11" t="s">
         <v>272</v>
       </c>
@@ -22468,8 +22465,8 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="571"/>
-      <c r="B26" s="574"/>
+      <c r="A26" s="574"/>
+      <c r="B26" s="576"/>
       <c r="C26" s="11" t="s">
         <v>273</v>
       </c>
@@ -22520,10 +22517,10 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="571" t="s">
+      <c r="A27" s="574" t="s">
         <v>277</v>
       </c>
-      <c r="B27" s="573" t="s">
+      <c r="B27" s="575" t="s">
         <v>271</v>
       </c>
       <c r="C27" s="37" t="s">
@@ -22576,8 +22573,8 @@
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A28" s="571"/>
-      <c r="B28" s="574"/>
+      <c r="A28" s="574"/>
+      <c r="B28" s="576"/>
       <c r="C28" s="11" t="s">
         <v>272</v>
       </c>
@@ -22628,8 +22625,8 @@
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A29" s="571"/>
-      <c r="B29" s="574"/>
+      <c r="A29" s="574"/>
+      <c r="B29" s="576"/>
       <c r="C29" s="11" t="s">
         <v>273</v>
       </c>
@@ -22680,8 +22677,8 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="571"/>
-      <c r="B30" s="574" t="s">
+      <c r="A30" s="574"/>
+      <c r="B30" s="576" t="s">
         <v>274</v>
       </c>
       <c r="C30" s="11" t="s">
@@ -22734,8 +22731,8 @@
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="571"/>
-      <c r="B31" s="574"/>
+      <c r="A31" s="574"/>
+      <c r="B31" s="576"/>
       <c r="C31" s="11" t="s">
         <v>272</v>
       </c>
@@ -22786,8 +22783,8 @@
       </c>
     </row>
     <row r="32" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="571"/>
-      <c r="B32" s="574"/>
+      <c r="A32" s="574"/>
+      <c r="B32" s="576"/>
       <c r="C32" s="11" t="s">
         <v>273</v>
       </c>
@@ -22838,10 +22835,10 @@
       </c>
     </row>
     <row r="33" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="571" t="s">
+      <c r="A33" s="574" t="s">
         <v>278</v>
       </c>
-      <c r="B33" s="573" t="s">
+      <c r="B33" s="575" t="s">
         <v>271</v>
       </c>
       <c r="C33" s="37" t="s">
@@ -22894,8 +22891,8 @@
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A34" s="571"/>
-      <c r="B34" s="574"/>
+      <c r="A34" s="574"/>
+      <c r="B34" s="576"/>
       <c r="C34" s="11" t="s">
         <v>272</v>
       </c>
@@ -22946,8 +22943,8 @@
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A35" s="571"/>
-      <c r="B35" s="574"/>
+      <c r="A35" s="574"/>
+      <c r="B35" s="576"/>
       <c r="C35" s="11" t="s">
         <v>273</v>
       </c>
@@ -22998,8 +22995,8 @@
       </c>
     </row>
     <row r="36" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="571"/>
-      <c r="B36" s="574" t="s">
+      <c r="A36" s="574"/>
+      <c r="B36" s="576" t="s">
         <v>274</v>
       </c>
       <c r="C36" s="11" t="s">
@@ -23052,8 +23049,8 @@
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A37" s="571"/>
-      <c r="B37" s="574"/>
+      <c r="A37" s="574"/>
+      <c r="B37" s="576"/>
       <c r="C37" s="11" t="s">
         <v>272</v>
       </c>
@@ -23104,8 +23101,8 @@
       </c>
     </row>
     <row r="38" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="571"/>
-      <c r="B38" s="574"/>
+      <c r="A38" s="574"/>
+      <c r="B38" s="576"/>
       <c r="C38" s="11" t="s">
         <v>273</v>
       </c>
@@ -23156,10 +23153,10 @@
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A39" s="571" t="s">
+      <c r="A39" s="574" t="s">
         <v>241</v>
       </c>
-      <c r="B39" s="573" t="s">
+      <c r="B39" s="575" t="s">
         <v>271</v>
       </c>
       <c r="C39" s="37" t="s">
@@ -23212,8 +23209,8 @@
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A40" s="571"/>
-      <c r="B40" s="574"/>
+      <c r="A40" s="574"/>
+      <c r="B40" s="576"/>
       <c r="C40" s="11" t="s">
         <v>272</v>
       </c>
@@ -23264,8 +23261,8 @@
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A41" s="571"/>
-      <c r="B41" s="574"/>
+      <c r="A41" s="574"/>
+      <c r="B41" s="576"/>
       <c r="C41" s="11" t="s">
         <v>273</v>
       </c>
@@ -23316,8 +23313,8 @@
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A42" s="571"/>
-      <c r="B42" s="574" t="s">
+      <c r="A42" s="574"/>
+      <c r="B42" s="576" t="s">
         <v>274</v>
       </c>
       <c r="C42" s="11" t="s">
@@ -23370,8 +23367,8 @@
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A43" s="571"/>
-      <c r="B43" s="574"/>
+      <c r="A43" s="574"/>
+      <c r="B43" s="576"/>
       <c r="C43" s="11" t="s">
         <v>272</v>
       </c>
@@ -23422,8 +23419,8 @@
       </c>
     </row>
     <row r="44" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="571"/>
-      <c r="B44" s="574"/>
+      <c r="A44" s="574"/>
+      <c r="B44" s="576"/>
       <c r="C44" s="11" t="s">
         <v>273</v>
       </c>
@@ -23474,10 +23471,10 @@
       </c>
     </row>
     <row r="45" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="571" t="s">
+      <c r="A45" s="574" t="s">
         <v>393</v>
       </c>
-      <c r="B45" s="573" t="s">
+      <c r="B45" s="575" t="s">
         <v>271</v>
       </c>
       <c r="C45" s="37" t="s">
@@ -23530,8 +23527,8 @@
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A46" s="571"/>
-      <c r="B46" s="574"/>
+      <c r="A46" s="574"/>
+      <c r="B46" s="576"/>
       <c r="C46" s="11" t="s">
         <v>272</v>
       </c>
@@ -23582,8 +23579,8 @@
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A47" s="571"/>
-      <c r="B47" s="574"/>
+      <c r="A47" s="574"/>
+      <c r="B47" s="576"/>
       <c r="C47" s="11" t="s">
         <v>273</v>
       </c>
@@ -23634,8 +23631,8 @@
       </c>
     </row>
     <row r="48" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="571"/>
-      <c r="B48" s="574" t="s">
+      <c r="A48" s="574"/>
+      <c r="B48" s="576" t="s">
         <v>274</v>
       </c>
       <c r="C48" s="11" t="s">
@@ -23688,8 +23685,8 @@
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A49" s="571"/>
-      <c r="B49" s="574"/>
+      <c r="A49" s="574"/>
+      <c r="B49" s="576"/>
       <c r="C49" s="11" t="s">
         <v>272</v>
       </c>
@@ -23740,8 +23737,8 @@
       </c>
     </row>
     <row r="50" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="571"/>
-      <c r="B50" s="574"/>
+      <c r="A50" s="574"/>
+      <c r="B50" s="576"/>
       <c r="C50" s="11" t="s">
         <v>273</v>
       </c>
@@ -23792,10 +23789,10 @@
       </c>
     </row>
     <row r="51" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="571" t="s">
+      <c r="A51" s="574" t="s">
         <v>394</v>
       </c>
-      <c r="B51" s="573" t="s">
+      <c r="B51" s="575" t="s">
         <v>271</v>
       </c>
       <c r="C51" s="37" t="s">
@@ -23848,8 +23845,8 @@
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A52" s="571"/>
-      <c r="B52" s="574"/>
+      <c r="A52" s="574"/>
+      <c r="B52" s="576"/>
       <c r="C52" s="11" t="s">
         <v>272</v>
       </c>
@@ -23900,8 +23897,8 @@
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A53" s="571"/>
-      <c r="B53" s="574"/>
+      <c r="A53" s="574"/>
+      <c r="B53" s="576"/>
       <c r="C53" s="11" t="s">
         <v>273</v>
       </c>
@@ -23952,8 +23949,8 @@
       </c>
     </row>
     <row r="54" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="571"/>
-      <c r="B54" s="574" t="s">
+      <c r="A54" s="574"/>
+      <c r="B54" s="576" t="s">
         <v>274</v>
       </c>
       <c r="C54" s="11" t="s">
@@ -24006,8 +24003,8 @@
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A55" s="571"/>
-      <c r="B55" s="574"/>
+      <c r="A55" s="574"/>
+      <c r="B55" s="576"/>
       <c r="C55" s="11" t="s">
         <v>272</v>
       </c>
@@ -24058,8 +24055,8 @@
       </c>
     </row>
     <row r="56" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="572"/>
-      <c r="B56" s="574"/>
+      <c r="A56" s="577"/>
+      <c r="B56" s="576"/>
       <c r="C56" s="11" t="s">
         <v>273</v>
       </c>
@@ -24111,25 +24108,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="A27:A32"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B36:B38"/>
     <mergeCell ref="A51:A56"/>
     <mergeCell ref="B51:B53"/>
     <mergeCell ref="B54:B56"/>
@@ -24139,6 +24117,25 @@
     <mergeCell ref="A45:A50"/>
     <mergeCell ref="B45:B47"/>
     <mergeCell ref="B48:B50"/>
+    <mergeCell ref="A27:A32"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -56700,7 +56697,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="60" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B3" s="61" t="s">
         <v>576</v>
@@ -56840,7 +56837,7 @@
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="60"/>
       <c r="B6" s="61" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C6" s="354">
         <v>53.747727971830976</v>
@@ -56884,7 +56881,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="60" t="s">
-        <v>579</v>
+        <v>399</v>
       </c>
       <c r="B7" s="61" t="s">
         <v>576</v>
@@ -57024,7 +57021,7 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="60"/>
       <c r="B10" s="61" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C10" s="354">
         <v>54.810216828985524</v>
@@ -57208,7 +57205,7 @@
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="60"/>
       <c r="B14" s="61" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C14" s="354">
         <v>48.035462363736258</v>
@@ -57392,7 +57389,7 @@
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="60"/>
       <c r="B18" s="61" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C18" s="354">
         <v>78.130278452675611</v>
@@ -57576,7 +57573,7 @@
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="60"/>
       <c r="B22" s="61" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C22" s="354">
         <v>88.364030628762535</v>
@@ -57760,7 +57757,7 @@
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="60"/>
       <c r="B26" s="61" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C26" s="354">
         <v>80.171314617411696</v>
@@ -57944,7 +57941,7 @@
     <row r="30" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="66"/>
       <c r="B30" s="61" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C30" s="354">
         <v>77.420896134762941</v>

--- a/data_input/MI_Buildings_Oorschot2023.xlsx
+++ b/data_input/MI_Buildings_Oorschot2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mira/Documents/IE/REAL UTOPIAN HOUSING/Post-GrowthHousingScenarios/Code/housing-footprints/data_input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6bba444eb789f06d/Documents/GitHub/Housing-Fooprints/housing-footprints/data_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEB5C0C-B410-C448-ADA9-0E521AE16BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9AEB5C0C-B410-C448-ADA9-0E521AE16BA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2C39521-1F1C-483A-A1FD-A828F655A606}"/>
   <bookViews>
-    <workbookView xWindow="10660" yWindow="500" windowWidth="14940" windowHeight="15500" tabRatio="902" firstSheet="8" activeTab="5" xr2:uid="{501A363E-84AB-4328-B285-EDCE5CC29F1E}"/>
+    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="10276" tabRatio="902" firstSheet="1" activeTab="6" xr2:uid="{501A363E-84AB-4328-B285-EDCE5CC29F1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Content" sheetId="24" r:id="rId1"/>
@@ -4526,7 +4526,7 @@
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4558,7 +4558,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7941,6 +7941,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7948,7 +7949,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7986,7 +7986,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10411,7 +10411,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12588,6 +12588,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -12595,7 +12596,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12633,7 +12633,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17485,12 +17485,12 @@
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="61.83203125" customWidth="1"/>
+    <col min="2" max="2" width="61.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="403" t="s">
         <v>556</v>
       </c>
@@ -17503,7 +17503,7 @@
       <c r="H1" s="405"/>
       <c r="I1" s="405"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="405"/>
       <c r="B2" s="405"/>
       <c r="C2" s="405"/>
@@ -17514,7 +17514,7 @@
       <c r="H2" s="405"/>
       <c r="I2" s="405"/>
     </row>
-    <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="406" t="s">
         <v>558</v>
       </c>
@@ -17527,7 +17527,7 @@
       <c r="H3" s="405"/>
       <c r="I3" s="405"/>
     </row>
-    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A4" s="406"/>
       <c r="B4" s="405"/>
       <c r="C4" s="405"/>
@@ -17538,7 +17538,7 @@
       <c r="H4" s="405"/>
       <c r="I4" s="405"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="543" t="s">
         <v>559</v>
       </c>
@@ -17551,7 +17551,7 @@
       <c r="H5" s="543"/>
       <c r="I5" s="543"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="543"/>
       <c r="B6" s="543"/>
       <c r="C6" s="543"/>
@@ -17562,7 +17562,7 @@
       <c r="H6" s="543"/>
       <c r="I6" s="543"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="405"/>
       <c r="B7" s="405"/>
       <c r="C7" s="405"/>
@@ -17573,7 +17573,7 @@
       <c r="H7" s="405"/>
       <c r="I7" s="405"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="544" t="s">
         <v>557</v>
       </c>
@@ -17586,7 +17586,7 @@
       <c r="H8" s="544"/>
       <c r="I8" s="407"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="544"/>
       <c r="B9" s="544"/>
       <c r="C9" s="544"/>
@@ -17597,7 +17597,7 @@
       <c r="H9" s="544"/>
       <c r="I9" s="407"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="407"/>
       <c r="B10" s="407"/>
       <c r="C10" s="407"/>
@@ -17608,7 +17608,7 @@
       <c r="H10" s="407"/>
       <c r="I10" s="407"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="407"/>
       <c r="B11" s="407"/>
       <c r="C11" s="407"/>
@@ -17619,19 +17619,19 @@
       <c r="H11" s="407"/>
       <c r="I11" s="407"/>
     </row>
-    <row r="12" spans="1:9" s="307" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" s="307" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A12" s="372" t="s">
         <v>501</v>
       </c>
       <c r="B12" s="372"/>
     </row>
-    <row r="13" spans="1:9" s="307" customFormat="1" ht="21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="307" customFormat="1" ht="21" x14ac:dyDescent="0.35">
       <c r="A13" s="373" t="s">
         <v>414</v>
       </c>
       <c r="B13" s="372"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="374" t="s">
         <v>448</v>
       </c>
@@ -17639,7 +17639,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="375" t="s">
         <v>449</v>
       </c>
@@ -17647,7 +17647,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="376" t="s">
         <v>450</v>
       </c>
@@ -17655,7 +17655,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="377" t="s">
         <v>451</v>
       </c>
@@ -17663,7 +17663,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="378" t="s">
         <v>452</v>
       </c>
@@ -17671,7 +17671,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="379" t="s">
         <v>453</v>
       </c>
@@ -17679,19 +17679,19 @@
         <v>499</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="57"/>
       <c r="B20" s="57"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="57"/>
       <c r="B21" s="57"/>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="57"/>
       <c r="B22" s="57"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="57"/>
       <c r="B23" s="57"/>
     </row>
@@ -17715,24 +17715,24 @@
     <tabColor theme="3" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:S52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.1640625" customWidth="1"/>
-    <col min="2" max="4" width="14.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="54.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="1"/>
-    <col min="9" max="9" width="44.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.83203125" customWidth="1"/>
-    <col min="14" max="14" width="18.33203125" customWidth="1"/>
-    <col min="15" max="15" width="19.6640625" customWidth="1"/>
-    <col min="16" max="16" width="23.5" customWidth="1"/>
-    <col min="17" max="17" width="25.1640625" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="31.28515625" customWidth="1"/>
+    <col min="7" max="7" width="54.85546875" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="1"/>
+    <col min="9" max="9" width="44.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.85546875" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" customWidth="1"/>
+    <col min="16" max="16" width="23.42578125" customWidth="1"/>
+    <col min="17" max="17" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="46.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="46.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="258" t="s">
         <v>188</v>
       </c>
@@ -17768,7 +17768,7 @@
       <c r="R1" s="42"/>
       <c r="S1" s="188"/>
     </row>
-    <row r="2" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="260" t="s">
         <v>88</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="261" t="s">
         <v>190</v>
       </c>
@@ -17855,7 +17855,7 @@
         <v>1.4528631597813424E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="261" t="s">
         <v>191</v>
       </c>
@@ -17897,7 +17897,7 @@
       </c>
       <c r="S4" s="281"/>
     </row>
-    <row r="5" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="260" t="s">
         <v>193</v>
       </c>
@@ -17938,7 +17938,7 @@
       </c>
       <c r="S5" s="281"/>
     </row>
-    <row r="6" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="262" t="s">
         <v>194</v>
       </c>
@@ -17979,7 +17979,7 @@
       </c>
       <c r="S6" s="281"/>
     </row>
-    <row r="7" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="262" t="s">
         <v>196</v>
       </c>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="S7" s="281"/>
     </row>
-    <row r="8" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="262" t="s">
         <v>197</v>
       </c>
@@ -18062,7 +18062,7 @@
       </c>
       <c r="S8" s="290"/>
     </row>
-    <row r="9" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="261" t="s">
         <v>199</v>
       </c>
@@ -18087,7 +18087,7 @@
       <c r="I9" s="271"/>
       <c r="J9" s="271"/>
     </row>
-    <row r="10" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="261" t="s">
         <v>201</v>
       </c>
@@ -18112,7 +18112,7 @@
       <c r="I10" s="271"/>
       <c r="J10" s="271"/>
     </row>
-    <row r="11" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="261" t="s">
         <v>203</v>
       </c>
@@ -18139,7 +18139,7 @@
       <c r="I11" s="271"/>
       <c r="J11" s="271"/>
     </row>
-    <row r="12" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="261" t="s">
         <v>205</v>
       </c>
@@ -18163,7 +18163,7 @@
       <c r="I12" s="271"/>
       <c r="J12" s="271"/>
     </row>
-    <row r="13" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="261" t="s">
         <v>207</v>
       </c>
@@ -18188,7 +18188,7 @@
       <c r="I13" s="271"/>
       <c r="J13" s="271"/>
     </row>
-    <row r="14" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="262" t="s">
         <v>209</v>
       </c>
@@ -18213,7 +18213,7 @@
       <c r="I14" s="271"/>
       <c r="J14" s="271"/>
     </row>
-    <row r="15" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="262" t="s">
         <v>421</v>
       </c>
@@ -18240,7 +18240,7 @@
       <c r="I15" s="271"/>
       <c r="J15" s="271"/>
     </row>
-    <row r="16" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="262" t="s">
         <v>422</v>
       </c>
@@ -18267,7 +18267,7 @@
       <c r="I16" s="271"/>
       <c r="J16" s="271"/>
     </row>
-    <row r="17" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="262" t="s">
         <v>214</v>
       </c>
@@ -18293,7 +18293,7 @@
       <c r="I17" s="271"/>
       <c r="J17" s="271"/>
     </row>
-    <row r="18" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="262" t="s">
         <v>180</v>
       </c>
@@ -18319,7 +18319,7 @@
       <c r="I18" s="271"/>
       <c r="J18" s="271"/>
     </row>
-    <row r="19" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="262" t="s">
         <v>86</v>
       </c>
@@ -18343,7 +18343,7 @@
       <c r="I19" s="271"/>
       <c r="J19" s="271"/>
     </row>
-    <row r="20" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="262" t="s">
         <v>87</v>
       </c>
@@ -18367,7 +18367,7 @@
       <c r="I20" s="271"/>
       <c r="J20" s="271"/>
     </row>
-    <row r="21" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="262" t="s">
         <v>218</v>
       </c>
@@ -18391,7 +18391,7 @@
       <c r="I21" s="271"/>
       <c r="J21" s="271"/>
     </row>
-    <row r="22" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" s="269" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="263" t="s">
         <v>220</v>
       </c>
@@ -18416,149 +18416,149 @@
       <c r="I22" s="271"/>
       <c r="J22" s="271"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" s="55"/>
       <c r="C23" s="55"/>
       <c r="D23" s="55"/>
       <c r="E23" s="55"/>
       <c r="F23" s="56"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="257"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="57" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="57" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="57"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="57"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="190" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>424</v>
       </c>
       <c r="H30"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>373</v>
       </c>
       <c r="H31"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>425</v>
       </c>
       <c r="H32"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>227</v>
       </c>
       <c r="H33"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>426</v>
       </c>
       <c r="H34"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>427</v>
       </c>
       <c r="H35"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="58" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="58" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="58"/>
       <c r="B52" s="1"/>
     </row>
@@ -18577,19 +18577,19 @@
     <tabColor rgb="FF8DAEC9"/>
   </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" customWidth="1"/>
-    <col min="4" max="5" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" customWidth="1"/>
+    <col min="4" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="488" t="s">
         <v>540</v>
       </c>
@@ -18617,7 +18617,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="478" t="s">
         <v>271</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>5095675.0844885828</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="467"/>
       <c r="B3" s="66"/>
       <c r="C3" s="67" t="s">
@@ -18677,7 +18677,7 @@
         <v>942333.28004642739</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="467"/>
       <c r="B4" s="57" t="s">
         <v>272</v>
@@ -18707,7 +18707,7 @@
         <v>5595324.3841417599</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="467"/>
       <c r="B5" s="57"/>
       <c r="C5" s="61" t="s">
@@ -18735,7 +18735,7 @@
         <v>1432215.365519857</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="467"/>
       <c r="B6" s="69" t="s">
         <v>273</v>
@@ -18765,7 +18765,7 @@
         <v>4384581.8860594379</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="467"/>
       <c r="B7" s="60"/>
       <c r="C7" s="61" t="s">
@@ -18793,7 +18793,7 @@
         <v>124044.191599132</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="478" t="s">
         <v>274</v>
       </c>
@@ -18825,7 +18825,7 @@
         <v>406264.67340727849</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="467"/>
       <c r="B9" s="57"/>
       <c r="C9" s="61" t="s">
@@ -18853,7 +18853,7 @@
         <v>208133.67615869909</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="467"/>
       <c r="B10" s="69" t="s">
         <v>272</v>
@@ -18883,7 +18883,7 @@
         <v>476990.9630019035</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="467"/>
       <c r="B11" s="66"/>
       <c r="C11" s="67" t="s">
@@ -18911,7 +18911,7 @@
         <v>252590.78889212309</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="467"/>
       <c r="B12" s="57" t="s">
         <v>273</v>
@@ -18941,7 +18941,7 @@
         <v>355080.81340085098</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="477"/>
       <c r="B13" s="68"/>
       <c r="C13" s="67" t="s">
@@ -18969,8 +18969,8 @@
         <v>7789.7676576923059</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="489" t="s">
         <v>541</v>
       </c>
@@ -19001,7 +19001,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="66"/>
       <c r="B16" s="68"/>
       <c r="C16" s="68">
@@ -19032,7 +19032,7 @@
         <v>1402271402.8442116</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="69" t="s">
         <v>271</v>
       </c>
@@ -19067,7 +19067,7 @@
         <v>1664853767.1409082</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="60"/>
       <c r="B18" s="57" t="s">
         <v>272</v>
@@ -19100,7 +19100,7 @@
         <v>1678736235.0191722</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="60"/>
       <c r="B19" s="57" t="s">
         <v>273</v>
@@ -19133,7 +19133,7 @@
         <v>1697849160.0382285</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="60" t="s">
         <v>274</v>
       </c>
@@ -19168,7 +19168,7 @@
         <v>1512152436.5548704</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="60"/>
       <c r="B21" s="57" t="s">
         <v>272</v>
@@ -19201,7 +19201,7 @@
         <v>1516584556.2912996</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="66"/>
       <c r="B22" s="68" t="s">
         <v>273</v>
@@ -19234,16 +19234,16 @@
         <v>1526201178.9007049</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C23" s="57"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C24" s="57"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C25" s="57"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C26" s="57"/>
     </row>
   </sheetData>
@@ -19258,14 +19258,14 @@
     <tabColor rgb="FF8DAEC9"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
-    <col min="3" max="4" width="8.83203125" style="512"/>
-    <col min="5" max="5" width="18.33203125" style="505" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="3" max="4" width="8.85546875" style="512"/>
+    <col min="5" max="5" width="18.28515625" style="505" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="492" t="s">
         <v>395</v>
       </c>
@@ -19277,7 +19277,7 @@
       <c r="E1" s="570"/>
       <c r="F1" s="494"/>
     </row>
-    <row r="2" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="495"/>
       <c r="B2" s="496"/>
       <c r="C2" s="513" t="s">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="F2" s="494"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="497" t="s">
         <v>398</v>
       </c>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="F3" s="494"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="497"/>
       <c r="B4" s="498" t="s">
         <v>267</v>
@@ -19328,7 +19328,7 @@
       <c r="E4" s="501"/>
       <c r="F4" s="494"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="497"/>
       <c r="B5" s="498" t="s">
         <v>268</v>
@@ -19344,7 +19344,7 @@
       <c r="E5" s="501"/>
       <c r="F5" s="494"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="497"/>
       <c r="B6" s="498" t="s">
         <v>455</v>
@@ -19360,7 +19360,7 @@
       <c r="E6" s="501"/>
       <c r="F6" s="494"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="497" t="s">
         <v>399</v>
       </c>
@@ -19381,7 +19381,7 @@
       </c>
       <c r="F7" s="494"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="497"/>
       <c r="B8" s="498" t="s">
         <v>267</v>
@@ -19397,7 +19397,7 @@
       <c r="E8" s="501"/>
       <c r="F8" s="494"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="497"/>
       <c r="B9" s="498" t="s">
         <v>268</v>
@@ -19413,7 +19413,7 @@
       <c r="E9" s="501"/>
       <c r="F9" s="494"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="497"/>
       <c r="B10" s="498" t="s">
         <v>455</v>
@@ -19429,7 +19429,7 @@
       <c r="E10" s="502"/>
       <c r="F10" s="494"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="497" t="s">
         <v>400</v>
       </c>
@@ -19450,7 +19450,7 @@
       </c>
       <c r="F11" s="494"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="497"/>
       <c r="B12" s="498" t="s">
         <v>267</v>
@@ -19466,7 +19466,7 @@
       <c r="E12" s="501"/>
       <c r="F12" s="494"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="497"/>
       <c r="B13" s="498" t="s">
         <v>268</v>
@@ -19482,7 +19482,7 @@
       <c r="E13" s="501"/>
       <c r="F13" s="494"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="497"/>
       <c r="B14" s="498" t="s">
         <v>455</v>
@@ -19498,7 +19498,7 @@
       <c r="E14" s="501"/>
       <c r="F14" s="494"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="497" t="s">
         <v>401</v>
       </c>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="F15" s="494"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="497"/>
       <c r="B16" s="498" t="s">
         <v>267</v>
@@ -19535,7 +19535,7 @@
       <c r="E16" s="501"/>
       <c r="F16" s="494"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="497"/>
       <c r="B17" s="498" t="s">
         <v>268</v>
@@ -19551,7 +19551,7 @@
       <c r="E17" s="501"/>
       <c r="F17" s="494"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="497"/>
       <c r="B18" s="498" t="s">
         <v>455</v>
@@ -19567,7 +19567,7 @@
       <c r="E18" s="502"/>
       <c r="F18" s="494"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="497" t="s">
         <v>402</v>
       </c>
@@ -19588,7 +19588,7 @@
       </c>
       <c r="F19" s="494"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="497"/>
       <c r="B20" s="498" t="s">
         <v>267</v>
@@ -19604,7 +19604,7 @@
       <c r="E20" s="501"/>
       <c r="F20" s="494"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="497"/>
       <c r="B21" s="498" t="s">
         <v>268</v>
@@ -19620,7 +19620,7 @@
       <c r="E21" s="501"/>
       <c r="F21" s="494"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="497"/>
       <c r="B22" s="498" t="s">
         <v>455</v>
@@ -19636,7 +19636,7 @@
       <c r="E22" s="501"/>
       <c r="F22" s="494"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="497" t="s">
         <v>403</v>
       </c>
@@ -19657,7 +19657,7 @@
       </c>
       <c r="F23" s="494"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="497"/>
       <c r="B24" s="498" t="s">
         <v>267</v>
@@ -19673,7 +19673,7 @@
       <c r="E24" s="501"/>
       <c r="F24" s="494"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="497"/>
       <c r="B25" s="498" t="s">
         <v>268</v>
@@ -19689,7 +19689,7 @@
       <c r="E25" s="501"/>
       <c r="F25" s="494"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="497"/>
       <c r="B26" s="498" t="s">
         <v>455</v>
@@ -19705,7 +19705,7 @@
       <c r="E26" s="502"/>
       <c r="F26" s="494"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="497" t="s">
         <v>404</v>
       </c>
@@ -19726,7 +19726,7 @@
       </c>
       <c r="F27" s="494"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="497"/>
       <c r="B28" s="498" t="s">
         <v>267</v>
@@ -19742,7 +19742,7 @@
       <c r="E28" s="503"/>
       <c r="F28" s="494"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="497"/>
       <c r="B29" s="498" t="s">
         <v>268</v>
@@ -19758,7 +19758,7 @@
       <c r="E29" s="503"/>
       <c r="F29" s="494"/>
     </row>
-    <row r="30" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="495"/>
       <c r="B30" s="496" t="s">
         <v>455</v>
@@ -19774,7 +19774,7 @@
       <c r="E30" s="504"/>
       <c r="F30" s="494"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D31" s="511"/>
     </row>
   </sheetData>
@@ -19792,19 +19792,19 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:P32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="11" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="8.83203125" style="130"/>
-    <col min="3" max="3" width="11.83203125" style="130" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="8.85546875" style="130"/>
+    <col min="3" max="3" width="11.85546875" style="130" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="9" style="130" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" style="130" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.1640625" style="130" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" style="130" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" style="130" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.140625" style="130" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="130" bestFit="1" customWidth="1"/>
     <col min="11" max="15" width="9" style="130" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.83203125" style="130"/>
+    <col min="16" max="16384" width="8.85546875" style="130"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="312" t="s">
         <v>265</v>
       </c>
@@ -19849,7 +19849,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="132" t="s">
         <v>386</v>
       </c>
@@ -19897,7 +19897,7 @@
       </c>
       <c r="P2" s="142"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="132"/>
       <c r="B3" s="143" t="s">
         <v>267</v>
@@ -19942,7 +19942,7 @@
         <v>123832.2194997067</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="132"/>
       <c r="B4" s="143" t="s">
         <v>268</v>
@@ -19987,7 +19987,7 @@
         <v>220402.87955134778</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="132"/>
       <c r="B5" s="143" t="s">
         <v>269</v>
@@ -20032,7 +20032,7 @@
         <v>108229.32908860011</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="132" t="s">
         <v>387</v>
       </c>
@@ -20079,7 +20079,7 @@
         <v>85598.59835845702</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="132"/>
       <c r="B7" s="143" t="s">
         <v>267</v>
@@ -20124,7 +20124,7 @@
         <v>157659.4651217545</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="132"/>
       <c r="B8" s="143" t="s">
         <v>268</v>
@@ -20169,7 +20169,7 @@
         <v>407714.75463844708</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="132"/>
       <c r="B9" s="143" t="s">
         <v>269</v>
@@ -20214,7 +20214,7 @@
         <v>131700.49770465211</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="132" t="s">
         <v>388</v>
       </c>
@@ -20261,7 +20261,7 @@
         <v>131543.76741575659</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="132"/>
       <c r="B11" s="143" t="s">
         <v>267</v>
@@ -20306,7 +20306,7 @@
         <v>272608.43491274951</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="132"/>
       <c r="B12" s="143" t="s">
         <v>268</v>
@@ -20351,7 +20351,7 @@
         <v>486428.84451934928</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="132"/>
       <c r="B13" s="143" t="s">
         <v>269</v>
@@ -20396,7 +20396,7 @@
         <v>340291.34916337871</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="132" t="s">
         <v>389</v>
       </c>
@@ -20443,7 +20443,7 @@
         <v>2904.861054122704</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="132"/>
       <c r="B15" s="143" t="s">
         <v>267</v>
@@ -20488,7 +20488,7 @@
         <v>10974.327009095261</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="132"/>
       <c r="B16" s="143" t="s">
         <v>268</v>
@@ -20533,7 +20533,7 @@
         <v>36260.933608670799</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="132"/>
       <c r="B17" s="143" t="s">
         <v>269</v>
@@ -20578,7 +20578,7 @@
         <v>26202.69497586511</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="132" t="s">
         <v>390</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>23442.490045868562</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="132"/>
       <c r="B19" s="143" t="s">
         <v>267</v>
@@ -20670,7 +20670,7 @@
         <v>24302.87893907824</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="132"/>
       <c r="B20" s="143" t="s">
         <v>268</v>
@@ -20715,7 +20715,7 @@
         <v>101413.29094303871</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="132"/>
       <c r="B21" s="143" t="s">
         <v>269</v>
@@ -20760,7 +20760,7 @@
         <v>75074.037365744996</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="132" t="s">
         <v>391</v>
       </c>
@@ -20807,7 +20807,7 @@
         <v>11029.13178603825</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="132"/>
       <c r="B23" s="143" t="s">
         <v>267</v>
@@ -20852,7 +20852,7 @@
         <v>46925.376924824515</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="132"/>
       <c r="B24" s="143" t="s">
         <v>268</v>
@@ -20897,7 +20897,7 @@
         <v>114948.62492062179</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="132"/>
       <c r="B25" s="143" t="s">
         <v>269</v>
@@ -20942,7 +20942,7 @@
         <v>69952.419225238205</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="132" t="s">
         <v>392</v>
       </c>
@@ -20989,7 +20989,7 @@
         <v>3135.0935818381831</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="132"/>
       <c r="B27" s="143" t="s">
         <v>267</v>
@@ -21034,7 +21034,7 @@
         <v>8566.0642705865102</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="132"/>
       <c r="B28" s="143" t="s">
         <v>268</v>
@@ -21079,7 +21079,7 @@
         <v>38874.145159517255</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="12" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="144"/>
       <c r="B29" s="145" t="s">
         <v>269</v>
@@ -21124,7 +21124,7 @@
         <v>22568.040042236189</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="H32" s="142"/>
     </row>
   </sheetData>
@@ -21138,13 +21138,13 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:R56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="20" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="20" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="168"/>
       <c r="B1" s="169"/>
       <c r="C1" s="170" t="s">
@@ -21196,7 +21196,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="571">
         <v>2018</v>
       </c>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="R2" s="175"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="573" t="s">
         <v>235</v>
       </c>
@@ -21300,7 +21300,7 @@
         <v>101327.10855100733</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="574"/>
       <c r="B4" s="576"/>
       <c r="C4" s="11" t="s">
@@ -21352,7 +21352,7 @@
         <v>109333.68255917942</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="574"/>
       <c r="B5" s="576"/>
       <c r="C5" s="11" t="s">
@@ -21404,7 +21404,7 @@
         <v>131027.97462448188</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="574"/>
       <c r="B6" s="576" t="s">
         <v>274</v>
@@ -21458,7 +21458,7 @@
         <v>39484.476841821073</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="574"/>
       <c r="B7" s="576"/>
       <c r="C7" s="11" t="s">
@@ -21510,7 +21510,7 @@
         <v>40859.075215163561</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="574"/>
       <c r="B8" s="576"/>
       <c r="C8" s="11" t="s">
@@ -21562,7 +21562,7 @@
         <v>53106.703470218003</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="574" t="s">
         <v>275</v>
       </c>
@@ -21618,7 +21618,7 @@
         <v>119579.92266604501</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="574"/>
       <c r="B10" s="576"/>
       <c r="C10" s="11" t="s">
@@ -21670,7 +21670,7 @@
         <v>129199.52689721044</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="574"/>
       <c r="B11" s="576"/>
       <c r="C11" s="11" t="s">
@@ -21722,7 +21722,7 @@
         <v>155428.66170538496</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="574"/>
       <c r="B12" s="576" t="s">
         <v>274</v>
@@ -21776,7 +21776,7 @@
         <v>46821.271216469482</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="574"/>
       <c r="B13" s="576"/>
       <c r="C13" s="11" t="s">
@@ -21828,7 +21828,7 @@
         <v>48459.40652673471</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="574"/>
       <c r="B14" s="576"/>
       <c r="C14" s="11" t="s">
@@ -21880,7 +21880,7 @@
         <v>63228.59310931174</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="574" t="s">
         <v>276</v>
       </c>
@@ -21936,7 +21936,7 @@
         <v>83074.294435969656</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="574"/>
       <c r="B16" s="576"/>
       <c r="C16" s="11" t="s">
@@ -21988,7 +21988,7 @@
         <v>89467.838221148457</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="574"/>
       <c r="B17" s="576"/>
       <c r="C17" s="11" t="s">
@@ -22040,7 +22040,7 @@
         <v>106627.28754357883</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="574"/>
       <c r="B18" s="576" t="s">
         <v>274</v>
@@ -22094,7 +22094,7 @@
         <v>32147.68246717269</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="574"/>
       <c r="B19" s="576"/>
       <c r="C19" s="11" t="s">
@@ -22146,7 +22146,7 @@
         <v>33258.743903592433</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="574"/>
       <c r="B20" s="576"/>
       <c r="C20" s="11" t="s">
@@ -22198,7 +22198,7 @@
         <v>42984.813831124287</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="574" t="s">
         <v>236</v>
       </c>
@@ -22254,7 +22254,7 @@
         <v>380362.19277958805</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="574"/>
       <c r="B22" s="576"/>
       <c r="C22" s="11" t="s">
@@ -22306,7 +22306,7 @@
         <v>412711.19491310348</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="574"/>
       <c r="B23" s="576"/>
       <c r="C23" s="11" t="s">
@@ -22358,7 +22358,7 @@
         <v>501558.15095471533</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="574"/>
       <c r="B24" s="576" t="s">
         <v>274</v>
@@ -22412,7 +22412,7 @@
         <v>150236.51087241841</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="574"/>
       <c r="B25" s="576"/>
       <c r="C25" s="11" t="s">
@@ -22464,7 +22464,7 @@
         <v>155535.0065472197</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="574"/>
       <c r="B26" s="576"/>
       <c r="C26" s="11" t="s">
@@ -22516,7 +22516,7 @@
         <v>205526.90276392378</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="574" t="s">
         <v>277</v>
       </c>
@@ -22572,7 +22572,7 @@
         <v>453373.44923973881</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="574"/>
       <c r="B28" s="576"/>
       <c r="C28" s="11" t="s">
@@ -22624,7 +22624,7 @@
         <v>492174.5722652275</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="574"/>
       <c r="B29" s="576"/>
       <c r="C29" s="11" t="s">
@@ -22676,7 +22676,7 @@
         <v>599160.89927832759</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="574"/>
       <c r="B30" s="576" t="s">
         <v>274</v>
@@ -22730,7 +22730,7 @@
         <v>179583.68837101193</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="574"/>
       <c r="B31" s="576"/>
       <c r="C31" s="11" t="s">
@@ -22782,7 +22782,7 @@
         <v>185936.33179350424</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="574"/>
       <c r="B32" s="576"/>
       <c r="C32" s="11" t="s">
@@ -22834,7 +22834,7 @@
         <v>246014.46132029858</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="574" t="s">
         <v>278</v>
       </c>
@@ -22890,7 +22890,7 @@
         <v>307350.9363194374</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="574"/>
       <c r="B34" s="576"/>
       <c r="C34" s="11" t="s">
@@ -22942,7 +22942,7 @@
         <v>333247.81756097963</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="574"/>
       <c r="B35" s="576"/>
       <c r="C35" s="11" t="s">
@@ -22994,7 +22994,7 @@
         <v>403955.40263110294</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="574"/>
       <c r="B36" s="576" t="s">
         <v>274</v>
@@ -23048,7 +23048,7 @@
         <v>120889.33337382477</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="574"/>
       <c r="B37" s="576"/>
       <c r="C37" s="11" t="s">
@@ -23100,7 +23100,7 @@
         <v>125133.68130093512</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="574"/>
       <c r="B38" s="576"/>
       <c r="C38" s="11" t="s">
@@ -23152,7 +23152,7 @@
         <v>165039.34420754886</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="574" t="s">
         <v>241</v>
       </c>
@@ -23208,7 +23208,7 @@
         <v>101327.10855100733</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="574"/>
       <c r="B40" s="576"/>
       <c r="C40" s="11" t="s">
@@ -23260,7 +23260,7 @@
         <v>109333.68255917942</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="574"/>
       <c r="B41" s="576"/>
       <c r="C41" s="11" t="s">
@@ -23312,7 +23312,7 @@
         <v>131027.97462448188</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="574"/>
       <c r="B42" s="576" t="s">
         <v>274</v>
@@ -23366,7 +23366,7 @@
         <v>39484.476841821073</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="574"/>
       <c r="B43" s="576"/>
       <c r="C43" s="11" t="s">
@@ -23418,7 +23418,7 @@
         <v>40859.075215163561</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="574"/>
       <c r="B44" s="576"/>
       <c r="C44" s="11" t="s">
@@ -23470,7 +23470,7 @@
         <v>53106.703470218003</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="574" t="s">
         <v>393</v>
       </c>
@@ -23526,7 +23526,7 @@
         <v>119579.92266604501</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="574"/>
       <c r="B46" s="576"/>
       <c r="C46" s="11" t="s">
@@ -23578,7 +23578,7 @@
         <v>129199.52689721044</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="574"/>
       <c r="B47" s="576"/>
       <c r="C47" s="11" t="s">
@@ -23630,7 +23630,7 @@
         <v>155428.66170538496</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="574"/>
       <c r="B48" s="576" t="s">
         <v>274</v>
@@ -23684,7 +23684,7 @@
         <v>46821.271216469482</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="574"/>
       <c r="B49" s="576"/>
       <c r="C49" s="11" t="s">
@@ -23736,7 +23736,7 @@
         <v>48459.40652673471</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="574"/>
       <c r="B50" s="576"/>
       <c r="C50" s="11" t="s">
@@ -23788,7 +23788,7 @@
         <v>63228.59310931174</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="574" t="s">
         <v>394</v>
       </c>
@@ -23844,7 +23844,7 @@
         <v>83074.294435969656</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="574"/>
       <c r="B52" s="576"/>
       <c r="C52" s="11" t="s">
@@ -23896,7 +23896,7 @@
         <v>89467.838221148457</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="574"/>
       <c r="B53" s="576"/>
       <c r="C53" s="11" t="s">
@@ -23948,7 +23948,7 @@
         <v>106627.28754357883</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="574"/>
       <c r="B54" s="576" t="s">
         <v>274</v>
@@ -24002,7 +24002,7 @@
         <v>32147.68246717269</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="574"/>
       <c r="B55" s="576"/>
       <c r="C55" s="11" t="s">
@@ -24054,7 +24054,7 @@
         <v>33258.743903592433</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="577"/>
       <c r="B56" s="576"/>
       <c r="C56" s="11" t="s">
@@ -24147,16 +24147,16 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:Y33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="423" t="s">
         <v>516</v>
@@ -24167,7 +24167,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="16"/>
       <c r="C2" s="4" t="s">
@@ -24180,7 +24180,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="38">
         <v>2018</v>
@@ -24193,7 +24193,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="17">
         <v>2050</v>
@@ -24208,7 +24208,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -24217,7 +24217,7 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="124" t="s">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="125" t="s">
@@ -24251,7 +24251,7 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="449">
         <v>2018</v>
@@ -24273,7 +24273,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="580" t="s">
         <v>235</v>
       </c>
@@ -24297,7 +24297,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="578"/>
       <c r="B10" s="11" t="s">
         <v>272</v>
@@ -24319,7 +24319,7 @@
       </c>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="578"/>
       <c r="B11" s="11" t="s">
         <v>273</v>
@@ -24341,7 +24341,7 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="578" t="s">
         <v>236</v>
       </c>
@@ -24360,7 +24360,7 @@
       </c>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="578"/>
       <c r="B13" s="11" t="s">
         <v>272</v>
@@ -24377,7 +24377,7 @@
       </c>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="578"/>
       <c r="B14" s="427" t="s">
         <v>273</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="578" t="s">
         <v>273</v>
       </c>
@@ -24413,7 +24413,7 @@
       </c>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="578"/>
       <c r="B16" s="11" t="s">
         <v>272</v>
@@ -24430,7 +24430,7 @@
       </c>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="579"/>
       <c r="B17" s="10" t="s">
         <v>273</v>
@@ -24456,7 +24456,7 @@
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -24474,7 +24474,7 @@
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="450" t="s">
         <v>518</v>
@@ -24502,7 +24502,7 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
     </row>
-    <row r="20" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="453" t="s">
         <v>521</v>
@@ -24522,7 +24522,7 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B21" s="460">
         <v>154</v>
       </c>
@@ -24539,7 +24539,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B22" s="460" t="s">
         <v>520</v>
       </c>
@@ -24556,7 +24556,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B23" s="456">
         <v>175</v>
       </c>
@@ -24573,7 +24573,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B24" s="456">
         <v>210</v>
       </c>
@@ -24590,7 +24590,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B25" s="456">
         <v>209</v>
       </c>
@@ -24607,7 +24607,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B26" s="456">
         <v>112</v>
       </c>
@@ -24624,7 +24624,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B27" s="457">
         <v>160</v>
       </c>
@@ -24641,14 +24641,14 @@
         <v>528</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B28" s="517"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="581" t="s">
         <v>553</v>
       </c>
@@ -24679,7 +24679,7 @@
       <c r="X29" s="518"/>
       <c r="Y29" s="519"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="582"/>
       <c r="B30" s="520" t="s">
         <v>551</v>
@@ -24688,21 +24688,21 @@
       <c r="D30" s="1"/>
       <c r="Y30" s="521"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="582"/>
       <c r="B31" s="130" t="s">
         <v>550</v>
       </c>
       <c r="Y31" s="521"/>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="582"/>
       <c r="B32" s="520" t="s">
         <v>552</v>
       </c>
       <c r="Y32" s="521"/>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="583"/>
       <c r="B33" s="458" t="s">
         <v>547</v>
@@ -24749,13 +24749,13 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:AB45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
         <v>254</v>
       </c>
@@ -24833,7 +24833,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="72"/>
       <c r="B2" s="69" t="s">
         <v>378</v>
@@ -24929,7 +24929,7 @@
         <v>101327.10855100733</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="71"/>
       <c r="B3" s="60"/>
       <c r="C3" s="61" t="s">
@@ -25022,7 +25022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="73"/>
       <c r="B4" s="66"/>
       <c r="C4" s="67" t="s">
@@ -25116,7 +25116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="72"/>
       <c r="B5" s="69" t="s">
         <v>236</v>
@@ -25211,7 +25211,7 @@
         <v>380362.19277958805</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="71"/>
       <c r="B6" s="60"/>
       <c r="C6" s="61" t="s">
@@ -25304,7 +25304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="73"/>
       <c r="B7" s="66"/>
       <c r="C7" s="67" t="s">
@@ -25397,7 +25397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="71"/>
       <c r="B8" s="60" t="s">
         <v>241</v>
@@ -25491,7 +25491,7 @@
         <v>101327.10855100733</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="71"/>
       <c r="B9" s="60"/>
       <c r="C9" s="61" t="s">
@@ -25584,7 +25584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="73"/>
       <c r="B10" s="66"/>
       <c r="C10" s="67" t="s">
@@ -25677,7 +25677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B12" s="136" t="s">
         <v>260</v>
       </c>
@@ -25701,8 +25701,8 @@
       <c r="T12" s="135"/>
       <c r="U12" s="135"/>
     </row>
-    <row r="13" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:25" s="137" customFormat="1" ht="70.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:25" s="137" customFormat="1" ht="70.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="380" t="s">
         <v>464</v>
       </c>
@@ -25763,7 +25763,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B15" s="140" t="s">
         <v>378</v>
       </c>
@@ -25831,7 +25831,7 @@
       <c r="T15" s="57"/>
       <c r="U15" s="61"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B16" s="132"/>
       <c r="C16" s="143" t="s">
         <v>259</v>
@@ -25905,7 +25905,7 @@
       </c>
       <c r="U16" s="61"/>
     </row>
-    <row r="17" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="144"/>
       <c r="C17" s="145" t="s">
         <v>244</v>
@@ -25982,7 +25982,7 @@
         <v>0.29041994855338249</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B18" s="140" t="s">
         <v>236</v>
       </c>
@@ -26050,7 +26050,7 @@
       <c r="T18" s="57"/>
       <c r="U18" s="61"/>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B19" s="132"/>
       <c r="C19" s="143" t="s">
         <v>259</v>
@@ -26124,7 +26124,7 @@
       </c>
       <c r="U19" s="61"/>
     </row>
-    <row r="20" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="144"/>
       <c r="C20" s="145" t="s">
         <v>244</v>
@@ -26201,7 +26201,7 @@
         <v>0.28330934447141159</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B21" s="132" t="s">
         <v>241</v>
       </c>
@@ -26269,7 +26269,7 @@
       <c r="T21" s="57"/>
       <c r="U21" s="61"/>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B22" s="132"/>
       <c r="C22" s="143" t="s">
         <v>259</v>
@@ -26343,7 +26343,7 @@
       </c>
       <c r="U22" s="61"/>
     </row>
-    <row r="23" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="144"/>
       <c r="C23" s="145" t="s">
         <v>244</v>
@@ -26420,13 +26420,13 @@
         <v>0.2904096515208871</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="V24" s="584" t="s">
         <v>496</v>
       </c>
       <c r="W24" s="585"/>
     </row>
-    <row r="25" spans="1:28" s="3" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" s="3" customFormat="1" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="381" t="s">
         <v>463</v>
       </c>
@@ -26493,7 +26493,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B26" s="16" t="str">
         <f t="shared" ref="B26:Q28" si="15">B15</f>
         <v>Conventional</v>
@@ -26573,7 +26573,7 @@
       <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B27" s="38"/>
       <c r="C27" s="11" t="str">
         <f t="shared" si="15"/>
@@ -26653,7 +26653,7 @@
       <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
     </row>
-    <row r="28" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B28" s="17"/>
       <c r="C28" s="10" t="str">
         <f t="shared" si="15"/>
@@ -26742,7 +26742,7 @@
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B29" s="38" t="str">
         <f t="shared" ref="B29:Q34" si="17">B18</f>
         <v>Biobased</v>
@@ -26822,7 +26822,7 @@
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B30" s="38"/>
       <c r="C30" s="11" t="str">
         <f t="shared" si="17"/>
@@ -26902,7 +26902,7 @@
       <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
     </row>
-    <row r="31" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="17"/>
       <c r="C31" s="10" t="str">
         <f t="shared" si="17"/>
@@ -26991,7 +26991,7 @@
       <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B32" s="16" t="str">
         <f>B21</f>
         <v>Circular</v>
@@ -27071,7 +27071,7 @@
       <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B33" s="38"/>
       <c r="C33" s="11" t="str">
         <f t="shared" si="17"/>
@@ -27151,7 +27151,7 @@
       <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
     </row>
-    <row r="34" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="17"/>
       <c r="C34" s="10" t="str">
         <f t="shared" si="17"/>
@@ -27240,14 +27240,14 @@
       <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
     </row>
-    <row r="35" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
     </row>
-    <row r="36" spans="1:28" ht="37" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="387" t="s">
         <v>465</v>
       </c>
@@ -27313,7 +27313,7 @@
       <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B37" s="16" t="s">
         <v>378</v>
       </c>
@@ -27372,7 +27372,7 @@
       <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B38" s="38"/>
       <c r="C38" s="11" t="s">
         <v>259</v>
@@ -27435,7 +27435,7 @@
       <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
     </row>
-    <row r="39" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="17"/>
       <c r="C39" s="10" t="s">
         <v>244</v>
@@ -27515,7 +27515,7 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B40" s="38" t="s">
         <v>236</v>
       </c>
@@ -27574,7 +27574,7 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B41" s="38"/>
       <c r="C41" s="11" t="s">
         <v>259</v>
@@ -27637,7 +27637,7 @@
       <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
     </row>
-    <row r="42" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="17"/>
       <c r="C42" s="10" t="s">
         <v>244</v>
@@ -27717,7 +27717,7 @@
       <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B43" s="16" t="s">
         <v>241</v>
       </c>
@@ -27776,7 +27776,7 @@
       <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B44" s="38"/>
       <c r="C44" s="11" t="s">
         <v>259</v>
@@ -27839,7 +27839,7 @@
       <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
     </row>
-    <row r="45" spans="1:28" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="17"/>
       <c r="C45" s="10" t="s">
         <v>244</v>
@@ -27930,22 +27930,22 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="11" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="8.83203125" style="130"/>
-    <col min="4" max="4" width="14.33203125" style="130" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.1640625" style="130" bestFit="1" customWidth="1"/>
-    <col min="7" max="13" width="11.83203125" style="130" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.6640625" style="130" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="11.83203125" style="130" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.1640625" style="130" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.83203125" style="130" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.6640625" style="130" bestFit="1" customWidth="1"/>
-    <col min="21" max="26" width="11.83203125" style="130" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="8.83203125" style="130"/>
+    <col min="1" max="3" width="8.85546875" style="130"/>
+    <col min="4" max="4" width="14.28515625" style="130" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="130" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="11.85546875" style="130" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="130" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="11.85546875" style="130" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" style="130" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.85546875" style="130" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" style="130" bestFit="1" customWidth="1"/>
+    <col min="21" max="26" width="11.85546875" style="130" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="8.85546875" style="130"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="40.700000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="297" t="s">
         <v>368</v>
       </c>
@@ -28048,7 +28048,7 @@
         <v>Other biobased materials</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="299"/>
       <c r="B2" s="130" t="s">
         <v>369</v>
@@ -28149,7 +28149,7 @@
         <v>101327.10855100733</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B3" s="130" t="s">
         <v>272</v>
       </c>
@@ -28249,7 +28249,7 @@
         <v>109333.68255917942</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B4" s="130" t="s">
         <v>273</v>
       </c>
@@ -28349,7 +28349,7 @@
         <v>131027.97462448188</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="130" t="s">
         <v>369</v>
       </c>
@@ -28446,7 +28446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B7" s="130" t="s">
         <v>272</v>
       </c>
@@ -28543,7 +28543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B8" s="130" t="s">
         <v>273</v>
       </c>
@@ -28640,11 +28640,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="T9" s="142"/>
     </row>
-    <row r="10" spans="1:26" ht="12" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:26" ht="37" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="12.75" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:26" ht="36.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="138" t="s">
         <v>233</v>
       </c>
@@ -28694,7 +28694,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B12" s="586" t="s">
         <v>369</v>
       </c>
@@ -28758,7 +28758,7 @@
         <v>101327.10855100733</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B13" s="587"/>
       <c r="C13" s="130" t="s">
         <v>259</v>
@@ -28819,7 +28819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B14" s="587" t="s">
         <v>272</v>
       </c>
@@ -28883,7 +28883,7 @@
         <v>109333.68255917942</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B15" s="587"/>
       <c r="C15" s="130" t="s">
         <v>259</v>
@@ -28944,7 +28944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B16" s="587" t="s">
         <v>273</v>
       </c>
@@ -29008,7 +29008,7 @@
         <v>131027.97462448188</v>
       </c>
     </row>
-    <row r="17" spans="2:19" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B17" s="587"/>
       <c r="C17" s="130" t="s">
         <v>259</v>
@@ -29069,16 +29069,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:19" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:19" x14ac:dyDescent="0.2">
       <c r="S18" s="303"/>
     </row>
-    <row r="19" spans="2:19" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:19" x14ac:dyDescent="0.2">
       <c r="S19" s="303"/>
     </row>
-    <row r="20" spans="2:19" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:19" x14ac:dyDescent="0.2">
       <c r="S20" s="303"/>
     </row>
-    <row r="21" spans="2:19" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:19" x14ac:dyDescent="0.2">
       <c r="S21" s="303"/>
     </row>
   </sheetData>
@@ -29098,14 +29098,14 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:X9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="16" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="8.1640625" customWidth="1"/>
-    <col min="19" max="24" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="16" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="8.140625" customWidth="1"/>
+    <col min="19" max="24" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="48" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="48" x14ac:dyDescent="0.25">
       <c r="A1" s="532" t="s">
         <v>234</v>
       </c>
@@ -29179,7 +29179,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="524" t="s">
         <v>381</v>
       </c>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="524" t="s">
         <v>381</v>
       </c>
@@ -29343,7 +29343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="524" t="s">
         <v>381</v>
       </c>
@@ -29425,7 +29425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="524" t="s">
         <v>380</v>
       </c>
@@ -29507,7 +29507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="524" t="s">
         <v>380</v>
       </c>
@@ -29589,7 +29589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="526" t="s">
         <v>380</v>
       </c>
@@ -29671,7 +29671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C8" s="59"/>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
@@ -29695,7 +29695,7 @@
       <c r="W8" s="59"/>
       <c r="X8" s="59"/>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="X9" s="59"/>
     </row>
   </sheetData>
@@ -29709,33 +29709,33 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:AC282"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5" style="57" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" style="60"/>
+    <col min="1" max="1" width="12.42578125" style="57" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="60"/>
     <col min="3" max="3" width="13" style="61" customWidth="1"/>
-    <col min="4" max="4" width="12.1640625" style="57" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" style="57" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" style="57" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5" style="57" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" style="57" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" style="57" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1640625" style="57" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" style="57" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="9.33203125" style="57" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" style="57" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="57" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" style="57" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="9.28515625" style="57" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9" style="57" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.1640625" style="57" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.140625" style="57" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9" style="57" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9" style="57" customWidth="1"/>
     <col min="20" max="22" width="9" style="57" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="57" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="9" style="57" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.83203125" style="57"/>
-    <col min="27" max="27" width="9.33203125" style="57" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.83203125" style="57"/>
+    <col min="26" max="26" width="8.85546875" style="57"/>
+    <col min="27" max="27" width="9.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.85546875" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="65" customFormat="1" ht="59.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="65" customFormat="1" ht="59.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
         <v>254</v>
       </c>
@@ -29818,7 +29818,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="79" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="72"/>
       <c r="B2" s="69" t="s">
         <v>235</v>
@@ -29917,7 +29917,7 @@
         <v>394374840.31495911</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="68" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" s="68" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="73"/>
       <c r="B3" s="66"/>
       <c r="C3" s="67" t="s">
@@ -30015,7 +30015,7 @@
         <v>97958207.063558996</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="79" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" s="79" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="72"/>
       <c r="B4" s="69" t="s">
         <v>236</v>
@@ -30118,7 +30118,7 @@
         <v>0.5588169546657733</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="68" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" s="68" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="73"/>
       <c r="B5" s="66"/>
       <c r="C5" s="67" t="s">
@@ -30215,7 +30215,7 @@
         <v>71125997.804888263</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="71"/>
       <c r="B6" s="60" t="s">
         <v>241</v>
@@ -30317,7 +30317,7 @@
         <v>0.54713323334737451</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="68" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" s="68" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="73"/>
       <c r="B7" s="66"/>
       <c r="C7" s="67" t="s">
@@ -30414,20 +30414,20 @@
         <v>92552801.04798691</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B9" s="57"/>
       <c r="C9" s="57"/>
       <c r="Q9" s="74"/>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B10" s="57"/>
       <c r="C10" s="57"/>
     </row>
-    <row r="11" spans="1:29" s="306" customFormat="1" ht="11" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:29" s="306" customFormat="1" ht="11" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="1:29" s="306" customFormat="1" ht="11" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="1:29" s="306" customFormat="1" ht="11" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" s="306" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:29" s="306" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:29" s="306" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:29" s="306" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="306"/>
       <c r="B15" s="306"/>
       <c r="C15" s="306"/>
@@ -30458,7 +30458,7 @@
       <c r="AB15" s="306"/>
       <c r="AC15" s="306"/>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="306"/>
       <c r="B16" s="306"/>
       <c r="C16" s="306"/>
@@ -30491,7 +30491,7 @@
       <c r="AB16" s="306"/>
       <c r="AC16" s="306"/>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="306"/>
       <c r="B17" s="306"/>
       <c r="C17" s="306"/>
@@ -30532,7 +30532,7 @@
       <c r="AB17" s="306"/>
       <c r="AC17" s="306"/>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="306"/>
       <c r="B18" s="306"/>
       <c r="C18" s="306"/>
@@ -30576,7 +30576,7 @@
       <c r="AB18" s="306"/>
       <c r="AC18" s="306"/>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="306"/>
       <c r="B19" s="306"/>
       <c r="C19" s="306"/>
@@ -30621,7 +30621,7 @@
       <c r="AB19" s="306"/>
       <c r="AC19" s="306"/>
     </row>
-    <row r="20" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="306"/>
       <c r="B20" s="306"/>
       <c r="C20" s="306"/>
@@ -30666,7 +30666,7 @@
       <c r="AB20" s="306"/>
       <c r="AC20" s="306"/>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="306"/>
       <c r="B21" s="306"/>
       <c r="C21" s="306"/>
@@ -30697,7 +30697,7 @@
       <c r="AB21" s="306"/>
       <c r="AC21" s="306"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="306"/>
       <c r="B22" s="306"/>
       <c r="C22" s="306"/>
@@ -30728,7 +30728,7 @@
       <c r="AB22" s="306"/>
       <c r="AC22" s="306"/>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="306"/>
       <c r="B23" s="306"/>
       <c r="C23" s="306"/>
@@ -30759,7 +30759,7 @@
       <c r="AB23" s="306"/>
       <c r="AC23" s="306"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="306"/>
       <c r="B24" s="306"/>
       <c r="C24" s="306"/>
@@ -30790,7 +30790,7 @@
       <c r="AB24" s="306"/>
       <c r="AC24" s="306"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="306"/>
       <c r="B25" s="306"/>
       <c r="C25" s="306"/>
@@ -30821,7 +30821,7 @@
       <c r="AB25" s="306"/>
       <c r="AC25" s="306"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="306"/>
       <c r="B26" s="306"/>
       <c r="C26" s="306"/>
@@ -30852,7 +30852,7 @@
       <c r="AB26" s="306"/>
       <c r="AC26" s="306"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="306"/>
       <c r="B27" s="306"/>
       <c r="C27" s="306"/>
@@ -30883,7 +30883,7 @@
       <c r="AB27" s="306"/>
       <c r="AC27" s="306"/>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="306"/>
       <c r="B28" s="306"/>
       <c r="C28" s="306"/>
@@ -30914,7 +30914,7 @@
       <c r="AB28" s="306"/>
       <c r="AC28" s="306"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="306"/>
       <c r="B29" s="306"/>
       <c r="C29" s="306"/>
@@ -30945,7 +30945,7 @@
       <c r="AB29" s="306"/>
       <c r="AC29" s="306"/>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B30" s="306"/>
       <c r="C30" s="306"/>
       <c r="D30" s="306"/>
@@ -30961,7 +30961,7 @@
       <c r="N30" s="306"/>
       <c r="O30" s="306"/>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B31" s="306"/>
       <c r="C31" s="306"/>
       <c r="D31" s="306"/>
@@ -30977,7 +30977,7 @@
       <c r="N31" s="306"/>
       <c r="O31" s="306"/>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B32" s="306"/>
       <c r="C32" s="306"/>
       <c r="D32" s="306"/>
@@ -30993,7 +30993,7 @@
       <c r="N32" s="306"/>
       <c r="O32" s="306"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="306"/>
       <c r="C33" s="306"/>
       <c r="D33" s="306"/>
@@ -31009,7 +31009,7 @@
       <c r="N33" s="306"/>
       <c r="O33" s="306"/>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="306"/>
       <c r="C34" s="306"/>
       <c r="D34" s="306"/>
@@ -31025,7 +31025,7 @@
       <c r="N34" s="306"/>
       <c r="O34" s="306"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="306"/>
       <c r="C35" s="306"/>
       <c r="D35" s="306"/>
@@ -31041,7 +31041,7 @@
       <c r="N35" s="306"/>
       <c r="O35" s="306"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B36" s="306"/>
       <c r="C36" s="306"/>
       <c r="D36" s="306"/>
@@ -31057,7 +31057,7 @@
       <c r="N36" s="306"/>
       <c r="O36" s="306"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37" s="306"/>
       <c r="C37" s="306"/>
       <c r="D37" s="306"/>
@@ -31073,284 +31073,284 @@
       <c r="N37" s="306"/>
       <c r="O37" s="306"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38" s="57"/>
       <c r="C38" s="57"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B39" s="57"/>
       <c r="C39" s="57"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40" s="57"/>
       <c r="C40" s="57"/>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" s="57"/>
       <c r="C41" s="57"/>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B42" s="57"/>
       <c r="C42" s="57"/>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="57"/>
       <c r="C43" s="57"/>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44" s="57"/>
       <c r="C44" s="57"/>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="57"/>
       <c r="C45" s="57"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B46" s="57"/>
       <c r="C46" s="57"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="57"/>
       <c r="C47" s="57"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B48" s="57"/>
       <c r="C48" s="57"/>
     </row>
-    <row r="49" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="52" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="54" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="56" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="59" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="60" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="61" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="62" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="63" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="82" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="83" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="84" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="85" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="86" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="87" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="88" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="89" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="90" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="91" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="92" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="93" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="94" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="95" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="96" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="97" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="98" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="99" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="100" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="101" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="102" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="104" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="105" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="106" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="107" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="108" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="109" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="110" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="111" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="112" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="113" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="114" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="115" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="116" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="117" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="118" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="119" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="120" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="121" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="122" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="123" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="124" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="125" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="126" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="127" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="128" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="129" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="130" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="131" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="132" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="133" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="134" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="135" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="136" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="137" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="138" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="139" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="140" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="141" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="142" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="143" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="144" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="145" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="146" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="147" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="148" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="149" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="150" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="151" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="152" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="153" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="154" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="155" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="156" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="157" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="158" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="159" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="160" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="161" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="162" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="163" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="164" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="165" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="166" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="167" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="168" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="169" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="170" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="171" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="172" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="173" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="174" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="175" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="176" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="177" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="178" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="179" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="180" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="181" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="182" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="183" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="184" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="185" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="186" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="187" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="188" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="189" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="190" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="191" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="192" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="193" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="194" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="195" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="196" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="197" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="198" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="199" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="200" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="201" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="202" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="203" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="204" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="205" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="206" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="207" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="208" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="209" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="210" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="211" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="212" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="213" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="214" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="215" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="216" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="217" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="218" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="219" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="220" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="221" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="222" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="223" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="224" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="225" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="226" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="227" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="228" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="229" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="230" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="231" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="232" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="233" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="234" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="235" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="236" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="237" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="238" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="239" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="240" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="241" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="242" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="243" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="244" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="245" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="246" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="247" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="248" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="249" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="250" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="251" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="252" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="253" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="254" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="255" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="256" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="257" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="258" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="259" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="260" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="261" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="262" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="263" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="264" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="265" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="266" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="267" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="268" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="269" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="270" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="271" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="272" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="273" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="274" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="275" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="276" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="277" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="278" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="279" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="280" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="281" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="282" s="57" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="50" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="52" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="54" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="55" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="56" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="57" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="58" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="59" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="61" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="62" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="63" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="64" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="65" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="66" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="68" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="69" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="70" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="71" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="72" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="73" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="74" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="75" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="76" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="77" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="78" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="79" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="95" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="96" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="97" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="98" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="99" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="100" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="101" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="102" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="103" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="104" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="105" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="106" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="107" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="108" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="109" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="110" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="111" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="112" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="113" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="114" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="115" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="116" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="117" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="118" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="119" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="120" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="121" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="122" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="123" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="124" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="125" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="126" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="127" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="128" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="129" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="130" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="131" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="132" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="133" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="134" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="135" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="136" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="137" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="138" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="139" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="140" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="141" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="142" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="143" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="144" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="145" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="146" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="147" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="148" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="149" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="150" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="151" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="152" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="153" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="154" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="155" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="156" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="157" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="158" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="159" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="160" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="161" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="162" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="163" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="164" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="165" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="166" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="167" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="168" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="169" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="170" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="171" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="172" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="173" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="174" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="175" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="176" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="177" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="178" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="179" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="180" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="181" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="182" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="183" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="184" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="185" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="186" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="187" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="188" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="189" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="190" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="191" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="192" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="193" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="194" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="195" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="196" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="197" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="198" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="199" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="200" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="201" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="202" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="203" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="204" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="205" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="206" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="207" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="208" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="209" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="210" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="211" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="212" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="213" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="214" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="215" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="216" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="217" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="218" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="219" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="220" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="221" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="222" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="223" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="224" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="225" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="226" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="227" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="228" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="229" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="230" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="231" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="232" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="233" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="234" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="235" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="236" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="237" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="238" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="239" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="240" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="241" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="242" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="243" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="244" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="245" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="246" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="247" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="248" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="249" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="250" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="251" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="252" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="253" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="254" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="255" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="256" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="257" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="258" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="259" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="260" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="261" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="262" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="263" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="264" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="265" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="266" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="267" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="268" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="269" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="270" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="271" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="272" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="273" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="274" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="275" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="276" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="277" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="278" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="279" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="280" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="281" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="282" s="57" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -31360,9 +31360,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC18034E-7D62-4647-B5A2-E87654E924DA}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>560</v>
       </c>
@@ -31370,7 +31370,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>561</v>
       </c>
@@ -31378,7 +31378,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>562</v>
       </c>
@@ -31386,7 +31386,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>563</v>
       </c>
@@ -31394,7 +31394,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>564</v>
       </c>
@@ -31402,7 +31402,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>565</v>
       </c>
@@ -31410,7 +31410,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>566</v>
       </c>
@@ -31432,20 +31432,20 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:AG58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="38"/>
-    <col min="2" max="3" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="8.85546875" style="38"/>
+    <col min="2" max="3" width="8.85546875" style="1"/>
     <col min="4" max="4" width="15" style="11" customWidth="1"/>
-    <col min="5" max="20" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.33203125" style="1" customWidth="1"/>
-    <col min="22" max="27" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.5" style="1" customWidth="1"/>
-    <col min="29" max="29" width="8.83203125" style="109"/>
-    <col min="30" max="16384" width="8.83203125" style="1"/>
+    <col min="5" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.28515625" style="1" customWidth="1"/>
+    <col min="22" max="27" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.42578125" style="1" customWidth="1"/>
+    <col min="29" max="29" width="8.85546875" style="109"/>
+    <col min="30" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="402" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="402" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="398" t="s">
         <v>385</v>
       </c>
@@ -36072,19 +36072,19 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AO135"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.83203125" customWidth="1"/>
-    <col min="12" max="17" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="21.1640625" customWidth="1"/>
-    <col min="29" max="29" width="7.5" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" customWidth="1"/>
+    <col min="4" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="12" max="17" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="21.140625" customWidth="1"/>
+    <col min="29" max="29" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="93" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" s="93" customFormat="1" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="87" t="s">
         <v>245</v>
       </c>
@@ -36162,7 +36162,7 @@
       </c>
       <c r="Z1" s="131"/>
     </row>
-    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="94"/>
       <c r="B2" s="69" t="s">
         <v>378</v>
@@ -36172,7 +36172,7 @@
       </c>
       <c r="D2" s="80">
         <f>(Demand!E2-Primary_secondary_demand!D3/GHG_Secondary_production!L6)*GHG_Primary_production!I4</f>
-        <v>22904023.228671234</v>
+        <v>22904023.228671178</v>
       </c>
       <c r="E2" s="78">
         <f>Primary_secondary_demand!E2*GHG_Primary_production!I3</f>
@@ -36256,7 +36256,7 @@
       </c>
       <c r="Z2" s="75"/>
     </row>
-    <row r="3" spans="1:40" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="95"/>
       <c r="B3" s="66"/>
       <c r="C3" s="68" t="s">
@@ -36350,7 +36350,7 @@
       </c>
       <c r="Z3" s="75"/>
     </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="94"/>
       <c r="B4" s="69" t="s">
         <v>236</v>
@@ -36446,7 +36446,7 @@
       </c>
       <c r="Z4" s="75"/>
     </row>
-    <row r="5" spans="1:40" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="95"/>
       <c r="B5" s="66"/>
       <c r="C5" s="68" t="s">
@@ -36540,7 +36540,7 @@
       </c>
       <c r="Z5" s="75"/>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A6" s="96"/>
       <c r="B6" s="60" t="s">
         <v>241</v>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="D6" s="84">
         <f>(Demand!E38-Primary_secondary_demand!D7/GHG_Secondary_production!L6)*GHG_Primary_production!I4</f>
-        <v>205583.96352947</v>
+        <v>205583.96352946945</v>
       </c>
       <c r="E6" s="75">
         <f>Primary_secondary_demand!E6*GHG_Primary_production!I3</f>
@@ -36635,7 +36635,7 @@
       </c>
       <c r="Z6" s="75"/>
     </row>
-    <row r="7" spans="1:40" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="95"/>
       <c r="B7" s="66"/>
       <c r="C7" s="68" t="s">
@@ -36729,8 +36729,8 @@
       </c>
       <c r="Z7" s="75"/>
     </row>
-    <row r="8" spans="1:40" s="108" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:40" s="97" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" s="108" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:40" s="97" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="588" t="s">
         <v>251</v>
       </c>
@@ -36755,7 +36755,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:40" s="97" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" s="97" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="590" t="s">
         <v>250</v>
       </c>
@@ -36797,7 +36797,7 @@
       <c r="Y10" s="98"/>
       <c r="Z10" s="98"/>
     </row>
-    <row r="11" spans="1:40" s="108" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:40" s="108" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="109"/>
       <c r="C11" s="109"/>
       <c r="D11" s="109"/>
@@ -36818,7 +36818,7 @@
       <c r="S11" s="109"/>
       <c r="T11" s="109"/>
     </row>
-    <row r="12" spans="1:40" s="115" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:40" s="115" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="112" t="s">
         <v>252</v>
       </c>
@@ -36844,7 +36844,7 @@
       <c r="S12" s="113"/>
       <c r="T12" s="113"/>
     </row>
-    <row r="13" spans="1:40" s="116" customFormat="1" ht="60.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:40" s="116" customFormat="1" ht="60.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="318" t="s">
         <v>413</v>
       </c>
@@ -36895,7 +36895,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="14" spans="1:40" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="580" t="s">
         <v>378</v>
       </c>
@@ -36904,7 +36904,7 @@
       </c>
       <c r="D14" s="80">
         <f>D2*1000</f>
-        <v>22904023228.671234</v>
+        <v>22904023228.671177</v>
       </c>
       <c r="E14" s="78">
         <f t="shared" ref="E14:G14" si="0">E2*1000</f>
@@ -36962,7 +36962,7 @@
       <c r="S14" s="1"/>
       <c r="T14" s="121">
         <f>SUM(D14:K14)+SUM(M14:Q14)</f>
-        <v>66714772528.913216</v>
+        <v>66714772528.913162</v>
       </c>
       <c r="AG14" s="57"/>
       <c r="AH14" s="57"/>
@@ -36973,7 +36973,7 @@
       <c r="AM14" s="57"/>
       <c r="AN14" s="57"/>
     </row>
-    <row r="15" spans="1:40" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:40" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="579"/>
       <c r="C15" s="125" t="s">
         <v>244</v>
@@ -37049,7 +37049,7 @@
       <c r="AM15" s="57"/>
       <c r="AN15" s="57"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.25">
       <c r="B16" s="580" t="s">
         <v>236</v>
       </c>
@@ -37127,7 +37127,7 @@
       <c r="AM16" s="57"/>
       <c r="AN16" s="57"/>
     </row>
-    <row r="17" spans="2:41" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="579"/>
       <c r="C17" s="125" t="s">
         <v>244</v>
@@ -37203,7 +37203,7 @@
       <c r="AM17" s="57"/>
       <c r="AN17" s="57"/>
     </row>
-    <row r="18" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:41" x14ac:dyDescent="0.25">
       <c r="B18" s="580" t="s">
         <v>241</v>
       </c>
@@ -37212,7 +37212,7 @@
       </c>
       <c r="D18" s="80">
         <f t="shared" ref="D18:G18" si="16">D6*1000</f>
-        <v>205583963.52947</v>
+        <v>205583963.52946943</v>
       </c>
       <c r="E18" s="78">
         <f t="shared" si="16"/>
@@ -37270,7 +37270,7 @@
       <c r="S18" s="1"/>
       <c r="T18" s="121">
         <f t="shared" si="11"/>
-        <v>27624326795.075191</v>
+        <v>27624326795.075188</v>
       </c>
       <c r="AG18" s="57"/>
       <c r="AH18" s="57"/>
@@ -37281,7 +37281,7 @@
       <c r="AM18" s="57"/>
       <c r="AN18" s="57"/>
     </row>
-    <row r="19" spans="2:41" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="579"/>
       <c r="C19" s="125" t="s">
         <v>244</v>
@@ -37366,7 +37366,7 @@
       <c r="AM19" s="57"/>
       <c r="AN19" s="57"/>
     </row>
-    <row r="20" spans="2:41" s="108" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:41" s="108" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="110"/>
       <c r="C20" s="110"/>
       <c r="D20" s="109"/>
@@ -37408,7 +37408,7 @@
       <c r="AN20" s="57"/>
       <c r="AO20"/>
     </row>
-    <row r="21" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:41" x14ac:dyDescent="0.25">
       <c r="B21" s="105" t="s">
         <v>378</v>
       </c>
@@ -37417,7 +37417,7 @@
       </c>
       <c r="D21" s="78">
         <f>D14+D15</f>
-        <v>44594541523.112488</v>
+        <v>44594541523.112434</v>
       </c>
       <c r="E21" s="78">
         <f t="shared" ref="E21:Q21" si="20">E14+E15</f>
@@ -37475,7 +37475,7 @@
       <c r="S21" s="1"/>
       <c r="T21" s="121">
         <f>SUM(D21:K21)+SUM(M21:Q21)</f>
-        <v>103526606338.08435</v>
+        <v>103526606338.08432</v>
       </c>
       <c r="X21" s="57"/>
       <c r="Y21" s="57"/>
@@ -37495,7 +37495,7 @@
       <c r="AM21" s="57"/>
       <c r="AN21" s="57"/>
     </row>
-    <row r="22" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:41" x14ac:dyDescent="0.25">
       <c r="B22" s="107" t="s">
         <v>236</v>
       </c>
@@ -37581,7 +37581,7 @@
       <c r="AM22" s="57"/>
       <c r="AN22" s="57"/>
     </row>
-    <row r="23" spans="2:41" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:41" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="106" t="s">
         <v>241</v>
       </c>
@@ -37668,7 +37668,7 @@
       <c r="AM23" s="57"/>
       <c r="AN23" s="57"/>
     </row>
-    <row r="24" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:41" x14ac:dyDescent="0.25">
       <c r="Y24" s="57"/>
       <c r="Z24" s="57"/>
       <c r="AA24" s="57"/>
@@ -37686,7 +37686,7 @@
       <c r="AM24" s="57"/>
       <c r="AN24" s="57"/>
     </row>
-    <row r="25" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:41" x14ac:dyDescent="0.25">
       <c r="L25" s="319" t="s">
         <v>436</v>
       </c>
@@ -37708,7 +37708,7 @@
       <c r="AM25" s="57"/>
       <c r="AN25" s="57"/>
     </row>
-    <row r="26" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:41" x14ac:dyDescent="0.25">
       <c r="X26" s="57"/>
       <c r="Y26" s="57"/>
       <c r="Z26" s="57"/>
@@ -37727,7 +37727,7 @@
       <c r="AM26" s="57"/>
       <c r="AN26" s="57"/>
     </row>
-    <row r="27" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:41" x14ac:dyDescent="0.25">
       <c r="X27" s="57"/>
       <c r="Y27" s="57"/>
       <c r="Z27" s="57"/>
@@ -37746,7 +37746,7 @@
       <c r="AM27" s="57"/>
       <c r="AN27" s="57"/>
     </row>
-    <row r="28" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:41" x14ac:dyDescent="0.25">
       <c r="X28" s="57"/>
       <c r="Y28" s="57"/>
       <c r="Z28" s="57"/>
@@ -37765,7 +37765,7 @@
       <c r="AM28" s="57"/>
       <c r="AN28" s="57"/>
     </row>
-    <row r="29" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:41" x14ac:dyDescent="0.25">
       <c r="X29" s="57"/>
       <c r="Y29" s="57"/>
       <c r="Z29" s="57"/>
@@ -37784,637 +37784,637 @@
       <c r="AM29" s="57"/>
       <c r="AN29" s="57"/>
     </row>
-    <row r="30" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:41" x14ac:dyDescent="0.25">
       <c r="X30" s="57"/>
       <c r="Y30" s="57"/>
       <c r="Z30" s="57"/>
       <c r="AA30" s="57"/>
     </row>
-    <row r="31" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:41" x14ac:dyDescent="0.25">
       <c r="X31" s="57"/>
       <c r="Y31" s="57"/>
       <c r="Z31" s="57"/>
       <c r="AA31" s="57"/>
     </row>
-    <row r="32" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:41" x14ac:dyDescent="0.25">
       <c r="X32" s="57"/>
       <c r="Y32" s="57"/>
       <c r="Z32" s="57"/>
       <c r="AA32" s="57"/>
     </row>
-    <row r="33" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X33" s="57"/>
       <c r="Y33" s="57"/>
       <c r="Z33" s="57"/>
       <c r="AA33" s="57"/>
     </row>
-    <row r="34" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X34" s="57"/>
       <c r="Y34" s="57"/>
       <c r="Z34" s="57"/>
       <c r="AA34" s="57"/>
     </row>
-    <row r="35" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X35" s="57"/>
       <c r="Y35" s="57"/>
       <c r="Z35" s="57"/>
       <c r="AA35" s="57"/>
     </row>
-    <row r="36" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X36" s="57"/>
       <c r="Y36" s="57"/>
       <c r="Z36" s="57"/>
       <c r="AA36" s="57"/>
     </row>
-    <row r="37" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X37" s="57"/>
       <c r="Y37" s="57"/>
       <c r="Z37" s="57"/>
       <c r="AA37" s="57"/>
     </row>
-    <row r="38" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X38" s="57"/>
       <c r="Y38" s="57"/>
       <c r="Z38" s="57"/>
       <c r="AA38" s="57"/>
     </row>
-    <row r="39" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X39" s="57"/>
       <c r="Y39" s="57"/>
       <c r="Z39" s="57"/>
       <c r="AA39" s="57"/>
     </row>
-    <row r="40" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X40" s="57"/>
       <c r="Y40" s="57"/>
       <c r="Z40" s="57"/>
       <c r="AA40" s="57"/>
     </row>
-    <row r="41" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X41" s="57"/>
       <c r="Y41" s="57"/>
       <c r="Z41" s="57"/>
       <c r="AA41" s="57"/>
     </row>
-    <row r="42" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X42" s="57"/>
       <c r="Y42" s="57"/>
       <c r="Z42" s="57"/>
       <c r="AA42" s="57"/>
     </row>
-    <row r="43" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X43" s="57"/>
       <c r="Y43" s="57"/>
       <c r="Z43" s="57"/>
       <c r="AA43" s="57"/>
     </row>
-    <row r="44" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X44" s="57"/>
       <c r="Y44" s="57"/>
       <c r="Z44" s="57"/>
       <c r="AA44" s="57"/>
     </row>
-    <row r="45" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X45" s="57"/>
       <c r="Y45" s="57"/>
       <c r="Z45" s="57"/>
       <c r="AA45" s="57"/>
     </row>
-    <row r="46" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X46" s="57"/>
       <c r="Y46" s="57"/>
       <c r="Z46" s="57"/>
       <c r="AA46" s="57"/>
     </row>
-    <row r="47" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X47" s="57"/>
       <c r="Y47" s="57"/>
       <c r="Z47" s="57"/>
       <c r="AA47" s="57"/>
     </row>
-    <row r="48" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X48" s="57"/>
       <c r="Y48" s="57"/>
       <c r="Z48" s="57"/>
       <c r="AA48" s="57"/>
     </row>
-    <row r="49" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X49" s="57"/>
       <c r="Y49" s="57"/>
       <c r="Z49" s="57"/>
       <c r="AA49" s="57"/>
     </row>
-    <row r="50" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X50" s="57"/>
       <c r="Y50" s="57"/>
       <c r="Z50" s="57"/>
       <c r="AA50" s="57"/>
     </row>
-    <row r="51" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="51" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X51" s="57"/>
       <c r="Y51" s="57"/>
       <c r="Z51" s="57"/>
       <c r="AA51" s="57"/>
     </row>
-    <row r="52" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="52" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X52" s="57"/>
       <c r="Y52" s="57"/>
       <c r="Z52" s="57"/>
       <c r="AA52" s="57"/>
     </row>
-    <row r="53" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X53" s="57"/>
       <c r="Y53" s="57"/>
       <c r="Z53" s="57"/>
       <c r="AA53" s="57"/>
     </row>
-    <row r="54" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="54" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X54" s="57"/>
       <c r="Y54" s="57"/>
       <c r="Z54" s="57"/>
       <c r="AA54" s="57"/>
     </row>
-    <row r="55" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X55" s="57"/>
       <c r="Y55" s="57"/>
       <c r="Z55" s="57"/>
       <c r="AA55" s="57"/>
     </row>
-    <row r="56" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="56" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X56" s="57"/>
       <c r="Y56" s="57"/>
       <c r="Z56" s="57"/>
       <c r="AA56" s="57"/>
     </row>
-    <row r="57" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="57" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X57" s="57"/>
       <c r="Y57" s="57"/>
       <c r="Z57" s="57"/>
       <c r="AA57" s="57"/>
     </row>
-    <row r="58" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X58" s="57"/>
       <c r="Y58" s="57"/>
       <c r="Z58" s="57"/>
       <c r="AA58" s="57"/>
     </row>
-    <row r="59" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X59" s="57"/>
       <c r="Y59" s="57"/>
       <c r="Z59" s="57"/>
       <c r="AA59" s="57"/>
     </row>
-    <row r="60" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X60" s="57"/>
       <c r="Y60" s="57"/>
       <c r="Z60" s="57"/>
       <c r="AA60" s="57"/>
     </row>
-    <row r="61" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X61" s="57"/>
       <c r="Y61" s="57"/>
       <c r="Z61" s="57"/>
       <c r="AA61" s="57"/>
     </row>
-    <row r="62" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X62" s="57"/>
       <c r="Y62" s="57"/>
       <c r="Z62" s="57"/>
       <c r="AA62" s="57"/>
     </row>
-    <row r="63" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X63" s="57"/>
       <c r="Y63" s="57"/>
       <c r="Z63" s="57"/>
       <c r="AA63" s="57"/>
     </row>
-    <row r="64" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="64" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X64" s="57"/>
       <c r="Y64" s="57"/>
       <c r="Z64" s="57"/>
       <c r="AA64" s="57"/>
     </row>
-    <row r="65" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="65" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X65" s="57"/>
       <c r="Y65" s="57"/>
       <c r="Z65" s="57"/>
       <c r="AA65" s="57"/>
     </row>
-    <row r="66" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="66" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X66" s="57"/>
       <c r="Y66" s="57"/>
       <c r="Z66" s="57"/>
       <c r="AA66" s="57"/>
     </row>
-    <row r="67" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X67" s="57"/>
       <c r="Y67" s="57"/>
       <c r="Z67" s="57"/>
       <c r="AA67" s="57"/>
     </row>
-    <row r="68" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="68" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X68" s="57"/>
       <c r="Y68" s="57"/>
       <c r="Z68" s="57"/>
       <c r="AA68" s="57"/>
     </row>
-    <row r="69" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="69" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X69" s="57"/>
       <c r="Y69" s="57"/>
       <c r="Z69" s="57"/>
       <c r="AA69" s="57"/>
     </row>
-    <row r="70" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="70" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X70" s="57"/>
       <c r="Y70" s="57"/>
       <c r="Z70" s="57"/>
       <c r="AA70" s="57"/>
     </row>
-    <row r="71" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="71" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X71" s="57"/>
       <c r="Y71" s="57"/>
       <c r="Z71" s="57"/>
       <c r="AA71" s="57"/>
     </row>
-    <row r="72" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="72" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X72" s="57"/>
       <c r="Y72" s="57"/>
       <c r="Z72" s="57"/>
       <c r="AA72" s="57"/>
     </row>
-    <row r="73" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X73" s="57"/>
       <c r="Y73" s="57"/>
       <c r="Z73" s="57"/>
       <c r="AA73" s="57"/>
     </row>
-    <row r="74" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="74" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X74" s="57"/>
       <c r="Y74" s="57"/>
       <c r="Z74" s="57"/>
       <c r="AA74" s="57"/>
     </row>
-    <row r="75" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="75" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X75" s="57"/>
       <c r="Y75" s="57"/>
       <c r="Z75" s="57"/>
       <c r="AA75" s="57"/>
     </row>
-    <row r="76" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="76" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X76" s="57"/>
       <c r="Y76" s="57"/>
       <c r="Z76" s="57"/>
       <c r="AA76" s="57"/>
     </row>
-    <row r="77" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X77" s="57"/>
       <c r="Y77" s="57"/>
       <c r="Z77" s="57"/>
       <c r="AA77" s="57"/>
     </row>
-    <row r="78" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="78" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X78" s="57"/>
       <c r="Y78" s="57"/>
       <c r="Z78" s="57"/>
       <c r="AA78" s="57"/>
     </row>
-    <row r="79" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="79" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X79" s="57"/>
       <c r="Y79" s="57"/>
       <c r="Z79" s="57"/>
       <c r="AA79" s="57"/>
     </row>
-    <row r="80" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X80" s="57"/>
       <c r="Y80" s="57"/>
       <c r="Z80" s="57"/>
       <c r="AA80" s="57"/>
     </row>
-    <row r="81" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X81" s="57"/>
       <c r="Y81" s="57"/>
       <c r="Z81" s="57"/>
       <c r="AA81" s="57"/>
     </row>
-    <row r="82" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X82" s="57"/>
       <c r="Y82" s="57"/>
       <c r="Z82" s="57"/>
       <c r="AA82" s="57"/>
     </row>
-    <row r="83" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="83" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X83" s="57"/>
       <c r="Y83" s="57"/>
       <c r="Z83" s="57"/>
       <c r="AA83" s="57"/>
     </row>
-    <row r="84" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X84" s="57"/>
       <c r="Y84" s="57"/>
       <c r="Z84" s="57"/>
       <c r="AA84" s="57"/>
     </row>
-    <row r="85" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="85" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X85" s="57"/>
       <c r="Y85" s="57"/>
       <c r="Z85" s="57"/>
       <c r="AA85" s="57"/>
     </row>
-    <row r="86" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="86" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X86" s="57"/>
       <c r="Y86" s="57"/>
       <c r="Z86" s="57"/>
       <c r="AA86" s="57"/>
     </row>
-    <row r="87" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="87" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X87" s="57"/>
       <c r="Y87" s="57"/>
       <c r="Z87" s="57"/>
       <c r="AA87" s="57"/>
     </row>
-    <row r="88" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="88" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X88" s="57"/>
       <c r="Y88" s="57"/>
       <c r="Z88" s="57"/>
       <c r="AA88" s="57"/>
     </row>
-    <row r="89" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="89" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X89" s="57"/>
       <c r="Y89" s="57"/>
       <c r="Z89" s="57"/>
       <c r="AA89" s="57"/>
     </row>
-    <row r="90" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X90" s="57"/>
       <c r="Y90" s="57"/>
       <c r="Z90" s="57"/>
       <c r="AA90" s="57"/>
     </row>
-    <row r="91" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="91" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X91" s="57"/>
       <c r="Y91" s="57"/>
       <c r="Z91" s="57"/>
       <c r="AA91" s="57"/>
     </row>
-    <row r="92" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X92" s="57"/>
       <c r="Y92" s="57"/>
       <c r="Z92" s="57"/>
       <c r="AA92" s="57"/>
     </row>
-    <row r="93" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="93" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X93" s="57"/>
       <c r="Y93" s="57"/>
       <c r="Z93" s="57"/>
       <c r="AA93" s="57"/>
     </row>
-    <row r="94" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="94" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X94" s="57"/>
       <c r="Y94" s="57"/>
       <c r="Z94" s="57"/>
       <c r="AA94" s="57"/>
     </row>
-    <row r="95" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X95" s="57"/>
       <c r="Y95" s="57"/>
       <c r="Z95" s="57"/>
       <c r="AA95" s="57"/>
     </row>
-    <row r="96" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="96" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X96" s="57"/>
       <c r="Y96" s="57"/>
       <c r="Z96" s="57"/>
       <c r="AA96" s="57"/>
     </row>
-    <row r="97" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X97" s="57"/>
       <c r="Y97" s="57"/>
       <c r="Z97" s="57"/>
       <c r="AA97" s="57"/>
     </row>
-    <row r="98" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="98" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X98" s="57"/>
       <c r="Y98" s="57"/>
       <c r="Z98" s="57"/>
       <c r="AA98" s="57"/>
     </row>
-    <row r="99" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="99" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X99" s="57"/>
       <c r="Y99" s="57"/>
       <c r="Z99" s="57"/>
       <c r="AA99" s="57"/>
     </row>
-    <row r="100" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="100" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X100" s="57"/>
       <c r="Y100" s="57"/>
       <c r="Z100" s="57"/>
       <c r="AA100" s="57"/>
     </row>
-    <row r="101" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X101" s="57"/>
       <c r="Y101" s="57"/>
       <c r="Z101" s="57"/>
       <c r="AA101" s="57"/>
     </row>
-    <row r="102" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X102" s="57"/>
       <c r="Y102" s="57"/>
       <c r="Z102" s="57"/>
       <c r="AA102" s="57"/>
     </row>
-    <row r="103" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="103" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X103" s="57"/>
       <c r="Y103" s="57"/>
       <c r="Z103" s="57"/>
       <c r="AA103" s="57"/>
     </row>
-    <row r="104" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="104" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X104" s="57"/>
       <c r="Y104" s="57"/>
       <c r="Z104" s="57"/>
       <c r="AA104" s="57"/>
     </row>
-    <row r="105" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="105" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X105" s="57"/>
       <c r="Y105" s="57"/>
       <c r="Z105" s="57"/>
       <c r="AA105" s="57"/>
     </row>
-    <row r="106" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="106" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X106" s="57"/>
       <c r="Y106" s="57"/>
       <c r="Z106" s="57"/>
       <c r="AA106" s="57"/>
     </row>
-    <row r="107" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="107" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X107" s="57"/>
       <c r="Y107" s="57"/>
       <c r="Z107" s="57"/>
       <c r="AA107" s="57"/>
     </row>
-    <row r="108" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="108" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X108" s="57"/>
       <c r="Y108" s="57"/>
       <c r="Z108" s="57"/>
       <c r="AA108" s="57"/>
     </row>
-    <row r="109" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="109" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X109" s="57"/>
       <c r="Y109" s="57"/>
       <c r="Z109" s="57"/>
       <c r="AA109" s="57"/>
     </row>
-    <row r="110" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="110" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X110" s="57"/>
       <c r="Y110" s="57"/>
       <c r="Z110" s="57"/>
       <c r="AA110" s="57"/>
     </row>
-    <row r="111" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="111" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X111" s="57"/>
       <c r="Y111" s="57"/>
       <c r="Z111" s="57"/>
       <c r="AA111" s="57"/>
     </row>
-    <row r="112" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="112" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X112" s="57"/>
       <c r="Y112" s="57"/>
       <c r="Z112" s="57"/>
       <c r="AA112" s="57"/>
     </row>
-    <row r="113" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="113" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X113" s="57"/>
       <c r="Y113" s="57"/>
       <c r="Z113" s="57"/>
       <c r="AA113" s="57"/>
     </row>
-    <row r="114" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="114" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X114" s="57"/>
       <c r="Y114" s="57"/>
       <c r="Z114" s="57"/>
       <c r="AA114" s="57"/>
     </row>
-    <row r="115" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="115" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X115" s="57"/>
       <c r="Y115" s="57"/>
       <c r="Z115" s="57"/>
       <c r="AA115" s="57"/>
     </row>
-    <row r="116" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="116" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X116" s="57"/>
       <c r="Y116" s="57"/>
       <c r="Z116" s="57"/>
       <c r="AA116" s="57"/>
     </row>
-    <row r="117" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="117" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X117" s="57"/>
       <c r="Y117" s="57"/>
       <c r="Z117" s="57"/>
       <c r="AA117" s="57"/>
     </row>
-    <row r="118" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="118" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X118" s="57"/>
       <c r="Y118" s="57"/>
       <c r="Z118" s="57"/>
       <c r="AA118" s="57"/>
     </row>
-    <row r="119" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="119" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X119" s="57"/>
       <c r="Y119" s="57"/>
       <c r="Z119" s="57"/>
       <c r="AA119" s="57"/>
     </row>
-    <row r="120" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="120" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X120" s="57"/>
       <c r="Y120" s="57"/>
       <c r="Z120" s="57"/>
       <c r="AA120" s="57"/>
     </row>
-    <row r="121" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="121" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X121" s="57"/>
       <c r="Y121" s="57"/>
       <c r="Z121" s="57"/>
       <c r="AA121" s="57"/>
     </row>
-    <row r="122" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="122" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X122" s="57"/>
       <c r="Y122" s="57"/>
       <c r="Z122" s="57"/>
       <c r="AA122" s="57"/>
     </row>
-    <row r="123" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="123" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X123" s="57"/>
       <c r="Y123" s="57"/>
       <c r="Z123" s="57"/>
       <c r="AA123" s="57"/>
     </row>
-    <row r="124" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="124" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X124" s="57"/>
       <c r="Y124" s="57"/>
       <c r="Z124" s="57"/>
       <c r="AA124" s="57"/>
     </row>
-    <row r="125" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="125" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X125" s="57"/>
       <c r="Y125" s="57"/>
       <c r="Z125" s="57"/>
       <c r="AA125" s="57"/>
     </row>
-    <row r="126" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="126" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X126" s="57"/>
       <c r="Y126" s="57"/>
       <c r="Z126" s="57"/>
       <c r="AA126" s="57"/>
     </row>
-    <row r="127" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="127" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X127" s="57"/>
       <c r="Y127" s="57"/>
       <c r="Z127" s="57"/>
       <c r="AA127" s="57"/>
     </row>
-    <row r="128" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="128" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X128" s="57"/>
       <c r="Y128" s="57"/>
       <c r="Z128" s="57"/>
       <c r="AA128" s="57"/>
     </row>
-    <row r="129" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="129" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X129" s="57"/>
       <c r="Y129" s="57"/>
       <c r="Z129" s="57"/>
       <c r="AA129" s="57"/>
     </row>
-    <row r="130" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="130" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X130" s="57"/>
       <c r="Y130" s="57"/>
       <c r="Z130" s="57"/>
       <c r="AA130" s="57"/>
     </row>
-    <row r="131" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="131" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X131" s="57"/>
       <c r="Y131" s="57"/>
       <c r="Z131" s="57"/>
       <c r="AA131" s="57"/>
     </row>
-    <row r="132" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="132" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X132" s="57"/>
       <c r="Y132" s="57"/>
       <c r="Z132" s="57"/>
       <c r="AA132" s="57"/>
     </row>
-    <row r="133" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="133" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X133" s="57"/>
       <c r="Y133" s="57"/>
       <c r="Z133" s="57"/>
       <c r="AA133" s="57"/>
     </row>
-    <row r="134" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="134" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X134" s="57"/>
       <c r="Y134" s="57"/>
       <c r="Z134" s="57"/>
       <c r="AA134" s="57"/>
     </row>
-    <row r="135" spans="24:27" x14ac:dyDescent="0.2">
+    <row r="135" spans="24:27" x14ac:dyDescent="0.25">
       <c r="X135" s="57"/>
       <c r="Y135" s="57"/>
       <c r="Z135" s="57"/>
@@ -38439,15 +38439,15 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:P17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="6" max="6" width="3.1640625" customWidth="1"/>
-    <col min="10" max="10" width="2.33203125" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="3.140625" customWidth="1"/>
+    <col min="10" max="10" width="2.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="32.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="32.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="57"/>
       <c r="B1" s="57"/>
       <c r="C1" s="591" t="s">
@@ -38467,7 +38467,7 @@
       <c r="L1" s="598"/>
       <c r="M1" s="599"/>
     </row>
-    <row r="2" spans="1:16" ht="76" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="476" t="s">
         <v>188</v>
       </c>
@@ -38504,7 +38504,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="467" t="s">
         <v>86</v>
       </c>
@@ -38547,7 +38547,7 @@
         <v>5.2477600242568923E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="467" t="s">
         <v>177</v>
       </c>
@@ -38590,7 +38590,7 @@
         <v>1.8825720644063135E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="467" t="s">
         <v>88</v>
       </c>
@@ -38633,7 +38633,7 @@
         <v>1.0455251418342318E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="467" t="s">
         <v>89</v>
       </c>
@@ -38652,7 +38652,7 @@
       <c r="L6" s="471"/>
       <c r="M6" s="472"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="467" t="s">
         <v>91</v>
       </c>
@@ -38671,7 +38671,7 @@
       <c r="L7" s="471"/>
       <c r="M7" s="472"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="467" t="s">
         <v>92</v>
       </c>
@@ -38714,7 +38714,7 @@
         <v>2.352369659215996E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="467" t="s">
         <v>167</v>
       </c>
@@ -38760,7 +38760,7 @@
       <c r="O9" s="59"/>
       <c r="P9" s="59"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="467" t="s">
         <v>94</v>
       </c>
@@ -38803,7 +38803,7 @@
         <v>1.2298318582843343E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="467" t="s">
         <v>173</v>
       </c>
@@ -38822,7 +38822,7 @@
       <c r="L11" s="471"/>
       <c r="M11" s="472"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="467" t="s">
         <v>178</v>
       </c>
@@ -38865,7 +38865,7 @@
         <v>2.1452813772139161E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="467" t="s">
         <v>87</v>
       </c>
@@ -38908,7 +38908,7 @@
         <v>1.4653488434762444E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="467" t="s">
         <v>379</v>
       </c>
@@ -38951,7 +38951,7 @@
         <v>5.3823788826330233E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="467" t="s">
         <v>110</v>
       </c>
@@ -38970,7 +38970,7 @@
       <c r="L15" s="471"/>
       <c r="M15" s="472"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="467" t="s">
         <v>180</v>
       </c>
@@ -39013,7 +39013,7 @@
         <v>6.260424338143867E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="477" t="s">
         <v>191</v>
       </c>
@@ -39133,31 +39133,31 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AF122"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="28.83203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.1640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="30.83203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" style="1" customWidth="1"/>
-    <col min="9" max="10" width="21.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.1640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" style="1"/>
-    <col min="13" max="13" width="19.83203125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="19.33203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="23.1640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="18.6640625" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="23.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33.140625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="30.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.7109375" style="1" customWidth="1"/>
+    <col min="9" max="10" width="21.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.85546875" style="1"/>
+    <col min="13" max="13" width="19.85546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="23.140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="311" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="130" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" s="130" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="309" t="s">
         <v>415</v>
       </c>
@@ -39171,7 +39171,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="130" customFormat="1" ht="14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" s="130" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="309" t="s">
         <v>416</v>
       </c>
@@ -39185,13 +39185,13 @@
         <v>357</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="202" customFormat="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" s="202" customFormat="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="310" t="s">
         <v>438</v>
       </c>
       <c r="C4" s="248"/>
     </row>
-    <row r="5" spans="1:17" ht="42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A5" s="256"/>
       <c r="B5" s="254" t="s">
         <v>360</v>
@@ -39224,7 +39224,7 @@
       <c r="P5" s="4"/>
       <c r="Q5" s="37"/>
     </row>
-    <row r="6" spans="1:17" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="223"/>
       <c r="D6" s="204"/>
       <c r="G6" s="189"/>
@@ -39244,7 +39244,7 @@
       <c r="M6" s="38"/>
       <c r="Q6" s="11"/>
     </row>
-    <row r="7" spans="1:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B7" s="223"/>
       <c r="C7" s="221" t="str">
         <f>Primary_secondary_demand!R17</f>
@@ -39415,7 +39415,7 @@
         <v>109017313.73759669</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="225"/>
       <c r="C10" s="225" t="str">
         <f>Primary_secondary_demand!R20</f>
@@ -39473,7 +39473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="4" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="227"/>
       <c r="B11" s="205" t="s">
         <v>303</v>
@@ -39496,7 +39496,7 @@
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A12" s="223">
         <v>1</v>
       </c>
@@ -39516,7 +39516,7 @@
       <c r="L12" s="213"/>
       <c r="M12" s="37"/>
     </row>
-    <row r="13" spans="1:17" ht="28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A13" s="228"/>
       <c r="B13" s="1">
         <v>0.83581168911900605</v>
@@ -39541,7 +39541,7 @@
         <v>1.2720944743433795</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="228"/>
       <c r="B14" s="209"/>
       <c r="C14" s="2">
@@ -39567,7 +39567,7 @@
         <v>0.3180236185858441</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="228"/>
       <c r="B15" s="209"/>
       <c r="C15" s="210"/>
@@ -39590,7 +39590,7 @@
       <c r="L15" s="5"/>
       <c r="M15" s="10"/>
     </row>
-    <row r="16" spans="1:17" ht="65.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="65.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="600"/>
       <c r="B16" s="601"/>
       <c r="C16" s="601"/>
@@ -39619,7 +39619,7 @@
         <v>1.5901180929292236</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="228"/>
       <c r="B17" s="209"/>
       <c r="C17" s="210"/>
@@ -39640,7 +39640,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A18" s="228"/>
       <c r="B18" s="209"/>
       <c r="C18" s="210"/>
@@ -39661,7 +39661,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A19" s="228"/>
       <c r="B19" s="209"/>
       <c r="C19" s="210"/>
@@ -39682,7 +39682,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A20" s="228"/>
       <c r="B20" s="1">
         <v>0.20895292227975101</v>
@@ -39700,7 +39700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="228"/>
       <c r="B21" s="210"/>
       <c r="C21" s="2">
@@ -39719,7 +39719,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="42" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A22" s="228"/>
       <c r="B22" s="210"/>
       <c r="C22" s="210"/>
@@ -39736,7 +39736,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A23" s="228"/>
       <c r="B23" s="210"/>
       <c r="C23" s="210"/>
@@ -39757,7 +39757,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A24" s="228"/>
       <c r="B24" s="210"/>
       <c r="C24" s="210"/>
@@ -39778,7 +39778,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A25" s="228"/>
       <c r="B25" s="210"/>
       <c r="C25" s="210"/>
@@ -39799,7 +39799,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="5" customFormat="1" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" s="5" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="229"/>
       <c r="B26" s="211"/>
       <c r="C26" s="211"/>
@@ -39820,7 +39820,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" s="4" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="227"/>
       <c r="B27" s="205" t="s">
         <v>321</v>
@@ -39835,7 +39835,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A28" s="223">
         <v>1</v>
       </c>
@@ -39851,7 +39851,7 @@
       <c r="L28" s="213"/>
       <c r="M28" s="37"/>
     </row>
-    <row r="29" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="228"/>
       <c r="B29" s="2">
         <v>0.21619113319396999</v>
@@ -39878,7 +39878,7 @@
         <v>0.34642066771158142</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="228"/>
       <c r="B30" s="210"/>
       <c r="C30" s="2">
@@ -39906,7 +39906,7 @@
         <v>1.3856826708463275</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="228"/>
       <c r="B31" s="210"/>
       <c r="C31" s="210"/>
@@ -39928,7 +39928,7 @@
       <c r="L31" s="5"/>
       <c r="M31" s="10"/>
     </row>
-    <row r="32" spans="1:13" ht="26.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="26.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="228"/>
       <c r="B32" s="210"/>
       <c r="C32" s="210"/>
@@ -39953,7 +39953,7 @@
         <v>1.7321033385579088</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A33" s="228"/>
       <c r="B33" s="210"/>
       <c r="C33" s="210"/>
@@ -39970,7 +39970,7 @@
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A34" s="228"/>
       <c r="B34" s="210"/>
       <c r="C34" s="210"/>
@@ -39987,7 +39987,7 @@
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A35" s="228"/>
       <c r="B35" s="2">
         <v>0.86476453277588095</v>
@@ -40007,7 +40007,7 @@
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="228"/>
       <c r="B36" s="210"/>
       <c r="C36" s="2">
@@ -40028,7 +40028,7 @@
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:13" ht="42" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A37" s="228"/>
       <c r="B37" s="210"/>
       <c r="C37" s="210"/>
@@ -40049,7 +40049,7 @@
       </c>
       <c r="I37" s="2"/>
     </row>
-    <row r="38" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A38" s="228"/>
       <c r="B38" s="210"/>
       <c r="C38" s="210"/>
@@ -40070,7 +40070,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A39" s="228"/>
       <c r="B39" s="210"/>
       <c r="C39" s="210"/>
@@ -40091,7 +40091,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="5" customFormat="1" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" s="5" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="229"/>
       <c r="B40" s="211"/>
       <c r="C40" s="211"/>
@@ -40112,7 +40112,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" s="4" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="227"/>
       <c r="B41" s="205" t="s">
         <v>322</v>
@@ -40127,7 +40127,7 @@
       <c r="H41" s="12"/>
       <c r="I41" s="12"/>
     </row>
-    <row r="42" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A42" s="223">
         <v>1</v>
       </c>
@@ -40147,7 +40147,7 @@
       <c r="L42" s="213"/>
       <c r="M42" s="216"/>
     </row>
-    <row r="43" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A43" s="228"/>
       <c r="B43" s="2">
         <v>0.83763985582732503</v>
@@ -40172,7 +40172,7 @@
         <v>1.3422185908854301</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="228"/>
       <c r="B44" s="210"/>
       <c r="C44" s="2">
@@ -40201,7 +40201,7 @@
         <v>0.33555464772135712</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="228"/>
       <c r="B45" s="210"/>
       <c r="C45" s="210"/>
@@ -40224,7 +40224,7 @@
       <c r="L45" s="5"/>
       <c r="M45" s="217"/>
     </row>
-    <row r="46" spans="1:13" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A46" s="228"/>
       <c r="B46" s="210"/>
       <c r="C46" s="210"/>
@@ -40253,7 +40253,7 @@
         <v>1.6777732386067872</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A47" s="228"/>
       <c r="B47" s="210"/>
       <c r="C47" s="210"/>
@@ -40274,7 +40274,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A48" s="228"/>
       <c r="B48" s="210"/>
       <c r="C48" s="210"/>
@@ -40295,7 +40295,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A49" s="228"/>
       <c r="B49" s="2">
         <v>0.20940996395683101</v>
@@ -40313,7 +40313,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="228"/>
       <c r="B50" s="210"/>
       <c r="C50" s="2">
@@ -40332,7 +40332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="42" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A51" s="228"/>
       <c r="B51" s="210"/>
       <c r="C51" s="210"/>
@@ -40352,7 +40352,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A52" s="228"/>
       <c r="B52" s="210"/>
       <c r="C52" s="210"/>
@@ -40373,7 +40373,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A53" s="228"/>
       <c r="B53" s="210"/>
       <c r="C53" s="210"/>
@@ -40394,7 +40394,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="5" customFormat="1" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" s="5" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A54" s="229"/>
       <c r="B54" s="211"/>
       <c r="C54" s="211"/>
@@ -40415,7 +40415,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" s="4" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A55" s="227"/>
       <c r="B55" s="205" t="s">
         <v>347</v>
@@ -40428,7 +40428,7 @@
       <c r="F55" s="12"/>
       <c r="G55" s="12"/>
     </row>
-    <row r="56" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A56" s="223">
         <v>1</v>
       </c>
@@ -40448,7 +40448,7 @@
       <c r="L56" s="213"/>
       <c r="M56" s="216"/>
     </row>
-    <row r="57" spans="1:13" ht="28" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A57" s="228"/>
       <c r="B57" s="2">
         <v>0.84448439952211296</v>
@@ -40470,7 +40470,7 @@
         <v>1.3411765839684058</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="228"/>
       <c r="B58" s="210"/>
       <c r="C58" s="2">
@@ -40496,7 +40496,7 @@
         <v>5.7421919282035265E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="42" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A59" s="228"/>
       <c r="B59" s="210"/>
       <c r="C59" s="210"/>
@@ -40527,7 +40527,7 @@
         <v>0.55587802902068695</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A60" s="228"/>
       <c r="B60" s="2">
         <v>3.5242560234373797E-2</v>
@@ -40553,7 +40553,7 @@
         <v>2.7228950587539599E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A61" s="228"/>
       <c r="B61" s="210"/>
       <c r="C61" s="2">
@@ -40580,7 +40580,7 @@
         <v>1.9817054828586678</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="42" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A62" s="228"/>
       <c r="B62" s="210"/>
       <c r="C62" s="210"/>
@@ -40600,7 +40600,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="42" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A63" s="228"/>
       <c r="B63" s="2">
         <v>0.55587802902068695</v>
@@ -40615,7 +40615,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="64" spans="1:13" s="5" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" s="5" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="229"/>
       <c r="B64" s="13">
         <v>2.7228950587539599E-2</v>
@@ -40632,8 +40632,8 @@
       <c r="F64" s="13"/>
       <c r="G64" s="13"/>
     </row>
-    <row r="66" spans="1:32" ht="14" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A67" s="321"/>
       <c r="B67" s="323" t="s">
         <v>308</v>
@@ -40642,7 +40642,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="68" spans="1:32" ht="28" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:32" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A68" s="160" t="s">
         <v>439</v>
       </c>
@@ -40657,7 +40657,7 @@
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
     </row>
-    <row r="69" spans="1:32" ht="14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A69" s="160" t="s">
         <v>440</v>
       </c>
@@ -40670,14 +40670,14 @@
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
     </row>
-    <row r="70" spans="1:32" ht="13.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:32" ht="13.35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="160"/>
       <c r="B70" s="245"/>
       <c r="C70" s="244"/>
       <c r="G70" s="207"/>
       <c r="H70" s="238"/>
     </row>
-    <row r="71" spans="1:32" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:32" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A71" s="158" t="s">
         <v>441</v>
       </c>
@@ -40693,7 +40693,7 @@
       <c r="H71" s="204"/>
       <c r="I71" s="204"/>
     </row>
-    <row r="72" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="325"/>
       <c r="B72" s="210"/>
       <c r="C72" s="210"/>
@@ -40704,7 +40704,7 @@
       <c r="H72" s="204"/>
       <c r="I72" s="204"/>
     </row>
-    <row r="73" spans="1:32" ht="28" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A73" s="159" t="s">
         <v>331</v>
       </c>
@@ -40725,7 +40725,7 @@
       <c r="I73" s="204"/>
       <c r="AF73"/>
     </row>
-    <row r="74" spans="1:32" ht="28" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:32" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A74" s="160" t="s">
         <v>332</v>
       </c>
@@ -40745,7 +40745,7 @@
       <c r="H74" s="204"/>
       <c r="I74" s="204"/>
     </row>
-    <row r="75" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:32" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A75" s="160" t="s">
         <v>333</v>
       </c>
@@ -40765,7 +40765,7 @@
       <c r="H75" s="204"/>
       <c r="I75" s="204"/>
     </row>
-    <row r="76" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A76" s="321" t="s">
         <v>337</v>
       </c>
@@ -40779,7 +40779,7 @@
       <c r="H76" s="204"/>
       <c r="I76" s="204"/>
     </row>
-    <row r="77" spans="1:32" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:32" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="160" t="s">
         <v>378</v>
       </c>
@@ -40804,7 +40804,7 @@
       <c r="I77" s="204"/>
       <c r="K77" s="237"/>
     </row>
-    <row r="78" spans="1:32" ht="14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A78" s="160" t="s">
         <v>236</v>
       </c>
@@ -40828,7 +40828,7 @@
       <c r="H78" s="204"/>
       <c r="I78" s="204"/>
     </row>
-    <row r="79" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A79" s="158" t="s">
         <v>241</v>
       </c>
@@ -40852,13 +40852,13 @@
       <c r="H79" s="204"/>
       <c r="I79" s="204"/>
     </row>
-    <row r="80" spans="1:32" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A80" s="160"/>
       <c r="G80" s="204"/>
       <c r="H80" s="204"/>
       <c r="I80" s="204"/>
     </row>
-    <row r="81" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A81" s="321" t="s">
         <v>258</v>
       </c>
@@ -40872,13 +40872,13 @@
       <c r="H81" s="204"/>
       <c r="I81" s="204"/>
     </row>
-    <row r="82" spans="1:9" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A82" s="160"/>
       <c r="G82" s="204"/>
       <c r="H82" s="204"/>
       <c r="I82" s="204"/>
     </row>
-    <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="322" t="s">
         <v>359</v>
       </c>
@@ -40888,7 +40888,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="159" t="s">
         <v>235</v>
       </c>
@@ -40905,7 +40905,7 @@
         <v>0.11692651444196828</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="160" t="s">
         <v>236</v>
       </c>
@@ -40922,7 +40922,7 @@
         <v>0.39206203083097213</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A86" s="158" t="s">
         <v>241</v>
       </c>
@@ -40942,7 +40942,7 @@
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="160"/>
     </row>
-    <row r="89" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="57"/>
       <c r="D89" s="1"/>
     </row>
@@ -40975,7 +40975,7 @@
     <row r="98" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D98" s="1"/>
     </row>
-    <row r="99" spans="4:4" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="4:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D99" s="237"/>
     </row>
     <row r="119" spans="6:13" x14ac:dyDescent="0.2">
@@ -40983,7 +40983,7 @@
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
     </row>
-    <row r="120" spans="6:13" ht="11.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="6:13" ht="11.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I120" s="253"/>
       <c r="J120" s="253"/>
       <c r="K120" s="253"/>
@@ -41023,18 +41023,18 @@
     <tabColor rgb="FFB3A2C7"/>
   </sheetPr>
   <dimension ref="A1:AA55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" style="48"/>
-    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="48"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="18" width="9" bestFit="1" customWidth="1"/>
     <col min="20" max="27" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="162" customFormat="1" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="162" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="164"/>
       <c r="B1" s="165" t="s">
         <v>385</v>
@@ -41115,7 +41115,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="167">
         <v>0</v>
       </c>
@@ -41196,7 +41196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="167">
         <v>1</v>
       </c>
@@ -41277,7 +41277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="167">
         <v>2</v>
       </c>
@@ -41358,7 +41358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="167">
         <v>3</v>
       </c>
@@ -41439,7 +41439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="167">
         <v>4</v>
       </c>
@@ -41520,7 +41520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="167">
         <v>5</v>
       </c>
@@ -41601,7 +41601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="167">
         <v>6</v>
       </c>
@@ -41682,7 +41682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="167">
         <v>7</v>
       </c>
@@ -41763,7 +41763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="167">
         <v>8</v>
       </c>
@@ -41844,7 +41844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="167">
         <v>9</v>
       </c>
@@ -41925,7 +41925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="167">
         <v>10</v>
       </c>
@@ -42006,7 +42006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="167">
         <v>11</v>
       </c>
@@ -42087,7 +42087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="167">
         <v>12</v>
       </c>
@@ -42168,7 +42168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="167">
         <v>13</v>
       </c>
@@ -42249,7 +42249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="167">
         <v>14</v>
       </c>
@@ -42330,7 +42330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="167">
         <v>15</v>
       </c>
@@ -42411,7 +42411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="167">
         <v>16</v>
       </c>
@@ -42492,7 +42492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="167">
         <v>17</v>
       </c>
@@ -42573,7 +42573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="167">
         <v>18</v>
       </c>
@@ -42654,7 +42654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="167">
         <v>19</v>
       </c>
@@ -42735,7 +42735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="167">
         <v>20</v>
       </c>
@@ -42816,7 +42816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="167">
         <v>21</v>
       </c>
@@ -42897,7 +42897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="167">
         <v>22</v>
       </c>
@@ -42978,7 +42978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="167">
         <v>23</v>
       </c>
@@ -43059,7 +43059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="167">
         <v>24</v>
       </c>
@@ -43140,7 +43140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="167">
         <v>25</v>
       </c>
@@ -43221,7 +43221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="167">
         <v>26</v>
       </c>
@@ -43302,7 +43302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="167">
         <v>27</v>
       </c>
@@ -43383,7 +43383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="167">
         <v>28</v>
       </c>
@@ -43464,7 +43464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="167">
         <v>29</v>
       </c>
@@ -43545,7 +43545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="167">
         <v>30</v>
       </c>
@@ -43626,7 +43626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="167">
         <v>31</v>
       </c>
@@ -43707,7 +43707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="167">
         <v>32</v>
       </c>
@@ -43788,7 +43788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="167">
         <v>33</v>
       </c>
@@ -43869,7 +43869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="167">
         <v>34</v>
       </c>
@@ -43950,7 +43950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="167">
         <v>35</v>
       </c>
@@ -44031,7 +44031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" s="167">
         <v>36</v>
       </c>
@@ -44112,7 +44112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="167">
         <v>37</v>
       </c>
@@ -44193,7 +44193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="167">
         <v>38</v>
       </c>
@@ -44274,7 +44274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="167">
         <v>39</v>
       </c>
@@ -44355,7 +44355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="167">
         <v>40</v>
       </c>
@@ -44436,7 +44436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="167">
         <v>41</v>
       </c>
@@ -44517,7 +44517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="167">
         <v>42</v>
       </c>
@@ -44598,7 +44598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="167">
         <v>43</v>
       </c>
@@ -44679,7 +44679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="167">
         <v>44</v>
       </c>
@@ -44760,7 +44760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="167">
         <v>45</v>
       </c>
@@ -44841,7 +44841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="167">
         <v>46</v>
       </c>
@@ -44922,7 +44922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" s="167">
         <v>47</v>
       </c>
@@ -45003,7 +45003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="167">
         <v>48</v>
       </c>
@@ -45084,7 +45084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="167">
         <v>49</v>
       </c>
@@ -45165,7 +45165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" s="167">
         <v>50</v>
       </c>
@@ -45246,7 +45246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" s="167">
         <v>51</v>
       </c>
@@ -45327,7 +45327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" s="167">
         <v>52</v>
       </c>
@@ -45408,7 +45408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" s="167">
         <v>53</v>
       </c>
@@ -45500,18 +45500,18 @@
     <tabColor rgb="FFB3A2C7"/>
   </sheetPr>
   <dimension ref="A1:AA55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="47" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" style="48" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="48" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="18" width="9" bestFit="1" customWidth="1"/>
     <col min="20" max="27" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="304" customFormat="1" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="304" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="326"/>
       <c r="B1" s="165" t="s">
         <v>385</v>
@@ -45592,7 +45592,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="395">
         <v>0</v>
       </c>
@@ -45673,7 +45673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="328">
         <v>1</v>
       </c>
@@ -45754,7 +45754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="328">
         <v>2</v>
       </c>
@@ -45835,7 +45835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="328">
         <v>3</v>
       </c>
@@ -45916,7 +45916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="328">
         <v>4</v>
       </c>
@@ -45997,7 +45997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="328">
         <v>5</v>
       </c>
@@ -46078,7 +46078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="328">
         <v>6</v>
       </c>
@@ -46159,7 +46159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="328">
         <v>7</v>
       </c>
@@ -46240,7 +46240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="328">
         <v>8</v>
       </c>
@@ -46321,7 +46321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="328">
         <v>9</v>
       </c>
@@ -46402,7 +46402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="328">
         <v>10</v>
       </c>
@@ -46483,7 +46483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="328">
         <v>11</v>
       </c>
@@ -46564,7 +46564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="328">
         <v>12</v>
       </c>
@@ -46645,7 +46645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="328">
         <v>13</v>
       </c>
@@ -46726,7 +46726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="328">
         <v>14</v>
       </c>
@@ -46807,7 +46807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="328">
         <v>15</v>
       </c>
@@ -46888,7 +46888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="328">
         <v>16</v>
       </c>
@@ -46969,7 +46969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="328">
         <v>17</v>
       </c>
@@ -47050,7 +47050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="395">
         <v>18</v>
       </c>
@@ -47131,7 +47131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="328">
         <v>19</v>
       </c>
@@ -47212,7 +47212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="328">
         <v>20</v>
       </c>
@@ -47293,7 +47293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="328">
         <v>21</v>
       </c>
@@ -47374,7 +47374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="328">
         <v>22</v>
       </c>
@@ -47455,7 +47455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="328">
         <v>23</v>
       </c>
@@ -47536,7 +47536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="328">
         <v>24</v>
       </c>
@@ -47617,7 +47617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="328">
         <v>25</v>
       </c>
@@ -47698,7 +47698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="328">
         <v>26</v>
       </c>
@@ -47779,7 +47779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="328">
         <v>27</v>
       </c>
@@ -47860,7 +47860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="328">
         <v>28</v>
       </c>
@@ -47941,7 +47941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="328">
         <v>29</v>
       </c>
@@ -48022,7 +48022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="328">
         <v>30</v>
       </c>
@@ -48103,7 +48103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="328">
         <v>31</v>
       </c>
@@ -48184,7 +48184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="328">
         <v>32</v>
       </c>
@@ -48265,7 +48265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="328">
         <v>33</v>
       </c>
@@ -48346,7 +48346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="328">
         <v>34</v>
       </c>
@@ -48427,7 +48427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="328">
         <v>35</v>
       </c>
@@ -48508,7 +48508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:27" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="395">
         <v>36</v>
       </c>
@@ -48589,7 +48589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" s="328">
         <v>37</v>
       </c>
@@ -48670,7 +48670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" s="328">
         <v>38</v>
       </c>
@@ -48751,7 +48751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" s="328">
         <v>39</v>
       </c>
@@ -48832,7 +48832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" s="328">
         <v>40</v>
       </c>
@@ -48913,7 +48913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" s="328">
         <v>41</v>
       </c>
@@ -48994,7 +48994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" s="328">
         <v>42</v>
       </c>
@@ -49075,7 +49075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" s="328">
         <v>43</v>
       </c>
@@ -49156,7 +49156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" s="328">
         <v>44</v>
       </c>
@@ -49237,7 +49237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="328">
         <v>45</v>
       </c>
@@ -49318,7 +49318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="328">
         <v>46</v>
       </c>
@@ -49399,7 +49399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" s="328">
         <v>47</v>
       </c>
@@ -49480,7 +49480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="328">
         <v>48</v>
       </c>
@@ -49561,7 +49561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="328">
         <v>49</v>
       </c>
@@ -49642,7 +49642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" s="328">
         <v>50</v>
       </c>
@@ -49723,7 +49723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" s="328">
         <v>51</v>
       </c>
@@ -49804,7 +49804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" s="328">
         <v>52</v>
       </c>
@@ -49885,7 +49885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" s="328">
         <v>53</v>
       </c>
@@ -49977,16 +49977,16 @@
     <tabColor rgb="FFB3A2C7"/>
   </sheetPr>
   <dimension ref="A1:Y36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="8.83203125" style="57"/>
-    <col min="4" max="18" width="8.83203125" style="57" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.33203125" style="57" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="8.83203125" style="57" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="8.83203125" style="57"/>
+    <col min="1" max="3" width="8.85546875" style="57"/>
+    <col min="4" max="18" width="8.85546875" style="57" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.28515625" style="57" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="8.85546875" style="57" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="8.85546875" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
         <v>254</v>
       </c>
@@ -50064,7 +50064,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="72"/>
       <c r="B2" s="69" t="s">
         <v>378</v>
@@ -50160,7 +50160,7 @@
         <v>101327.10855100733</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="71"/>
       <c r="B3" s="60"/>
       <c r="C3" s="61" t="s">
@@ -50253,7 +50253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="73"/>
       <c r="B4" s="66"/>
       <c r="C4" s="67" t="s">
@@ -50347,7 +50347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="72"/>
       <c r="B5" s="69" t="s">
         <v>236</v>
@@ -50442,7 +50442,7 @@
         <v>380362.19277958805</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="71"/>
       <c r="B6" s="60"/>
       <c r="C6" s="61" t="s">
@@ -50535,7 +50535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="73"/>
       <c r="B7" s="66"/>
       <c r="C7" s="67" t="s">
@@ -50628,7 +50628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="71"/>
       <c r="B8" s="60" t="s">
         <v>241</v>
@@ -50722,7 +50722,7 @@
         <v>101327.10855100733</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="71"/>
       <c r="B9" s="60"/>
       <c r="C9" s="61" t="s">
@@ -50815,7 +50815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="73"/>
       <c r="B10" s="66"/>
       <c r="C10" s="67" t="s">
@@ -50908,12 +50908,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="57" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="37" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="138" t="s">
         <v>233</v>
       </c>
@@ -50972,7 +50972,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B15" s="69" t="s">
         <v>378</v>
       </c>
@@ -51040,7 +51040,7 @@
         <v>492333047.3785181</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B16" s="132"/>
       <c r="C16" s="143" t="s">
         <v>259</v>
@@ -51106,7 +51106,7 @@
         <v>203533411.02620864</v>
       </c>
     </row>
-    <row r="17" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="144"/>
       <c r="C17" s="145" t="s">
         <v>244</v>
@@ -51180,7 +51180,7 @@
         <v>7.8906026136745758E-2</v>
       </c>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="140" t="s">
         <v>236</v>
       </c>
@@ -51249,7 +51249,7 @@
       </c>
       <c r="T18" s="349"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" s="132"/>
       <c r="C19" s="143" t="s">
         <v>259</v>
@@ -51316,7 +51316,7 @@
       </c>
       <c r="T19" s="349"/>
     </row>
-    <row r="20" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="144"/>
       <c r="C20" s="145" t="s">
         <v>244</v>
@@ -51390,7 +51390,7 @@
         <v>5.492500964286065E-2</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" s="132" t="s">
         <v>241</v>
       </c>
@@ -51459,7 +51459,7 @@
       </c>
       <c r="T21" s="349"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" s="132"/>
       <c r="C22" s="143" t="s">
         <v>259</v>
@@ -51526,7 +51526,7 @@
       </c>
       <c r="T22" s="349"/>
     </row>
-    <row r="23" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="144"/>
       <c r="C23" s="145" t="s">
         <v>244</v>
@@ -51600,7 +51600,7 @@
         <v>0.12334309427671863</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="351" t="s">
         <v>375</v>
       </c>
@@ -51620,7 +51620,7 @@
       <c r="P25" s="351"/>
       <c r="Q25" s="351"/>
     </row>
-    <row r="26" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="351"/>
       <c r="C26" s="351"/>
       <c r="D26" s="351"/>
@@ -51638,7 +51638,7 @@
       <c r="P26" s="351"/>
       <c r="Q26" s="351"/>
     </row>
-    <row r="27" spans="2:21" ht="37" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:21" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="329" t="s">
         <v>233</v>
       </c>
@@ -51688,7 +51688,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="334" t="s">
         <v>378</v>
       </c>
@@ -51742,7 +51742,7 @@
         <v>492333047.3785181</v>
       </c>
     </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="339"/>
       <c r="C29" s="340" t="s">
         <v>259</v>
@@ -51794,7 +51794,7 @@
         <v>203533411.02620864</v>
       </c>
     </row>
-    <row r="30" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="344"/>
       <c r="C30" s="345" t="s">
         <v>244</v>
@@ -51850,7 +51850,7 @@
         <v>0.12006133464707393</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="334" t="s">
         <v>236</v>
       </c>
@@ -51905,7 +51905,7 @@
       </c>
       <c r="T31" s="349"/>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="339"/>
       <c r="C32" s="340" t="s">
         <v>259</v>
@@ -51958,7 +51958,7 @@
       </c>
       <c r="T32" s="349"/>
     </row>
-    <row r="33" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="344"/>
       <c r="C33" s="345" t="s">
         <v>244</v>
@@ -52014,7 +52014,7 @@
         <v>0.23524603264323438</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B34" s="339" t="s">
         <v>241</v>
       </c>
@@ -52069,7 +52069,7 @@
       </c>
       <c r="T34" s="349"/>
     </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B35" s="339"/>
       <c r="C35" s="340" t="s">
         <v>259</v>
@@ -52122,7 +52122,7 @@
       </c>
       <c r="T35" s="349"/>
     </row>
-    <row r="36" spans="2:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="344"/>
       <c r="C36" s="345" t="s">
         <v>244</v>
@@ -52189,9 +52189,9 @@
     <tabColor rgb="FFB3A2C7"/>
   </sheetPr>
   <dimension ref="A1:AB55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="538"/>
       <c r="B1" s="382" t="s">
         <v>466</v>
@@ -52275,7 +52275,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="397">
         <v>0</v>
       </c>
@@ -52355,7 +52355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" s="382">
         <v>1</v>
       </c>
@@ -52435,7 +52435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" s="382">
         <v>2</v>
       </c>
@@ -52515,7 +52515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" s="382">
         <v>3</v>
       </c>
@@ -52595,7 +52595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" s="382">
         <v>4</v>
       </c>
@@ -52675,7 +52675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="382">
         <v>5</v>
       </c>
@@ -52755,7 +52755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" s="382">
         <v>6</v>
       </c>
@@ -52835,7 +52835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="382">
         <v>7</v>
       </c>
@@ -52915,7 +52915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="382">
         <v>8</v>
       </c>
@@ -52995,7 +52995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="382">
         <v>9</v>
       </c>
@@ -53075,7 +53075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" s="382">
         <v>10</v>
       </c>
@@ -53155,7 +53155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" s="382">
         <v>11</v>
       </c>
@@ -53235,7 +53235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" s="382">
         <v>12</v>
       </c>
@@ -53315,7 +53315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" s="382">
         <v>13</v>
       </c>
@@ -53395,7 +53395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" s="382">
         <v>14</v>
       </c>
@@ -53475,7 +53475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="382">
         <v>15</v>
       </c>
@@ -53555,7 +53555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="382">
         <v>16</v>
       </c>
@@ -53635,7 +53635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="382">
         <v>17</v>
       </c>
@@ -53715,7 +53715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:28" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="397">
         <v>18</v>
       </c>
@@ -53795,7 +53795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="382">
         <v>19</v>
       </c>
@@ -53875,7 +53875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="382">
         <v>20</v>
       </c>
@@ -53955,7 +53955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="382">
         <v>21</v>
       </c>
@@ -54035,7 +54035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="382">
         <v>22</v>
       </c>
@@ -54115,7 +54115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="382">
         <v>23</v>
       </c>
@@ -54195,7 +54195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="382">
         <v>24</v>
       </c>
@@ -54275,7 +54275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="382">
         <v>25</v>
       </c>
@@ -54355,7 +54355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="382">
         <v>26</v>
       </c>
@@ -54435,7 +54435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="382">
         <v>27</v>
       </c>
@@ -54515,7 +54515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="382">
         <v>28</v>
       </c>
@@ -54595,7 +54595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="382">
         <v>29</v>
       </c>
@@ -54675,7 +54675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="382">
         <v>30</v>
       </c>
@@ -54755,7 +54755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="382">
         <v>31</v>
       </c>
@@ -54835,7 +54835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="382">
         <v>32</v>
       </c>
@@ -54915,7 +54915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="382">
         <v>33</v>
       </c>
@@ -54995,7 +54995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="382">
         <v>34</v>
       </c>
@@ -55075,7 +55075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="382">
         <v>35</v>
       </c>
@@ -55155,7 +55155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:28" s="135" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:28" s="135" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="397">
         <v>36</v>
       </c>
@@ -55235,7 +55235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A39" s="382">
         <v>37</v>
       </c>
@@ -55315,7 +55315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A40" s="382">
         <v>38</v>
       </c>
@@ -55395,7 +55395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A41" s="382">
         <v>39</v>
       </c>
@@ -55475,7 +55475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A42" s="382">
         <v>40</v>
       </c>
@@ -55555,7 +55555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A43" s="382">
         <v>41</v>
       </c>
@@ -55635,7 +55635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A44" s="382">
         <v>42</v>
       </c>
@@ -55715,7 +55715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A45" s="382">
         <v>43</v>
       </c>
@@ -55795,7 +55795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A46" s="382">
         <v>44</v>
       </c>
@@ -55875,7 +55875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A47" s="382">
         <v>45</v>
       </c>
@@ -55955,7 +55955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A48" s="382">
         <v>46</v>
       </c>
@@ -56035,7 +56035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A49" s="382">
         <v>47</v>
       </c>
@@ -56115,7 +56115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A50" s="382">
         <v>48</v>
       </c>
@@ -56195,7 +56195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A51" s="382">
         <v>49</v>
       </c>
@@ -56275,7 +56275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A52" s="382">
         <v>50</v>
       </c>
@@ -56355,7 +56355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A53" s="382">
         <v>51</v>
       </c>
@@ -56435,7 +56435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A54" s="382">
         <v>52</v>
       </c>
@@ -56515,7 +56515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A55" s="382">
         <v>53</v>
       </c>
@@ -56603,9 +56603,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07BB1108-8C3C-F641-97AC-472BA22EDCB3}">
   <dimension ref="A1:O30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="69" t="s">
         <v>395</v>
       </c>
@@ -56652,7 +56652,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="66"/>
       <c r="B2" s="67"/>
       <c r="C2" s="352" t="s">
@@ -56695,7 +56695,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="60" t="s">
         <v>579</v>
       </c>
@@ -56742,7 +56742,7 @@
         <v>1.5863528683098591</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="60"/>
       <c r="B4" s="61" t="s">
         <v>577</v>
@@ -56788,7 +56788,7 @@
         <v>1.9276526771126758</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="60"/>
       <c r="B5" s="61" t="s">
         <v>575</v>
@@ -56834,7 +56834,7 @@
         <v>1.9343643245305164</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="60"/>
       <c r="B6" s="61" t="s">
         <v>578</v>
@@ -56879,7 +56879,7 @@
         <v>2.0107568838028169</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="60" t="s">
         <v>399</v>
       </c>
@@ -56926,7 +56926,7 @@
         <v>1.37412562173913</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="60"/>
       <c r="B8" s="61" t="s">
         <v>577</v>
@@ -56972,7 +56972,7 @@
         <v>1.9604835096618356</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="60"/>
       <c r="B9" s="61" t="s">
         <v>575</v>
@@ -57018,7 +57018,7 @@
         <v>1.9730191130434778</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="60"/>
       <c r="B10" s="61" t="s">
         <v>578</v>
@@ -57063,7 +57063,7 @@
         <v>2.0533810913043462</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="60" t="s">
         <v>400</v>
       </c>
@@ -57110,7 +57110,7 @@
         <v>2.0109270461538458</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="60"/>
       <c r="B12" s="61" t="s">
         <v>577</v>
@@ -57156,7 +57156,7 @@
         <v>3.1644151946886443</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="60"/>
       <c r="B13" s="61" t="s">
         <v>575</v>
@@ -57202,7 +57202,7 @@
         <v>3.1290036838827837</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="60"/>
       <c r="B14" s="61" t="s">
         <v>578</v>
@@ -57247,7 +57247,7 @@
         <v>3.1135820868131865</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="60" t="s">
         <v>580</v>
       </c>
@@ -57294,7 +57294,7 @@
         <v>1.9778029835636648</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="60"/>
       <c r="B16" s="61" t="s">
         <v>577</v>
@@ -57340,7 +57340,7 @@
         <v>4.6279342452771148</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="60"/>
       <c r="B17" s="61" t="s">
         <v>575</v>
@@ -57386,7 +57386,7 @@
         <v>4.7904670616979228</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="60"/>
       <c r="B18" s="61" t="s">
         <v>578</v>
@@ -57431,7 +57431,7 @@
         <v>4.725455303754778</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="60" t="s">
         <v>402</v>
       </c>
@@ -57478,7 +57478,7 @@
         <v>2.1094656848136637</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="60"/>
       <c r="B20" s="61" t="s">
         <v>577</v>
@@ -57524,7 +57524,7 @@
         <v>2.044294966726389</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="60"/>
       <c r="B21" s="61" t="s">
         <v>575</v>
@@ -57570,7 +57570,7 @@
         <v>2.1939223311544422</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="60"/>
       <c r="B22" s="61" t="s">
         <v>578</v>
@@ -57615,7 +57615,7 @@
         <v>2.1294871696786899</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="60" t="s">
         <v>403</v>
       </c>
@@ -57662,7 +57662,7 @@
         <v>0.39648400197510358</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="60"/>
       <c r="B24" s="61" t="s">
         <v>577</v>
@@ -57708,7 +57708,7 @@
         <v>0.37791461881461524</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="60"/>
       <c r="B25" s="61" t="s">
         <v>575</v>
@@ -57754,7 +57754,7 @@
         <v>0.31221953719456014</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="60"/>
       <c r="B26" s="61" t="s">
         <v>578</v>
@@ -57799,7 +57799,7 @@
         <v>0.30647138029337567</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="60" t="s">
         <v>404</v>
       </c>
@@ -57846,7 +57846,7 @@
         <v>2.0345576971713086</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="60"/>
       <c r="B28" s="61" t="s">
         <v>577</v>
@@ -57892,7 +57892,7 @@
         <v>3.2508215694719356</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="60"/>
       <c r="B29" s="61" t="s">
         <v>575</v>
@@ -57938,7 +57938,7 @@
         <v>3.1764030885579571</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="66"/>
       <c r="B30" s="61" t="s">
         <v>578</v>
@@ -57994,18 +57994,18 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:O30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="15" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="69" t="s">
         <v>395</v>
       </c>
@@ -58052,7 +58052,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="66"/>
       <c r="B2" s="67"/>
       <c r="C2" s="352" t="s">
@@ -58095,7 +58095,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="60" t="s">
         <v>398</v>
       </c>
@@ -58142,7 +58142,7 @@
         <v>1.5863528683098591</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="60"/>
       <c r="B4" s="61" t="s">
         <v>267</v>
@@ -58187,7 +58187,7 @@
         <v>1.9293660499999998</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="60"/>
       <c r="B5" s="61" t="s">
         <v>268</v>
@@ -58232,7 +58232,7 @@
         <v>1.9190858126760564</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="60"/>
       <c r="B6" s="61" t="s">
         <v>455</v>
@@ -58277,7 +58277,7 @@
         <v>2.0107568838028169</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="60" t="s">
         <v>399</v>
       </c>
@@ -58324,7 +58324,7 @@
         <v>1.37412562173913</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="60"/>
       <c r="B8" s="61" t="s">
         <v>267</v>
@@ -58369,7 +58369,7 @@
         <v>1.9611908681159418</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="60"/>
       <c r="B9" s="61" t="s">
         <v>268</v>
@@ -58414,7 +58414,7 @@
         <v>1.9569467173913042</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="60"/>
       <c r="B10" s="61" t="s">
         <v>455</v>
@@ -58459,7 +58459,7 @@
         <v>2.0533810913043462</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="60" t="s">
         <v>400</v>
       </c>
@@ -58506,7 +58506,7 @@
         <v>2.0109270461538458</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="60"/>
       <c r="B12" s="61" t="s">
         <v>267</v>
@@ -58551,7 +58551,7 @@
         <v>3.1708806329670325</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="60"/>
       <c r="B13" s="61" t="s">
         <v>268</v>
@@ -58596,7 +58596,7 @@
         <v>3.1320880032967029</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="60"/>
       <c r="B14" s="61" t="s">
         <v>455</v>
@@ -58641,7 +58641,7 @@
         <v>3.1135820868131865</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="60" t="s">
         <v>401</v>
       </c>
@@ -58688,7 +58688,7 @@
         <v>1.9778029835636648</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="60"/>
       <c r="B16" s="61" t="s">
         <v>267</v>
@@ -58733,7 +58733,7 @@
         <v>4.5928272116752273</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="60"/>
       <c r="B17" s="61" t="s">
         <v>268</v>
@@ -58778,7 +58778,7 @@
         <v>4.8034694132865514</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="60"/>
       <c r="B18" s="61" t="s">
         <v>455</v>
@@ -58823,7 +58823,7 @@
         <v>4.725455303754778</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="60" t="s">
         <v>402</v>
       </c>
@@ -58870,7 +58870,7 @@
         <v>2.1094656848136637</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="60"/>
       <c r="B20" s="61" t="s">
         <v>267</v>
@@ -58915,7 +58915,7 @@
         <v>2.0117920873817479</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="60"/>
       <c r="B21" s="61" t="s">
         <v>268</v>
@@ -58960,7 +58960,7 @@
         <v>2.2068093634495929</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="60"/>
       <c r="B22" s="61" t="s">
         <v>455</v>
@@ -59005,7 +59005,7 @@
         <v>2.1294871696786899</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="60" t="s">
         <v>403</v>
       </c>
@@ -59052,7 +59052,7 @@
         <v>0.39648400197510358</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="60"/>
       <c r="B24" s="61" t="s">
         <v>267</v>
@@ -59097,7 +59097,7 @@
         <v>0.39082370886257889</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="60"/>
       <c r="B25" s="61" t="s">
         <v>268</v>
@@ -59142,7 +59142,7 @@
         <v>0.31336916857479702</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="60"/>
       <c r="B26" s="61" t="s">
         <v>455</v>
@@ -59187,7 +59187,7 @@
         <v>0.30647138029337567</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="60" t="s">
         <v>404</v>
       </c>
@@ -59234,7 +59234,7 @@
         <v>2.0345576971713086</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="60"/>
       <c r="B28" s="61" t="s">
         <v>267</v>
@@ -59279,7 +59279,7 @@
         <v>3.2637090449413471</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="60"/>
       <c r="B29" s="61" t="s">
         <v>268</v>
@@ -59324,7 +59324,7 @@
         <v>3.1863841921248763</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="66"/>
       <c r="B30" s="67" t="s">
         <v>455</v>
@@ -59381,20 +59381,20 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:V40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="10" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="21" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.83203125" style="1"/>
+    <col min="22" max="22" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="4" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="4" customFormat="1" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="355" t="s">
         <v>378</v>
       </c>
@@ -59462,7 +59462,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="9" customFormat="1" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" s="9" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="357"/>
       <c r="B2" s="358" t="s">
         <v>454</v>
@@ -59936,7 +59936,7 @@
         <v>12.871991247264772</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="217" t="s">
         <v>392</v>
       </c>
@@ -60004,7 +60004,7 @@
         <v>13.505494505494504</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="354"/>
       <c r="C10" s="354"/>
       <c r="D10" s="354"/>
@@ -60027,7 +60027,7 @@
       <c r="U10" s="354"/>
       <c r="V10" s="354"/>
     </row>
-    <row r="11" spans="1:22" s="9" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" s="9" customFormat="1" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="359" t="s">
         <v>236</v>
       </c>
@@ -60095,7 +60095,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="9" customFormat="1" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" s="9" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="359"/>
       <c r="B12" s="358" t="s">
         <v>454</v>
@@ -60569,7 +60569,7 @@
         <v>12.871991247264772</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="217" t="s">
         <v>392</v>
       </c>
@@ -60637,7 +60637,7 @@
         <v>13.505494505494504</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="354"/>
       <c r="C20" s="354"/>
       <c r="D20" s="354"/>
@@ -60660,7 +60660,7 @@
       <c r="U20" s="354"/>
       <c r="V20" s="354"/>
     </row>
-    <row r="21" spans="1:22" s="9" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" s="9" customFormat="1" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="357" t="s">
         <v>241</v>
       </c>
@@ -60728,7 +60728,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:22" s="9" customFormat="1" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" s="9" customFormat="1" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="357"/>
       <c r="B22" s="358" t="s">
         <v>454</v>
@@ -61202,7 +61202,7 @@
         <v>12.87199124726477</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="217" t="s">
         <v>392</v>
       </c>
@@ -61270,8 +61270,8 @@
         <v>13.505494505494504</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="14" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:22" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:22" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="355" t="s">
         <v>574</v>
       </c>
@@ -61339,7 +61339,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="357"/>
       <c r="B33" s="358" t="s">
         <v>454</v>
@@ -61813,7 +61813,7 @@
         <v>12.87199124726477</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="14" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A40" s="217" t="s">
         <v>392</v>
       </c>
@@ -61893,13 +61893,13 @@
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:L8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" ht="58.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="3" customFormat="1" ht="58.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C1" s="386" t="s">
         <v>199</v>
       </c>
@@ -61919,7 +61919,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="421" t="s">
         <v>507</v>
       </c>
@@ -61944,7 +61944,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="545" t="s">
         <v>508</v>
       </c>
@@ -61974,7 +61974,7 @@
       <c r="K3" s="549"/>
       <c r="L3" s="549"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="546"/>
       <c r="B4" s="47" t="s">
         <v>241</v>
@@ -61996,7 +61996,7 @@
       <c r="K4" s="549"/>
       <c r="L4" s="549"/>
     </row>
-    <row r="5" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="547"/>
       <c r="B5" s="384" t="s">
         <v>236</v>
@@ -62019,7 +62019,7 @@
       <c r="K5" s="549"/>
       <c r="L5" s="549"/>
     </row>
-    <row r="8" spans="1:12" ht="73" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="72.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="550" t="s">
         <v>545</v>
       </c>
@@ -62046,19 +62046,20 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:R55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="36.83203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.1640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="18.1640625" customWidth="1"/>
-    <col min="9" max="9" width="13.6640625" style="47" customWidth="1"/>
-    <col min="11" max="11" width="47.83203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="29.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" style="47" customWidth="1"/>
+    <col min="11" max="11" width="47.85546875" style="3" customWidth="1"/>
     <col min="12" max="12" width="23" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="34" customFormat="1" ht="78.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="34" customFormat="1" ht="78.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33"/>
       <c r="B1" s="31" t="s">
         <v>6</v>
@@ -62092,7 +62093,7 @@
       </c>
       <c r="L1" s="557"/>
     </row>
-    <row r="2" spans="1:18" s="46" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="46" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>86</v>
       </c>
@@ -62124,7 +62125,7 @@
       <c r="K2" s="14"/>
       <c r="L2" s="9"/>
     </row>
-    <row r="3" spans="1:18" s="46" customFormat="1" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" s="46" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>177</v>
       </c>
@@ -62156,7 +62157,7 @@
       <c r="K3" s="14"/>
       <c r="L3" s="9"/>
     </row>
-    <row r="4" spans="1:18" s="46" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" s="46" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>88</v>
       </c>
@@ -62182,7 +62183,7 @@
         <v>5</v>
       </c>
       <c r="I4" s="15">
-        <v>0.11748738381164731</v>
+        <v>0.117487383811647</v>
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="50" t="s">
@@ -62190,7 +62191,7 @@
       </c>
       <c r="L4" s="9"/>
     </row>
-    <row r="5" spans="1:18" s="46" customFormat="1" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" s="46" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
         <v>89</v>
       </c>
@@ -62222,7 +62223,7 @@
       <c r="K5" s="14"/>
       <c r="L5" s="9"/>
     </row>
-    <row r="6" spans="1:18" s="42" customFormat="1" ht="56" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" s="42" customFormat="1" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A6" s="551" t="s">
         <v>90</v>
       </c>
@@ -62256,7 +62257,7 @@
       <c r="K6" s="12"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:18" s="44" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" s="44" customFormat="1" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="552"/>
       <c r="B7" s="13" t="s">
         <v>124</v>
@@ -62288,7 +62289,7 @@
       <c r="K7" s="13"/>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="1:18" s="46" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" s="46" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
         <v>91</v>
       </c>
@@ -62320,7 +62321,7 @@
       <c r="K8" s="14"/>
       <c r="L8" s="9"/>
     </row>
-    <row r="9" spans="1:18" s="42" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" s="42" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="240" t="s">
         <v>92</v>
       </c>
@@ -62358,7 +62359,7 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:18" s="42" customFormat="1" ht="56" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" s="42" customFormat="1" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A10" s="554" t="s">
         <v>167</v>
       </c>
@@ -62405,7 +62406,7 @@
       <c r="P10" s="79"/>
       <c r="R10" s="79"/>
     </row>
-    <row r="11" spans="1:18" ht="56" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A11" s="555"/>
       <c r="B11" s="2" t="s">
         <v>133</v>
@@ -62450,7 +62451,7 @@
       <c r="P11" s="57"/>
       <c r="R11" s="57"/>
     </row>
-    <row r="12" spans="1:18" ht="56" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="64.5" x14ac:dyDescent="0.25">
       <c r="A12" s="555"/>
       <c r="B12" s="2" t="s">
         <v>136</v>
@@ -62484,7 +62485,7 @@
       <c r="M12" s="57"/>
       <c r="N12" s="57"/>
     </row>
-    <row r="13" spans="1:18" s="44" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" s="44" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="556"/>
       <c r="B13" s="13" t="s">
         <v>338</v>
@@ -62525,7 +62526,7 @@
       </c>
       <c r="N13" s="68"/>
     </row>
-    <row r="14" spans="1:18" ht="28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A14" s="551" t="s">
         <v>94</v>
       </c>
@@ -62559,7 +62560,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="39" x14ac:dyDescent="0.25">
       <c r="A15" s="553"/>
       <c r="B15" s="2" t="s">
         <v>142</v>
@@ -62591,7 +62592,7 @@
       <c r="K15" s="233"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:18" ht="42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="51.75" x14ac:dyDescent="0.25">
       <c r="A16" s="553"/>
       <c r="B16" s="2" t="s">
         <v>145</v>
@@ -62625,7 +62626,7 @@
       </c>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="39" x14ac:dyDescent="0.25">
       <c r="A17" s="553"/>
       <c r="B17" s="2" t="s">
         <v>148</v>
@@ -62659,7 +62660,7 @@
       </c>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="39" x14ac:dyDescent="0.25">
       <c r="A18" s="553"/>
       <c r="B18" s="2" t="s">
         <v>151</v>
@@ -62693,7 +62694,7 @@
       </c>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:12" s="53" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="53" customFormat="1" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="552"/>
       <c r="B19" s="20" t="s">
         <v>154</v>
@@ -62729,7 +62730,7 @@
         <v>3.3333333333333335E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="46" customFormat="1" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" s="46" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>173</v>
       </c>
@@ -62761,7 +62762,7 @@
       <c r="K20" s="14"/>
       <c r="L20" s="9"/>
     </row>
-    <row r="21" spans="1:12" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="49" t="s">
         <v>178</v>
       </c>
@@ -62793,7 +62794,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:12" s="46" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="46" customFormat="1" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
         <v>87</v>
       </c>
@@ -62825,7 +62826,7 @@
       <c r="K22" s="14"/>
       <c r="L22" s="9"/>
     </row>
-    <row r="23" spans="1:12" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="49" t="s">
         <v>179</v>
       </c>
@@ -62857,7 +62858,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:12" s="46" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="46" customFormat="1" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
         <v>170</v>
       </c>
@@ -62889,7 +62890,7 @@
       <c r="K24" s="14"/>
       <c r="L24" s="9"/>
     </row>
-    <row r="25" spans="1:12" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
         <v>105</v>
       </c>
@@ -62921,7 +62922,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:12" s="46" customFormat="1" ht="29" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" s="46" customFormat="1" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
         <v>110</v>
       </c>
@@ -62953,7 +62954,7 @@
       <c r="K26" s="14"/>
       <c r="L26" s="9"/>
     </row>
-    <row r="27" spans="1:12" s="46" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" s="46" customFormat="1" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>180</v>
       </c>
@@ -62985,90 +62986,90 @@
       <c r="K27" s="14"/>
       <c r="L27" s="9"/>
     </row>
-    <row r="29" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="371" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="369" t="s">
         <v>460</v>
       </c>
       <c r="C30" s="3"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="3"/>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33" s="3"/>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34" s="3"/>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C35" s="3"/>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C36" s="3"/>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C37" s="3"/>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="3:3" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:3" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="3:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="3"/>
     </row>
-    <row r="41" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C41" s="3"/>
     </row>
-    <row r="42" spans="3:3" ht="16.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:3" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="3"/>
     </row>
-    <row r="43" spans="3:3" ht="13.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:3" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="3"/>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C44" s="3"/>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C45" s="3"/>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C46" s="3"/>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C47" s="3"/>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C48" s="3"/>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C49" s="3"/>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C50" s="3"/>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C51" s="3"/>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C52" s="3"/>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C53" s="3"/>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C54" s="3"/>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C55" s="3"/>
     </row>
   </sheetData>
@@ -63089,22 +63090,22 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:L39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" style="30" customWidth="1"/>
-    <col min="2" max="2" width="35.6640625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="8.83203125" style="1"/>
-    <col min="5" max="5" width="23.1640625" style="2" customWidth="1"/>
-    <col min="6" max="7" width="8.83203125" style="1"/>
-    <col min="8" max="8" width="18.1640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" style="38" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" style="8" customWidth="1"/>
-    <col min="11" max="11" width="45.6640625" style="367" customWidth="1"/>
-    <col min="12" max="12" width="30.5" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="15.28515625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" style="2" customWidth="1"/>
+    <col min="3" max="4" width="8.85546875" style="1"/>
+    <col min="5" max="5" width="23.140625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="8.85546875" style="1"/>
+    <col min="8" max="8" width="18.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="38" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="45.7109375" style="367" customWidth="1"/>
+    <col min="12" max="12" width="30.42578125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="34" customFormat="1" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="34" customFormat="1" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33"/>
       <c r="B1" s="31" t="s">
         <v>6</v>
@@ -63140,7 +63141,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" ht="56" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" s="4" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A2" s="563" t="s">
         <v>86</v>
       </c>
@@ -63178,7 +63179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="5" customFormat="1" ht="52.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="5" customFormat="1" ht="52.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="564"/>
       <c r="B3" s="13" t="s">
         <v>14</v>
@@ -63212,7 +63213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A4" s="563" t="s">
         <v>106</v>
       </c>
@@ -63247,7 +63248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="62" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="60.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="564"/>
       <c r="B5" s="2" t="s">
         <v>21</v>
@@ -63280,7 +63281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="9" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" s="9" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
         <v>88</v>
       </c>
@@ -63316,7 +63317,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" s="4" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A7" s="558" t="s">
         <v>89</v>
       </c>
@@ -63352,7 +63353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" s="5" customFormat="1" ht="52.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="5" customFormat="1" ht="52.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="560"/>
       <c r="B8" s="13" t="s">
         <v>34</v>
@@ -63386,7 +63387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" s="4" customFormat="1" ht="56" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" s="4" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="561" t="s">
         <v>90</v>
       </c>
@@ -63422,7 +63423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="5" customFormat="1" ht="52.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="5" customFormat="1" ht="52.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="565"/>
       <c r="B10" s="13" t="s">
         <v>43</v>
@@ -63458,7 +63459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" s="4" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" s="558" t="s">
         <v>91</v>
       </c>
@@ -63492,7 +63493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="5" customFormat="1" ht="52.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" s="5" customFormat="1" ht="52.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="560"/>
       <c r="B12" s="13" t="s">
         <v>51</v>
@@ -63526,7 +63527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" s="4" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A13" s="558" t="s">
         <v>92</v>
       </c>
@@ -63564,7 +63565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="39.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="559"/>
       <c r="B14" s="2" t="s">
         <v>58</v>
@@ -63597,7 +63598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12" s="5" customFormat="1" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="5" customFormat="1" ht="14.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="560"/>
       <c r="B15" s="13" t="s">
         <v>61</v>
@@ -63633,7 +63634,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="4" customFormat="1" ht="56" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" s="4" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A16" s="558" t="s">
         <v>93</v>
       </c>
@@ -63671,7 +63672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="35.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="35.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="559"/>
       <c r="B17" s="2" t="s">
         <v>68</v>
@@ -63707,7 +63708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="5" customFormat="1" ht="24.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="5" customFormat="1" ht="24.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="560"/>
       <c r="B18" s="13" t="s">
         <v>47</v>
@@ -63741,7 +63742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="4" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" s="4" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A19" s="558" t="s">
         <v>94</v>
       </c>
@@ -63775,7 +63776,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="559"/>
       <c r="B20" s="2" t="s">
         <v>78</v>
@@ -63805,7 +63806,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="559"/>
       <c r="B21" s="2" t="s">
         <v>81</v>
@@ -63836,7 +63837,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="22" spans="1:12" s="5" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" s="5" customFormat="1" ht="40.700000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="560"/>
       <c r="B22" s="13" t="s">
         <v>83</v>
@@ -63868,7 +63869,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
         <v>87</v>
       </c>
@@ -63900,7 +63901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="9" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="9" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
         <v>99</v>
       </c>
@@ -63934,7 +63935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="56" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A25" s="561" t="s">
         <v>105</v>
       </c>
@@ -63969,7 +63970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="562"/>
       <c r="B26" s="2" t="s">
         <v>47</v>
@@ -64002,7 +64003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="9" customFormat="1" ht="43" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" s="9" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
         <v>110</v>
       </c>
@@ -64038,7 +64039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="56" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A28" s="29" t="s">
         <v>112</v>
       </c>
@@ -64129,14 +64130,14 @@
     <tabColor theme="7" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:X12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="21" width="8.83203125" style="57"/>
-    <col min="22" max="22" width="10.1640625" style="57" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.83203125" style="57"/>
+    <col min="1" max="21" width="8.85546875" style="57"/>
+    <col min="22" max="22" width="10.140625" style="57" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.85546875" style="57"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="57" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="64.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="87" t="s">
         <v>245</v>
       </c>
@@ -64208,7 +64209,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="94"/>
       <c r="B2" s="183"/>
       <c r="C2" s="79" t="s">
@@ -64216,7 +64217,7 @@
       </c>
       <c r="D2" s="80">
         <f>GHG_Primary_production!I4</f>
-        <v>0.11748738381164731</v>
+        <v>0.117487383811647</v>
       </c>
       <c r="E2" s="78">
         <f>GHG_Primary_production!I3</f>
@@ -64298,7 +64299,7 @@
         <v>8.3101444498223723E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="198" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="198" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="193"/>
       <c r="B3" s="194"/>
       <c r="C3" s="195" t="s">
@@ -64383,14 +64384,14 @@
         <v>0.74412603207059036</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="136" t="s">
         <v>295</v>
       </c>
       <c r="B6" s="136"/>
       <c r="C6" s="136"/>
     </row>
-    <row r="7" spans="1:24" s="130" customFormat="1" ht="11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:24" s="130" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A7" s="566" t="s">
         <v>292</v>
       </c>
@@ -64455,7 +64456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="130" customFormat="1" ht="12" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" s="130" customFormat="1" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="566"/>
       <c r="B8" s="130" t="s">
         <v>294</v>
@@ -64494,13 +64495,13 @@
       <c r="W8" s="192"/>
       <c r="X8" s="192"/>
     </row>
-    <row r="9" spans="1:24" s="130" customFormat="1" ht="24" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:24" s="130" customFormat="1" ht="36" x14ac:dyDescent="0.2">
       <c r="C9" s="199" t="s">
         <v>291</v>
       </c>
       <c r="D9" s="142">
         <f>D2</f>
-        <v>0.11748738381164731</v>
+        <v>0.117487383811647</v>
       </c>
       <c r="E9" s="142">
         <f t="shared" ref="E9:X9" si="0">E2</f>
@@ -64583,7 +64584,7 @@
         <v>8.3101444498223723E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="130" customFormat="1" ht="25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" s="130" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C10" s="200" t="s">
         <v>292</v>
       </c>
@@ -64672,7 +64673,7 @@
         <v>0.74412603207059036</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="V12" s="349"/>
     </row>
   </sheetData>
